--- a/app/templates/protocol_template_2.xlsx
+++ b/app/templates/protocol_template_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\BAZA_ALL\zprp-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C5600A-B1D4-4F2F-BCEB-F3A38EAA5366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792C7F5-BD8F-46FE-9B3D-7A7FEE213935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -825,28 +825,52 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -858,6 +882,30 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -894,10 +942,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -954,12 +999,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -996,9 +1035,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1032,12 +1068,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1170,36 +1200,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1455,22 +1455,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1867,54 +1858,54 @@
       <c r="N1" s="192"/>
       <c r="O1" s="192"/>
       <c r="P1" s="192"/>
-      <c r="Q1" s="150" t="s">
+      <c r="Q1" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="150"/>
-      <c r="AK1" s="150"/>
-      <c r="AL1" s="150"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="150"/>
-      <c r="AO1" s="150"/>
-      <c r="AP1" s="150"/>
-      <c r="AQ1" s="151"/>
-      <c r="AR1" s="127" t="s">
+      <c r="R1" s="160"/>
+      <c r="S1" s="160"/>
+      <c r="T1" s="160"/>
+      <c r="U1" s="160"/>
+      <c r="V1" s="160"/>
+      <c r="W1" s="160"/>
+      <c r="X1" s="160"/>
+      <c r="Y1" s="160"/>
+      <c r="Z1" s="160"/>
+      <c r="AA1" s="160"/>
+      <c r="AB1" s="160"/>
+      <c r="AC1" s="160"/>
+      <c r="AD1" s="160"/>
+      <c r="AE1" s="160"/>
+      <c r="AF1" s="160"/>
+      <c r="AG1" s="160"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="160"/>
+      <c r="AJ1" s="160"/>
+      <c r="AK1" s="160"/>
+      <c r="AL1" s="160"/>
+      <c r="AM1" s="160"/>
+      <c r="AN1" s="160"/>
+      <c r="AO1" s="160"/>
+      <c r="AP1" s="160"/>
+      <c r="AQ1" s="161"/>
+      <c r="AR1" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="AS1" s="127"/>
-      <c r="AT1" s="127"/>
-      <c r="AU1" s="127"/>
-      <c r="AV1" s="127"/>
-      <c r="AW1" s="127"/>
-      <c r="AX1" s="127"/>
-      <c r="AY1" s="127"/>
-      <c r="AZ1" s="127"/>
-      <c r="BA1" s="127"/>
-      <c r="BB1" s="127"/>
-      <c r="BC1" s="127"/>
-      <c r="BD1" s="127"/>
-      <c r="BE1" s="127"/>
-      <c r="BF1" s="127"/>
-      <c r="BG1" s="127"/>
-      <c r="BH1" s="127"/>
+      <c r="AS1" s="137"/>
+      <c r="AT1" s="137"/>
+      <c r="AU1" s="137"/>
+      <c r="AV1" s="137"/>
+      <c r="AW1" s="137"/>
+      <c r="AX1" s="137"/>
+      <c r="AY1" s="137"/>
+      <c r="AZ1" s="137"/>
+      <c r="BA1" s="137"/>
+      <c r="BB1" s="137"/>
+      <c r="BC1" s="137"/>
+      <c r="BD1" s="137"/>
+      <c r="BE1" s="137"/>
+      <c r="BF1" s="137"/>
+      <c r="BG1" s="137"/>
+      <c r="BH1" s="137"/>
     </row>
     <row r="2" spans="2:62" ht="13.2" customHeight="1">
       <c r="B2" s="193"/>
@@ -1932,71 +1923,71 @@
       <c r="N2" s="194"/>
       <c r="O2" s="194"/>
       <c r="P2" s="194"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="152"/>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="152"/>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="152"/>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="152"/>
-      <c r="AO2" s="152"/>
-      <c r="AP2" s="152"/>
-      <c r="AQ2" s="153"/>
-      <c r="AR2" s="128"/>
-      <c r="AS2" s="128"/>
-      <c r="AT2" s="128"/>
-      <c r="AU2" s="128"/>
-      <c r="AV2" s="128"/>
-      <c r="AW2" s="128"/>
-      <c r="AX2" s="128"/>
-      <c r="AY2" s="128"/>
-      <c r="AZ2" s="128"/>
-      <c r="BA2" s="128"/>
-      <c r="BB2" s="128"/>
-      <c r="BC2" s="128"/>
-      <c r="BD2" s="128"/>
-      <c r="BE2" s="128"/>
-      <c r="BF2" s="128"/>
-      <c r="BG2" s="128"/>
-      <c r="BH2" s="128"/>
+      <c r="Q2" s="162"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="162"/>
+      <c r="T2" s="162"/>
+      <c r="U2" s="162"/>
+      <c r="V2" s="162"/>
+      <c r="W2" s="162"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="162"/>
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="162"/>
+      <c r="AC2" s="162"/>
+      <c r="AD2" s="162"/>
+      <c r="AE2" s="162"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="162"/>
+      <c r="AH2" s="162"/>
+      <c r="AI2" s="162"/>
+      <c r="AJ2" s="162"/>
+      <c r="AK2" s="162"/>
+      <c r="AL2" s="162"/>
+      <c r="AM2" s="162"/>
+      <c r="AN2" s="162"/>
+      <c r="AO2" s="162"/>
+      <c r="AP2" s="162"/>
+      <c r="AQ2" s="163"/>
+      <c r="AR2" s="138"/>
+      <c r="AS2" s="138"/>
+      <c r="AT2" s="138"/>
+      <c r="AU2" s="138"/>
+      <c r="AV2" s="138"/>
+      <c r="AW2" s="138"/>
+      <c r="AX2" s="138"/>
+      <c r="AY2" s="138"/>
+      <c r="AZ2" s="138"/>
+      <c r="BA2" s="138"/>
+      <c r="BB2" s="138"/>
+      <c r="BC2" s="138"/>
+      <c r="BD2" s="138"/>
+      <c r="BE2" s="138"/>
+      <c r="BF2" s="138"/>
+      <c r="BG2" s="138"/>
+      <c r="BH2" s="138"/>
     </row>
     <row r="3" spans="2:62" ht="13.2" customHeight="1">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="131"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="141"/>
       <c r="S3" s="198" t="s">
         <v>1</v>
       </c>
@@ -2094,28 +2085,28 @@
       <c r="AJ4" s="196"/>
       <c r="AK4" s="196"/>
       <c r="AL4" s="197"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="122"/>
-      <c r="AQ4" s="122"/>
-      <c r="AR4" s="122"/>
-      <c r="AS4" s="122"/>
-      <c r="AT4" s="122"/>
-      <c r="AU4" s="122"/>
-      <c r="AV4" s="122"/>
-      <c r="AW4" s="122"/>
-      <c r="AX4" s="122"/>
-      <c r="AY4" s="122"/>
-      <c r="AZ4" s="122"/>
-      <c r="BA4" s="122"/>
-      <c r="BB4" s="122"/>
-      <c r="BC4" s="122"/>
-      <c r="BD4" s="122"/>
-      <c r="BE4" s="122"/>
-      <c r="BF4" s="122"/>
-      <c r="BG4" s="122"/>
-      <c r="BH4" s="123"/>
+      <c r="AM4" s="131"/>
+      <c r="AN4" s="132"/>
+      <c r="AO4" s="132"/>
+      <c r="AP4" s="132"/>
+      <c r="AQ4" s="132"/>
+      <c r="AR4" s="132"/>
+      <c r="AS4" s="132"/>
+      <c r="AT4" s="132"/>
+      <c r="AU4" s="132"/>
+      <c r="AV4" s="132"/>
+      <c r="AW4" s="132"/>
+      <c r="AX4" s="132"/>
+      <c r="AY4" s="132"/>
+      <c r="AZ4" s="132"/>
+      <c r="BA4" s="132"/>
+      <c r="BB4" s="132"/>
+      <c r="BC4" s="132"/>
+      <c r="BD4" s="132"/>
+      <c r="BE4" s="132"/>
+      <c r="BF4" s="132"/>
+      <c r="BG4" s="132"/>
+      <c r="BH4" s="133"/>
     </row>
     <row r="5" spans="2:62" ht="13.2" customHeight="1">
       <c r="B5" s="7"/>
@@ -2161,49 +2152,49 @@
       <c r="AJ5" s="196"/>
       <c r="AK5" s="196"/>
       <c r="AL5" s="197"/>
-      <c r="AM5" s="124"/>
-      <c r="AN5" s="125"/>
-      <c r="AO5" s="125"/>
-      <c r="AP5" s="125"/>
-      <c r="AQ5" s="125"/>
-      <c r="AR5" s="125"/>
-      <c r="AS5" s="125"/>
-      <c r="AT5" s="125"/>
-      <c r="AU5" s="125"/>
-      <c r="AV5" s="125"/>
-      <c r="AW5" s="125"/>
-      <c r="AX5" s="125"/>
-      <c r="AY5" s="125"/>
-      <c r="AZ5" s="125"/>
-      <c r="BA5" s="125"/>
-      <c r="BB5" s="125"/>
-      <c r="BC5" s="125"/>
-      <c r="BD5" s="125"/>
-      <c r="BE5" s="125"/>
-      <c r="BF5" s="125"/>
-      <c r="BG5" s="125"/>
-      <c r="BH5" s="126"/>
+      <c r="AM5" s="134"/>
+      <c r="AN5" s="135"/>
+      <c r="AO5" s="135"/>
+      <c r="AP5" s="135"/>
+      <c r="AQ5" s="135"/>
+      <c r="AR5" s="135"/>
+      <c r="AS5" s="135"/>
+      <c r="AT5" s="135"/>
+      <c r="AU5" s="135"/>
+      <c r="AV5" s="135"/>
+      <c r="AW5" s="135"/>
+      <c r="AX5" s="135"/>
+      <c r="AY5" s="135"/>
+      <c r="AZ5" s="135"/>
+      <c r="BA5" s="135"/>
+      <c r="BB5" s="135"/>
+      <c r="BC5" s="135"/>
+      <c r="BD5" s="135"/>
+      <c r="BE5" s="135"/>
+      <c r="BF5" s="135"/>
+      <c r="BG5" s="135"/>
+      <c r="BH5" s="136"/>
     </row>
     <row r="6" spans="2:62" ht="13.2" customHeight="1">
-      <c r="B6" s="129" t="s">
+      <c r="B6" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="131"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="141"/>
       <c r="S6" s="200"/>
       <c r="T6" s="201"/>
       <c r="U6" s="17"/>
@@ -2352,23 +2343,23 @@
       <c r="X8" s="186"/>
       <c r="Y8" s="186"/>
       <c r="Z8" s="187"/>
-      <c r="AA8" s="155" t="s">
+      <c r="AA8" s="165" t="s">
         <v>75</v>
       </c>
-      <c r="AB8" s="156"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="157"/>
-      <c r="AE8" s="157"/>
-      <c r="AF8" s="158"/>
-      <c r="AG8" s="93" t="s">
+      <c r="AB8" s="166"/>
+      <c r="AC8" s="167"/>
+      <c r="AD8" s="167"/>
+      <c r="AE8" s="167"/>
+      <c r="AF8" s="168"/>
+      <c r="AG8" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="AH8" s="94"/>
-      <c r="AI8" s="95"/>
-      <c r="AJ8" s="95"/>
-      <c r="AK8" s="95"/>
-      <c r="AL8" s="96"/>
-      <c r="AM8" s="163" t="s">
+      <c r="AH8" s="107"/>
+      <c r="AI8" s="108"/>
+      <c r="AJ8" s="108"/>
+      <c r="AK8" s="108"/>
+      <c r="AL8" s="109"/>
+      <c r="AM8" s="87" t="s">
         <v>2</v>
       </c>
       <c r="AN8" s="28"/>
@@ -2388,7 +2379,7 @@
       <c r="AZ8" s="28"/>
       <c r="BA8" s="28"/>
       <c r="BB8" s="29"/>
-      <c r="BC8" s="163" t="s">
+      <c r="BC8" s="87" t="s">
         <v>4</v>
       </c>
       <c r="BD8" s="28"/>
@@ -2398,136 +2389,136 @@
       <c r="BH8" s="29"/>
     </row>
     <row r="9" spans="2:62">
-      <c r="B9" s="163" t="s">
+      <c r="B9" s="87" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
-      <c r="E9" s="161">
+      <c r="E9" s="171">
         <f>D4</f>
         <v>0</v>
       </c>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
-      <c r="L9" s="161"/>
-      <c r="M9" s="161"/>
-      <c r="N9" s="161"/>
-      <c r="O9" s="161"/>
-      <c r="P9" s="161"/>
-      <c r="Q9" s="161"/>
-      <c r="R9" s="161"/>
-      <c r="S9" s="161"/>
-      <c r="T9" s="161"/>
-      <c r="U9" s="162"/>
-      <c r="V9" s="116" t="s">
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
+      <c r="H9" s="171"/>
+      <c r="I9" s="171"/>
+      <c r="J9" s="171"/>
+      <c r="K9" s="171"/>
+      <c r="L9" s="171"/>
+      <c r="M9" s="171"/>
+      <c r="N9" s="171"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="171"/>
+      <c r="Q9" s="171"/>
+      <c r="R9" s="171"/>
+      <c r="S9" s="171"/>
+      <c r="T9" s="171"/>
+      <c r="U9" s="172"/>
+      <c r="V9" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="W9" s="117"/>
-      <c r="X9" s="117"/>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="117"/>
-      <c r="AA9" s="117"/>
-      <c r="AB9" s="117"/>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117"/>
-      <c r="AG9" s="117"/>
-      <c r="AH9" s="117"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="118"/>
-      <c r="AM9" s="55" t="s">
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
+      <c r="AA9" s="57"/>
+      <c r="AB9" s="57"/>
+      <c r="AC9" s="57"/>
+      <c r="AD9" s="57"/>
+      <c r="AE9" s="57"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="57"/>
+      <c r="AH9" s="57"/>
+      <c r="AI9" s="57"/>
+      <c r="AJ9" s="57"/>
+      <c r="AK9" s="57"/>
+      <c r="AL9" s="58"/>
+      <c r="AM9" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="AN9" s="50"/>
-      <c r="AO9" s="50"/>
-      <c r="AP9" s="50"/>
-      <c r="AQ9" s="50"/>
-      <c r="AR9" s="50"/>
-      <c r="AS9" s="50"/>
-      <c r="AT9" s="50"/>
-      <c r="AU9" s="50"/>
-      <c r="AV9" s="50"/>
-      <c r="AW9" s="50"/>
-      <c r="AX9" s="50"/>
-      <c r="AY9" s="50"/>
-      <c r="AZ9" s="50"/>
-      <c r="BA9" s="50"/>
-      <c r="BB9" s="50"/>
-      <c r="BC9" s="50"/>
-      <c r="BD9" s="50"/>
-      <c r="BE9" s="50"/>
-      <c r="BF9" s="50"/>
-      <c r="BG9" s="50"/>
-      <c r="BH9" s="51"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="71"/>
+      <c r="AP9" s="71"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="71"/>
+      <c r="AS9" s="71"/>
+      <c r="AT9" s="71"/>
+      <c r="AU9" s="71"/>
+      <c r="AV9" s="71"/>
+      <c r="AW9" s="71"/>
+      <c r="AX9" s="71"/>
+      <c r="AY9" s="71"/>
+      <c r="AZ9" s="71"/>
+      <c r="BA9" s="71"/>
+      <c r="BB9" s="71"/>
+      <c r="BC9" s="71"/>
+      <c r="BD9" s="71"/>
+      <c r="BE9" s="71"/>
+      <c r="BF9" s="71"/>
+      <c r="BG9" s="71"/>
+      <c r="BH9" s="63"/>
     </row>
     <row r="10" spans="2:62">
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="116" t="s">
+      <c r="C10" s="58"/>
+      <c r="D10" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="117"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="117"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="117"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="117"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="116" t="s">
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="S10" s="118"/>
-      <c r="T10" s="116" t="s">
+      <c r="S10" s="58"/>
+      <c r="T10" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="U10" s="118"/>
-      <c r="V10" s="116" t="s">
+      <c r="U10" s="58"/>
+      <c r="V10" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="W10" s="118"/>
-      <c r="X10" s="116" t="s">
+      <c r="W10" s="58"/>
+      <c r="X10" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="Y10" s="117"/>
-      <c r="Z10" s="118"/>
-      <c r="AA10" s="116" t="s">
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="58"/>
+      <c r="AA10" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AB10" s="117"/>
-      <c r="AC10" s="118"/>
-      <c r="AD10" s="116" t="s">
+      <c r="AB10" s="57"/>
+      <c r="AC10" s="58"/>
+      <c r="AD10" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AE10" s="117"/>
-      <c r="AF10" s="118"/>
-      <c r="AG10" s="116" t="s">
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="58"/>
+      <c r="AG10" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="AH10" s="117"/>
-      <c r="AI10" s="118"/>
-      <c r="AJ10" s="116" t="s">
+      <c r="AH10" s="57"/>
+      <c r="AI10" s="58"/>
+      <c r="AJ10" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="118"/>
+      <c r="AK10" s="57"/>
+      <c r="AL10" s="58"/>
       <c r="AM10" s="188"/>
       <c r="AN10" s="189"/>
-      <c r="AO10" s="91" t="s">
+      <c r="AO10" s="67" t="s">
         <v>7</v>
       </c>
       <c r="AP10" s="190"/>
@@ -2535,12 +2526,12 @@
       <c r="AR10" s="190"/>
       <c r="AS10" s="190"/>
       <c r="AT10" s="190"/>
-      <c r="AU10" s="92"/>
+      <c r="AU10" s="68"/>
       <c r="AV10" s="188"/>
       <c r="AW10" s="189"/>
       <c r="AX10" s="188"/>
       <c r="AY10" s="189"/>
-      <c r="AZ10" s="91" t="s">
+      <c r="AZ10" s="67" t="s">
         <v>8</v>
       </c>
       <c r="BA10" s="190"/>
@@ -2548,51 +2539,51 @@
       <c r="BC10" s="190"/>
       <c r="BD10" s="190"/>
       <c r="BE10" s="190"/>
-      <c r="BF10" s="92"/>
+      <c r="BF10" s="68"/>
       <c r="BG10" s="188"/>
       <c r="BH10" s="189"/>
     </row>
     <row r="11" spans="2:62">
-      <c r="B11" s="111"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="57"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="106"/>
-      <c r="S11" s="107"/>
-      <c r="T11" s="91"/>
-      <c r="U11" s="107"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="109"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="109"/>
-      <c r="AC11" s="110"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="109"/>
-      <c r="AF11" s="110"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="109"/>
-      <c r="AI11" s="110"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="109"/>
-      <c r="AL11" s="110"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="65"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="118"/>
+      <c r="S11" s="119"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="119"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="122"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="121"/>
+      <c r="Z11" s="122"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="121"/>
+      <c r="AC11" s="122"/>
+      <c r="AD11" s="72"/>
+      <c r="AE11" s="121"/>
+      <c r="AF11" s="122"/>
+      <c r="AG11" s="72"/>
+      <c r="AH11" s="121"/>
+      <c r="AI11" s="122"/>
+      <c r="AJ11" s="72"/>
+      <c r="AK11" s="121"/>
+      <c r="AL11" s="122"/>
       <c r="AM11" s="188"/>
       <c r="AN11" s="189"/>
-      <c r="AO11" s="91" t="s">
+      <c r="AO11" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AP11" s="190"/>
@@ -2600,12 +2591,12 @@
       <c r="AR11" s="190"/>
       <c r="AS11" s="190"/>
       <c r="AT11" s="190"/>
-      <c r="AU11" s="92"/>
+      <c r="AU11" s="68"/>
       <c r="AV11" s="188"/>
       <c r="AW11" s="189"/>
       <c r="AX11" s="188"/>
       <c r="AY11" s="189"/>
-      <c r="AZ11" s="91" t="s">
+      <c r="AZ11" s="67" t="s">
         <v>9</v>
       </c>
       <c r="BA11" s="190"/>
@@ -2613,49 +2604,49 @@
       <c r="BC11" s="190"/>
       <c r="BD11" s="190"/>
       <c r="BE11" s="190"/>
-      <c r="BF11" s="92"/>
+      <c r="BF11" s="68"/>
       <c r="BG11" s="188"/>
       <c r="BH11" s="189"/>
       <c r="BJ11" s="11"/>
     </row>
     <row r="12" spans="2:62">
-      <c r="B12" s="55"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="107"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="107"/>
-      <c r="V12" s="108"/>
-      <c r="W12" s="110"/>
-      <c r="X12" s="108"/>
-      <c r="Y12" s="109"/>
-      <c r="Z12" s="110"/>
-      <c r="AA12" s="108"/>
-      <c r="AB12" s="109"/>
-      <c r="AC12" s="110"/>
-      <c r="AD12" s="108"/>
-      <c r="AE12" s="109"/>
-      <c r="AF12" s="110"/>
-      <c r="AG12" s="108"/>
-      <c r="AH12" s="109"/>
-      <c r="AI12" s="110"/>
-      <c r="AJ12" s="108"/>
-      <c r="AK12" s="109"/>
-      <c r="AL12" s="110"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="65"/>
+      <c r="P12" s="65"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="118"/>
+      <c r="S12" s="119"/>
+      <c r="T12" s="118"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="122"/>
+      <c r="X12" s="120"/>
+      <c r="Y12" s="121"/>
+      <c r="Z12" s="122"/>
+      <c r="AA12" s="120"/>
+      <c r="AB12" s="121"/>
+      <c r="AC12" s="122"/>
+      <c r="AD12" s="120"/>
+      <c r="AE12" s="121"/>
+      <c r="AF12" s="122"/>
+      <c r="AG12" s="120"/>
+      <c r="AH12" s="121"/>
+      <c r="AI12" s="122"/>
+      <c r="AJ12" s="120"/>
+      <c r="AK12" s="121"/>
+      <c r="AL12" s="122"/>
       <c r="AM12" s="237" t="s">
         <v>10</v>
       </c>
@@ -2696,43 +2687,43 @@
       <c r="BH12" s="232"/>
     </row>
     <row r="13" spans="2:62">
-      <c r="B13" s="55"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="57"/>
-      <c r="P13" s="57"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="106"/>
-      <c r="S13" s="107"/>
-      <c r="T13" s="106"/>
-      <c r="U13" s="107"/>
-      <c r="V13" s="108"/>
-      <c r="W13" s="110"/>
-      <c r="X13" s="108"/>
-      <c r="Y13" s="109"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="108"/>
-      <c r="AB13" s="109"/>
-      <c r="AC13" s="110"/>
-      <c r="AD13" s="108"/>
-      <c r="AE13" s="109"/>
-      <c r="AF13" s="110"/>
-      <c r="AG13" s="108"/>
-      <c r="AH13" s="109"/>
-      <c r="AI13" s="110"/>
-      <c r="AJ13" s="108"/>
-      <c r="AK13" s="109"/>
-      <c r="AL13" s="110"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="119"/>
+      <c r="T13" s="118"/>
+      <c r="U13" s="119"/>
+      <c r="V13" s="120"/>
+      <c r="W13" s="122"/>
+      <c r="X13" s="120"/>
+      <c r="Y13" s="121"/>
+      <c r="Z13" s="122"/>
+      <c r="AA13" s="120"/>
+      <c r="AB13" s="121"/>
+      <c r="AC13" s="122"/>
+      <c r="AD13" s="120"/>
+      <c r="AE13" s="121"/>
+      <c r="AF13" s="122"/>
+      <c r="AG13" s="120"/>
+      <c r="AH13" s="121"/>
+      <c r="AI13" s="122"/>
+      <c r="AJ13" s="120"/>
+      <c r="AK13" s="121"/>
+      <c r="AL13" s="122"/>
       <c r="AM13" s="239"/>
       <c r="AN13" s="240"/>
       <c r="AO13" s="233"/>
@@ -2757,43 +2748,43 @@
       <c r="BH13" s="234"/>
     </row>
     <row r="14" spans="2:62">
-      <c r="B14" s="55"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="106"/>
-      <c r="S14" s="107"/>
-      <c r="T14" s="106"/>
-      <c r="U14" s="107"/>
-      <c r="V14" s="108"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="108"/>
-      <c r="Y14" s="109"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="108"/>
-      <c r="AB14" s="109"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="108"/>
-      <c r="AE14" s="109"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="108"/>
-      <c r="AH14" s="109"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="108"/>
-      <c r="AK14" s="109"/>
-      <c r="AL14" s="110"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="119"/>
+      <c r="T14" s="118"/>
+      <c r="U14" s="119"/>
+      <c r="V14" s="120"/>
+      <c r="W14" s="122"/>
+      <c r="X14" s="120"/>
+      <c r="Y14" s="121"/>
+      <c r="Z14" s="122"/>
+      <c r="AA14" s="120"/>
+      <c r="AB14" s="121"/>
+      <c r="AC14" s="122"/>
+      <c r="AD14" s="120"/>
+      <c r="AE14" s="121"/>
+      <c r="AF14" s="122"/>
+      <c r="AG14" s="120"/>
+      <c r="AH14" s="121"/>
+      <c r="AI14" s="122"/>
+      <c r="AJ14" s="120"/>
+      <c r="AK14" s="121"/>
+      <c r="AL14" s="122"/>
       <c r="AM14" s="241"/>
       <c r="AN14" s="242"/>
       <c r="AO14" s="235"/>
@@ -2818,914 +2809,914 @@
       <c r="BH14" s="236"/>
     </row>
     <row r="15" spans="2:62">
-      <c r="B15" s="55"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="57"/>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="106"/>
-      <c r="S15" s="107"/>
-      <c r="T15" s="106"/>
-      <c r="U15" s="107"/>
-      <c r="V15" s="108"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="108"/>
-      <c r="Y15" s="109"/>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="108"/>
-      <c r="AB15" s="109"/>
-      <c r="AC15" s="110"/>
-      <c r="AD15" s="108"/>
-      <c r="AE15" s="109"/>
-      <c r="AF15" s="110"/>
-      <c r="AG15" s="108"/>
-      <c r="AH15" s="109"/>
-      <c r="AI15" s="110"/>
-      <c r="AJ15" s="108"/>
-      <c r="AK15" s="109"/>
-      <c r="AL15" s="110"/>
-      <c r="AM15" s="111"/>
-      <c r="AN15" s="112"/>
-      <c r="AO15" s="113"/>
-      <c r="AP15" s="60"/>
-      <c r="AQ15" s="114"/>
-      <c r="AR15" s="62"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="118"/>
+      <c r="S15" s="119"/>
+      <c r="T15" s="118"/>
+      <c r="U15" s="119"/>
+      <c r="V15" s="120"/>
+      <c r="W15" s="122"/>
+      <c r="X15" s="120"/>
+      <c r="Y15" s="121"/>
+      <c r="Z15" s="122"/>
+      <c r="AA15" s="120"/>
+      <c r="AB15" s="121"/>
+      <c r="AC15" s="122"/>
+      <c r="AD15" s="120"/>
+      <c r="AE15" s="121"/>
+      <c r="AF15" s="122"/>
+      <c r="AG15" s="120"/>
+      <c r="AH15" s="121"/>
+      <c r="AI15" s="122"/>
+      <c r="AJ15" s="120"/>
+      <c r="AK15" s="121"/>
+      <c r="AL15" s="122"/>
+      <c r="AM15" s="123"/>
+      <c r="AN15" s="124"/>
+      <c r="AO15" s="125"/>
+      <c r="AP15" s="76"/>
+      <c r="AQ15" s="126"/>
+      <c r="AR15" s="78"/>
       <c r="AS15" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT15" s="115"/>
-      <c r="AU15" s="64"/>
-      <c r="AV15" s="59"/>
-      <c r="AW15" s="60"/>
-      <c r="AX15" s="55"/>
-      <c r="AY15" s="112"/>
-      <c r="AZ15" s="113"/>
-      <c r="BA15" s="60"/>
-      <c r="BB15" s="114"/>
-      <c r="BC15" s="62"/>
+      <c r="AT15" s="127"/>
+      <c r="AU15" s="80"/>
+      <c r="AV15" s="75"/>
+      <c r="AW15" s="76"/>
+      <c r="AX15" s="62"/>
+      <c r="AY15" s="124"/>
+      <c r="AZ15" s="125"/>
+      <c r="BA15" s="76"/>
+      <c r="BB15" s="126"/>
+      <c r="BC15" s="78"/>
       <c r="BD15" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE15" s="115"/>
-      <c r="BF15" s="64"/>
-      <c r="BG15" s="59"/>
-      <c r="BH15" s="60"/>
+      <c r="BE15" s="127"/>
+      <c r="BF15" s="80"/>
+      <c r="BG15" s="75"/>
+      <c r="BH15" s="76"/>
     </row>
     <row r="16" spans="2:62">
-      <c r="B16" s="55"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="106"/>
-      <c r="S16" s="107"/>
-      <c r="T16" s="106"/>
-      <c r="U16" s="107"/>
-      <c r="V16" s="108"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="108"/>
-      <c r="Y16" s="109"/>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="108"/>
-      <c r="AB16" s="109"/>
-      <c r="AC16" s="110"/>
-      <c r="AD16" s="108"/>
-      <c r="AE16" s="109"/>
-      <c r="AF16" s="110"/>
-      <c r="AG16" s="108"/>
-      <c r="AH16" s="109"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="108"/>
-      <c r="AK16" s="109"/>
-      <c r="AL16" s="110"/>
-      <c r="AM16" s="55"/>
-      <c r="AN16" s="112"/>
-      <c r="AO16" s="113"/>
-      <c r="AP16" s="60"/>
-      <c r="AQ16" s="114"/>
-      <c r="AR16" s="62"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="118"/>
+      <c r="U16" s="119"/>
+      <c r="V16" s="120"/>
+      <c r="W16" s="122"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="122"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="121"/>
+      <c r="AC16" s="122"/>
+      <c r="AD16" s="120"/>
+      <c r="AE16" s="121"/>
+      <c r="AF16" s="122"/>
+      <c r="AG16" s="120"/>
+      <c r="AH16" s="121"/>
+      <c r="AI16" s="122"/>
+      <c r="AJ16" s="120"/>
+      <c r="AK16" s="121"/>
+      <c r="AL16" s="122"/>
+      <c r="AM16" s="62"/>
+      <c r="AN16" s="124"/>
+      <c r="AO16" s="125"/>
+      <c r="AP16" s="76"/>
+      <c r="AQ16" s="126"/>
+      <c r="AR16" s="78"/>
       <c r="AS16" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT16" s="115"/>
-      <c r="AU16" s="64"/>
-      <c r="AV16" s="59"/>
-      <c r="AW16" s="60"/>
-      <c r="AX16" s="55"/>
-      <c r="AY16" s="112"/>
-      <c r="AZ16" s="59"/>
-      <c r="BA16" s="60"/>
-      <c r="BB16" s="114"/>
-      <c r="BC16" s="62"/>
+      <c r="AT16" s="127"/>
+      <c r="AU16" s="80"/>
+      <c r="AV16" s="75"/>
+      <c r="AW16" s="76"/>
+      <c r="AX16" s="62"/>
+      <c r="AY16" s="124"/>
+      <c r="AZ16" s="75"/>
+      <c r="BA16" s="76"/>
+      <c r="BB16" s="126"/>
+      <c r="BC16" s="78"/>
       <c r="BD16" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE16" s="115"/>
-      <c r="BF16" s="64"/>
-      <c r="BG16" s="113"/>
-      <c r="BH16" s="60"/>
+      <c r="BE16" s="127"/>
+      <c r="BF16" s="80"/>
+      <c r="BG16" s="125"/>
+      <c r="BH16" s="76"/>
     </row>
     <row r="17" spans="2:60">
-      <c r="B17" s="55"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="106"/>
-      <c r="S17" s="107"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="107"/>
-      <c r="V17" s="108"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="108"/>
-      <c r="Y17" s="109"/>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="108"/>
-      <c r="AB17" s="109"/>
-      <c r="AC17" s="110"/>
-      <c r="AD17" s="108"/>
-      <c r="AE17" s="109"/>
-      <c r="AF17" s="110"/>
-      <c r="AG17" s="108"/>
-      <c r="AH17" s="109"/>
-      <c r="AI17" s="110"/>
-      <c r="AJ17" s="108"/>
-      <c r="AK17" s="109"/>
-      <c r="AL17" s="110"/>
-      <c r="AM17" s="55"/>
-      <c r="AN17" s="112"/>
-      <c r="AO17" s="113"/>
-      <c r="AP17" s="60"/>
-      <c r="AQ17" s="114"/>
-      <c r="AR17" s="62"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="65"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="118"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="118"/>
+      <c r="U17" s="119"/>
+      <c r="V17" s="120"/>
+      <c r="W17" s="122"/>
+      <c r="X17" s="120"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="122"/>
+      <c r="AA17" s="120"/>
+      <c r="AB17" s="121"/>
+      <c r="AC17" s="122"/>
+      <c r="AD17" s="120"/>
+      <c r="AE17" s="121"/>
+      <c r="AF17" s="122"/>
+      <c r="AG17" s="120"/>
+      <c r="AH17" s="121"/>
+      <c r="AI17" s="122"/>
+      <c r="AJ17" s="120"/>
+      <c r="AK17" s="121"/>
+      <c r="AL17" s="122"/>
+      <c r="AM17" s="62"/>
+      <c r="AN17" s="124"/>
+      <c r="AO17" s="125"/>
+      <c r="AP17" s="76"/>
+      <c r="AQ17" s="126"/>
+      <c r="AR17" s="78"/>
       <c r="AS17" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT17" s="115"/>
-      <c r="AU17" s="64"/>
-      <c r="AV17" s="59"/>
-      <c r="AW17" s="60"/>
-      <c r="AX17" s="111"/>
-      <c r="AY17" s="112"/>
-      <c r="AZ17" s="59"/>
-      <c r="BA17" s="60"/>
-      <c r="BB17" s="61"/>
-      <c r="BC17" s="62"/>
+      <c r="AT17" s="127"/>
+      <c r="AU17" s="80"/>
+      <c r="AV17" s="75"/>
+      <c r="AW17" s="76"/>
+      <c r="AX17" s="123"/>
+      <c r="AY17" s="124"/>
+      <c r="AZ17" s="75"/>
+      <c r="BA17" s="76"/>
+      <c r="BB17" s="77"/>
+      <c r="BC17" s="78"/>
       <c r="BD17" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE17" s="63"/>
-      <c r="BF17" s="64"/>
-      <c r="BG17" s="59"/>
-      <c r="BH17" s="60"/>
+      <c r="BE17" s="79"/>
+      <c r="BF17" s="80"/>
+      <c r="BG17" s="75"/>
+      <c r="BH17" s="76"/>
     </row>
     <row r="18" spans="2:60">
-      <c r="B18" s="55"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="106"/>
-      <c r="S18" s="107"/>
-      <c r="T18" s="106"/>
-      <c r="U18" s="107"/>
-      <c r="V18" s="108"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="109"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="109"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="108"/>
-      <c r="AE18" s="109"/>
-      <c r="AF18" s="110"/>
-      <c r="AG18" s="108"/>
-      <c r="AH18" s="109"/>
-      <c r="AI18" s="110"/>
-      <c r="AJ18" s="108"/>
-      <c r="AK18" s="109"/>
-      <c r="AL18" s="110"/>
-      <c r="AM18" s="111"/>
-      <c r="AN18" s="112"/>
-      <c r="AO18" s="113"/>
-      <c r="AP18" s="60"/>
-      <c r="AQ18" s="114"/>
-      <c r="AR18" s="62"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="65"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="118"/>
+      <c r="S18" s="119"/>
+      <c r="T18" s="118"/>
+      <c r="U18" s="119"/>
+      <c r="V18" s="120"/>
+      <c r="W18" s="122"/>
+      <c r="X18" s="120"/>
+      <c r="Y18" s="121"/>
+      <c r="Z18" s="122"/>
+      <c r="AA18" s="120"/>
+      <c r="AB18" s="121"/>
+      <c r="AC18" s="122"/>
+      <c r="AD18" s="120"/>
+      <c r="AE18" s="121"/>
+      <c r="AF18" s="122"/>
+      <c r="AG18" s="120"/>
+      <c r="AH18" s="121"/>
+      <c r="AI18" s="122"/>
+      <c r="AJ18" s="120"/>
+      <c r="AK18" s="121"/>
+      <c r="AL18" s="122"/>
+      <c r="AM18" s="123"/>
+      <c r="AN18" s="124"/>
+      <c r="AO18" s="125"/>
+      <c r="AP18" s="76"/>
+      <c r="AQ18" s="126"/>
+      <c r="AR18" s="78"/>
       <c r="AS18" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT18" s="115"/>
-      <c r="AU18" s="64"/>
-      <c r="AV18" s="59"/>
-      <c r="AW18" s="60"/>
-      <c r="AX18" s="111"/>
-      <c r="AY18" s="112"/>
-      <c r="AZ18" s="59"/>
-      <c r="BA18" s="60"/>
-      <c r="BB18" s="61"/>
-      <c r="BC18" s="62"/>
+      <c r="AT18" s="127"/>
+      <c r="AU18" s="80"/>
+      <c r="AV18" s="75"/>
+      <c r="AW18" s="76"/>
+      <c r="AX18" s="123"/>
+      <c r="AY18" s="124"/>
+      <c r="AZ18" s="75"/>
+      <c r="BA18" s="76"/>
+      <c r="BB18" s="77"/>
+      <c r="BC18" s="78"/>
       <c r="BD18" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE18" s="63"/>
-      <c r="BF18" s="64"/>
-      <c r="BG18" s="59"/>
-      <c r="BH18" s="60"/>
+      <c r="BE18" s="79"/>
+      <c r="BF18" s="80"/>
+      <c r="BG18" s="75"/>
+      <c r="BH18" s="76"/>
     </row>
     <row r="19" spans="2:60">
-      <c r="B19" s="55"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="106"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="106"/>
-      <c r="U19" s="107"/>
-      <c r="V19" s="108"/>
-      <c r="W19" s="110"/>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="109"/>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="109"/>
-      <c r="AC19" s="110"/>
-      <c r="AD19" s="108"/>
-      <c r="AE19" s="109"/>
-      <c r="AF19" s="110"/>
-      <c r="AG19" s="108"/>
-      <c r="AH19" s="109"/>
-      <c r="AI19" s="110"/>
-      <c r="AJ19" s="108"/>
-      <c r="AK19" s="109"/>
-      <c r="AL19" s="110"/>
-      <c r="AM19" s="111"/>
-      <c r="AN19" s="112"/>
-      <c r="AO19" s="59"/>
-      <c r="AP19" s="60"/>
-      <c r="AQ19" s="61"/>
-      <c r="AR19" s="62"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="119"/>
+      <c r="T19" s="118"/>
+      <c r="U19" s="119"/>
+      <c r="V19" s="120"/>
+      <c r="W19" s="122"/>
+      <c r="X19" s="120"/>
+      <c r="Y19" s="121"/>
+      <c r="Z19" s="122"/>
+      <c r="AA19" s="120"/>
+      <c r="AB19" s="121"/>
+      <c r="AC19" s="122"/>
+      <c r="AD19" s="120"/>
+      <c r="AE19" s="121"/>
+      <c r="AF19" s="122"/>
+      <c r="AG19" s="120"/>
+      <c r="AH19" s="121"/>
+      <c r="AI19" s="122"/>
+      <c r="AJ19" s="120"/>
+      <c r="AK19" s="121"/>
+      <c r="AL19" s="122"/>
+      <c r="AM19" s="123"/>
+      <c r="AN19" s="124"/>
+      <c r="AO19" s="75"/>
+      <c r="AP19" s="76"/>
+      <c r="AQ19" s="77"/>
+      <c r="AR19" s="78"/>
       <c r="AS19" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT19" s="63"/>
-      <c r="AU19" s="64"/>
-      <c r="AV19" s="59"/>
-      <c r="AW19" s="60"/>
-      <c r="AX19" s="111"/>
-      <c r="AY19" s="112"/>
-      <c r="AZ19" s="59"/>
-      <c r="BA19" s="60"/>
-      <c r="BB19" s="61"/>
-      <c r="BC19" s="62"/>
+      <c r="AT19" s="79"/>
+      <c r="AU19" s="80"/>
+      <c r="AV19" s="75"/>
+      <c r="AW19" s="76"/>
+      <c r="AX19" s="123"/>
+      <c r="AY19" s="124"/>
+      <c r="AZ19" s="75"/>
+      <c r="BA19" s="76"/>
+      <c r="BB19" s="77"/>
+      <c r="BC19" s="78"/>
       <c r="BD19" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE19" s="63"/>
-      <c r="BF19" s="64"/>
-      <c r="BG19" s="59"/>
-      <c r="BH19" s="60"/>
+      <c r="BE19" s="79"/>
+      <c r="BF19" s="80"/>
+      <c r="BG19" s="75"/>
+      <c r="BH19" s="76"/>
     </row>
     <row r="20" spans="2:60">
-      <c r="B20" s="55"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="106"/>
-      <c r="S20" s="107"/>
-      <c r="T20" s="106"/>
-      <c r="U20" s="107"/>
-      <c r="V20" s="108"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="108"/>
-      <c r="Y20" s="109"/>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="108"/>
-      <c r="AB20" s="109"/>
-      <c r="AC20" s="110"/>
-      <c r="AD20" s="108"/>
-      <c r="AE20" s="109"/>
-      <c r="AF20" s="110"/>
-      <c r="AG20" s="108"/>
-      <c r="AH20" s="109"/>
-      <c r="AI20" s="110"/>
-      <c r="AJ20" s="108"/>
-      <c r="AK20" s="109"/>
-      <c r="AL20" s="110"/>
-      <c r="AM20" s="111"/>
-      <c r="AN20" s="112"/>
-      <c r="AO20" s="59"/>
-      <c r="AP20" s="60"/>
-      <c r="AQ20" s="61"/>
-      <c r="AR20" s="62"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="119"/>
+      <c r="T20" s="118"/>
+      <c r="U20" s="119"/>
+      <c r="V20" s="120"/>
+      <c r="W20" s="122"/>
+      <c r="X20" s="120"/>
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="122"/>
+      <c r="AA20" s="120"/>
+      <c r="AB20" s="121"/>
+      <c r="AC20" s="122"/>
+      <c r="AD20" s="120"/>
+      <c r="AE20" s="121"/>
+      <c r="AF20" s="122"/>
+      <c r="AG20" s="120"/>
+      <c r="AH20" s="121"/>
+      <c r="AI20" s="122"/>
+      <c r="AJ20" s="120"/>
+      <c r="AK20" s="121"/>
+      <c r="AL20" s="122"/>
+      <c r="AM20" s="123"/>
+      <c r="AN20" s="124"/>
+      <c r="AO20" s="75"/>
+      <c r="AP20" s="76"/>
+      <c r="AQ20" s="77"/>
+      <c r="AR20" s="78"/>
       <c r="AS20" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT20" s="63"/>
-      <c r="AU20" s="64"/>
-      <c r="AV20" s="59"/>
-      <c r="AW20" s="60"/>
-      <c r="AX20" s="111"/>
-      <c r="AY20" s="112"/>
-      <c r="AZ20" s="59"/>
-      <c r="BA20" s="60"/>
-      <c r="BB20" s="61"/>
-      <c r="BC20" s="62"/>
+      <c r="AT20" s="79"/>
+      <c r="AU20" s="80"/>
+      <c r="AV20" s="75"/>
+      <c r="AW20" s="76"/>
+      <c r="AX20" s="123"/>
+      <c r="AY20" s="124"/>
+      <c r="AZ20" s="75"/>
+      <c r="BA20" s="76"/>
+      <c r="BB20" s="77"/>
+      <c r="BC20" s="78"/>
       <c r="BD20" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE20" s="63"/>
-      <c r="BF20" s="64"/>
-      <c r="BG20" s="59"/>
-      <c r="BH20" s="60"/>
+      <c r="BE20" s="79"/>
+      <c r="BF20" s="80"/>
+      <c r="BG20" s="75"/>
+      <c r="BH20" s="76"/>
     </row>
     <row r="21" spans="2:60">
-      <c r="B21" s="55"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="106"/>
-      <c r="S21" s="107"/>
-      <c r="T21" s="106"/>
-      <c r="U21" s="107"/>
-      <c r="V21" s="108"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="108"/>
-      <c r="Y21" s="109"/>
-      <c r="Z21" s="110"/>
-      <c r="AA21" s="108"/>
-      <c r="AB21" s="109"/>
-      <c r="AC21" s="110"/>
-      <c r="AD21" s="108"/>
-      <c r="AE21" s="109"/>
-      <c r="AF21" s="110"/>
-      <c r="AG21" s="108"/>
-      <c r="AH21" s="109"/>
-      <c r="AI21" s="110"/>
-      <c r="AJ21" s="108"/>
-      <c r="AK21" s="109"/>
-      <c r="AL21" s="110"/>
-      <c r="AM21" s="55"/>
-      <c r="AN21" s="112"/>
-      <c r="AO21" s="113"/>
-      <c r="AP21" s="60"/>
-      <c r="AQ21" s="114"/>
-      <c r="AR21" s="62"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="119"/>
+      <c r="T21" s="118"/>
+      <c r="U21" s="119"/>
+      <c r="V21" s="120"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="120"/>
+      <c r="Y21" s="121"/>
+      <c r="Z21" s="122"/>
+      <c r="AA21" s="120"/>
+      <c r="AB21" s="121"/>
+      <c r="AC21" s="122"/>
+      <c r="AD21" s="120"/>
+      <c r="AE21" s="121"/>
+      <c r="AF21" s="122"/>
+      <c r="AG21" s="120"/>
+      <c r="AH21" s="121"/>
+      <c r="AI21" s="122"/>
+      <c r="AJ21" s="120"/>
+      <c r="AK21" s="121"/>
+      <c r="AL21" s="122"/>
+      <c r="AM21" s="62"/>
+      <c r="AN21" s="124"/>
+      <c r="AO21" s="125"/>
+      <c r="AP21" s="76"/>
+      <c r="AQ21" s="126"/>
+      <c r="AR21" s="78"/>
       <c r="AS21" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT21" s="115"/>
-      <c r="AU21" s="64"/>
-      <c r="AV21" s="59"/>
-      <c r="AW21" s="60"/>
-      <c r="AX21" s="111"/>
-      <c r="AY21" s="112"/>
-      <c r="AZ21" s="59"/>
-      <c r="BA21" s="60"/>
-      <c r="BB21" s="61"/>
-      <c r="BC21" s="62"/>
+      <c r="AT21" s="127"/>
+      <c r="AU21" s="80"/>
+      <c r="AV21" s="75"/>
+      <c r="AW21" s="76"/>
+      <c r="AX21" s="123"/>
+      <c r="AY21" s="124"/>
+      <c r="AZ21" s="75"/>
+      <c r="BA21" s="76"/>
+      <c r="BB21" s="77"/>
+      <c r="BC21" s="78"/>
       <c r="BD21" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE21" s="63"/>
-      <c r="BF21" s="64"/>
-      <c r="BG21" s="59"/>
-      <c r="BH21" s="60"/>
+      <c r="BE21" s="79"/>
+      <c r="BF21" s="80"/>
+      <c r="BG21" s="75"/>
+      <c r="BH21" s="76"/>
     </row>
     <row r="22" spans="2:60">
-      <c r="B22" s="55"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="107"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="107"/>
-      <c r="V22" s="108"/>
-      <c r="W22" s="110"/>
-      <c r="X22" s="108"/>
-      <c r="Y22" s="109"/>
-      <c r="Z22" s="110"/>
-      <c r="AA22" s="108"/>
-      <c r="AB22" s="109"/>
-      <c r="AC22" s="110"/>
-      <c r="AD22" s="108"/>
-      <c r="AE22" s="109"/>
-      <c r="AF22" s="110"/>
-      <c r="AG22" s="108"/>
-      <c r="AH22" s="109"/>
-      <c r="AI22" s="110"/>
-      <c r="AJ22" s="108"/>
-      <c r="AK22" s="109"/>
-      <c r="AL22" s="110"/>
-      <c r="AM22" s="111"/>
-      <c r="AN22" s="112"/>
-      <c r="AO22" s="59"/>
-      <c r="AP22" s="60"/>
-      <c r="AQ22" s="61"/>
-      <c r="AR22" s="62"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="119"/>
+      <c r="T22" s="118"/>
+      <c r="U22" s="119"/>
+      <c r="V22" s="120"/>
+      <c r="W22" s="122"/>
+      <c r="X22" s="120"/>
+      <c r="Y22" s="121"/>
+      <c r="Z22" s="122"/>
+      <c r="AA22" s="120"/>
+      <c r="AB22" s="121"/>
+      <c r="AC22" s="122"/>
+      <c r="AD22" s="120"/>
+      <c r="AE22" s="121"/>
+      <c r="AF22" s="122"/>
+      <c r="AG22" s="120"/>
+      <c r="AH22" s="121"/>
+      <c r="AI22" s="122"/>
+      <c r="AJ22" s="120"/>
+      <c r="AK22" s="121"/>
+      <c r="AL22" s="122"/>
+      <c r="AM22" s="123"/>
+      <c r="AN22" s="124"/>
+      <c r="AO22" s="75"/>
+      <c r="AP22" s="76"/>
+      <c r="AQ22" s="77"/>
+      <c r="AR22" s="78"/>
       <c r="AS22" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT22" s="63"/>
-      <c r="AU22" s="64"/>
-      <c r="AV22" s="59"/>
-      <c r="AW22" s="60"/>
-      <c r="AX22" s="111"/>
-      <c r="AY22" s="112"/>
-      <c r="AZ22" s="59"/>
-      <c r="BA22" s="60"/>
-      <c r="BB22" s="61"/>
-      <c r="BC22" s="62"/>
+      <c r="AT22" s="79"/>
+      <c r="AU22" s="80"/>
+      <c r="AV22" s="75"/>
+      <c r="AW22" s="76"/>
+      <c r="AX22" s="123"/>
+      <c r="AY22" s="124"/>
+      <c r="AZ22" s="75"/>
+      <c r="BA22" s="76"/>
+      <c r="BB22" s="77"/>
+      <c r="BC22" s="78"/>
       <c r="BD22" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE22" s="63"/>
-      <c r="BF22" s="64"/>
-      <c r="BG22" s="59"/>
-      <c r="BH22" s="60"/>
+      <c r="BE22" s="79"/>
+      <c r="BF22" s="80"/>
+      <c r="BG22" s="75"/>
+      <c r="BH22" s="76"/>
     </row>
     <row r="23" spans="2:60">
-      <c r="B23" s="55"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="57"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="106"/>
-      <c r="S23" s="107"/>
-      <c r="T23" s="106"/>
-      <c r="U23" s="107"/>
-      <c r="V23" s="108"/>
-      <c r="W23" s="110"/>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="109"/>
-      <c r="Z23" s="110"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="109"/>
-      <c r="AC23" s="110"/>
-      <c r="AD23" s="108"/>
-      <c r="AE23" s="109"/>
-      <c r="AF23" s="110"/>
-      <c r="AG23" s="108"/>
-      <c r="AH23" s="109"/>
-      <c r="AI23" s="110"/>
-      <c r="AJ23" s="108"/>
-      <c r="AK23" s="109"/>
-      <c r="AL23" s="110"/>
-      <c r="AM23" s="55"/>
-      <c r="AN23" s="112"/>
-      <c r="AO23" s="113"/>
-      <c r="AP23" s="60"/>
-      <c r="AQ23" s="114"/>
-      <c r="AR23" s="62"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="118"/>
+      <c r="S23" s="119"/>
+      <c r="T23" s="118"/>
+      <c r="U23" s="119"/>
+      <c r="V23" s="120"/>
+      <c r="W23" s="122"/>
+      <c r="X23" s="120"/>
+      <c r="Y23" s="121"/>
+      <c r="Z23" s="122"/>
+      <c r="AA23" s="120"/>
+      <c r="AB23" s="121"/>
+      <c r="AC23" s="122"/>
+      <c r="AD23" s="120"/>
+      <c r="AE23" s="121"/>
+      <c r="AF23" s="122"/>
+      <c r="AG23" s="120"/>
+      <c r="AH23" s="121"/>
+      <c r="AI23" s="122"/>
+      <c r="AJ23" s="120"/>
+      <c r="AK23" s="121"/>
+      <c r="AL23" s="122"/>
+      <c r="AM23" s="62"/>
+      <c r="AN23" s="124"/>
+      <c r="AO23" s="125"/>
+      <c r="AP23" s="76"/>
+      <c r="AQ23" s="126"/>
+      <c r="AR23" s="78"/>
       <c r="AS23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT23" s="115"/>
-      <c r="AU23" s="64"/>
-      <c r="AV23" s="59"/>
-      <c r="AW23" s="60"/>
-      <c r="AX23" s="111"/>
-      <c r="AY23" s="112"/>
-      <c r="AZ23" s="59"/>
-      <c r="BA23" s="60"/>
-      <c r="BB23" s="61"/>
-      <c r="BC23" s="62"/>
+      <c r="AT23" s="127"/>
+      <c r="AU23" s="80"/>
+      <c r="AV23" s="75"/>
+      <c r="AW23" s="76"/>
+      <c r="AX23" s="123"/>
+      <c r="AY23" s="124"/>
+      <c r="AZ23" s="75"/>
+      <c r="BA23" s="76"/>
+      <c r="BB23" s="77"/>
+      <c r="BC23" s="78"/>
       <c r="BD23" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE23" s="63"/>
-      <c r="BF23" s="64"/>
-      <c r="BG23" s="59"/>
-      <c r="BH23" s="60"/>
+      <c r="BE23" s="79"/>
+      <c r="BF23" s="80"/>
+      <c r="BG23" s="75"/>
+      <c r="BH23" s="76"/>
     </row>
     <row r="24" spans="2:60">
-      <c r="B24" s="55"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="57"/>
-      <c r="P24" s="57"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="106"/>
-      <c r="S24" s="107"/>
-      <c r="T24" s="106"/>
-      <c r="U24" s="107"/>
-      <c r="V24" s="108"/>
-      <c r="W24" s="110"/>
-      <c r="X24" s="108"/>
-      <c r="Y24" s="109"/>
-      <c r="Z24" s="110"/>
-      <c r="AA24" s="108"/>
-      <c r="AB24" s="109"/>
-      <c r="AC24" s="110"/>
-      <c r="AD24" s="108"/>
-      <c r="AE24" s="109"/>
-      <c r="AF24" s="110"/>
-      <c r="AG24" s="108"/>
-      <c r="AH24" s="109"/>
-      <c r="AI24" s="110"/>
-      <c r="AJ24" s="108"/>
-      <c r="AK24" s="109"/>
-      <c r="AL24" s="110"/>
-      <c r="AM24" s="111"/>
-      <c r="AN24" s="112"/>
-      <c r="AO24" s="59"/>
-      <c r="AP24" s="60"/>
-      <c r="AQ24" s="61"/>
-      <c r="AR24" s="62"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="119"/>
+      <c r="T24" s="118"/>
+      <c r="U24" s="119"/>
+      <c r="V24" s="120"/>
+      <c r="W24" s="122"/>
+      <c r="X24" s="120"/>
+      <c r="Y24" s="121"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="120"/>
+      <c r="AB24" s="121"/>
+      <c r="AC24" s="122"/>
+      <c r="AD24" s="120"/>
+      <c r="AE24" s="121"/>
+      <c r="AF24" s="122"/>
+      <c r="AG24" s="120"/>
+      <c r="AH24" s="121"/>
+      <c r="AI24" s="122"/>
+      <c r="AJ24" s="120"/>
+      <c r="AK24" s="121"/>
+      <c r="AL24" s="122"/>
+      <c r="AM24" s="123"/>
+      <c r="AN24" s="124"/>
+      <c r="AO24" s="75"/>
+      <c r="AP24" s="76"/>
+      <c r="AQ24" s="77"/>
+      <c r="AR24" s="78"/>
       <c r="AS24" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT24" s="63"/>
-      <c r="AU24" s="64"/>
-      <c r="AV24" s="59"/>
-      <c r="AW24" s="60"/>
-      <c r="AX24" s="111"/>
-      <c r="AY24" s="112"/>
-      <c r="AZ24" s="59"/>
-      <c r="BA24" s="60"/>
-      <c r="BB24" s="61"/>
-      <c r="BC24" s="62"/>
+      <c r="AT24" s="79"/>
+      <c r="AU24" s="80"/>
+      <c r="AV24" s="75"/>
+      <c r="AW24" s="76"/>
+      <c r="AX24" s="123"/>
+      <c r="AY24" s="124"/>
+      <c r="AZ24" s="75"/>
+      <c r="BA24" s="76"/>
+      <c r="BB24" s="77"/>
+      <c r="BC24" s="78"/>
       <c r="BD24" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE24" s="63"/>
-      <c r="BF24" s="64"/>
-      <c r="BG24" s="59"/>
-      <c r="BH24" s="60"/>
+      <c r="BE24" s="79"/>
+      <c r="BF24" s="80"/>
+      <c r="BG24" s="75"/>
+      <c r="BH24" s="76"/>
     </row>
     <row r="25" spans="2:60">
-      <c r="B25" s="55"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="107"/>
-      <c r="T25" s="106"/>
-      <c r="U25" s="107"/>
-      <c r="V25" s="108"/>
-      <c r="W25" s="110"/>
-      <c r="X25" s="108"/>
-      <c r="Y25" s="109"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="108"/>
-      <c r="AB25" s="109"/>
-      <c r="AC25" s="110"/>
-      <c r="AD25" s="108"/>
-      <c r="AE25" s="109"/>
-      <c r="AF25" s="110"/>
-      <c r="AG25" s="108"/>
-      <c r="AH25" s="109"/>
-      <c r="AI25" s="110"/>
-      <c r="AJ25" s="108"/>
-      <c r="AK25" s="109"/>
-      <c r="AL25" s="110"/>
-      <c r="AM25" s="55"/>
-      <c r="AN25" s="112"/>
-      <c r="AO25" s="113"/>
-      <c r="AP25" s="60"/>
-      <c r="AQ25" s="114"/>
-      <c r="AR25" s="62"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="118"/>
+      <c r="S25" s="119"/>
+      <c r="T25" s="118"/>
+      <c r="U25" s="119"/>
+      <c r="V25" s="120"/>
+      <c r="W25" s="122"/>
+      <c r="X25" s="120"/>
+      <c r="Y25" s="121"/>
+      <c r="Z25" s="122"/>
+      <c r="AA25" s="120"/>
+      <c r="AB25" s="121"/>
+      <c r="AC25" s="122"/>
+      <c r="AD25" s="120"/>
+      <c r="AE25" s="121"/>
+      <c r="AF25" s="122"/>
+      <c r="AG25" s="120"/>
+      <c r="AH25" s="121"/>
+      <c r="AI25" s="122"/>
+      <c r="AJ25" s="120"/>
+      <c r="AK25" s="121"/>
+      <c r="AL25" s="122"/>
+      <c r="AM25" s="62"/>
+      <c r="AN25" s="124"/>
+      <c r="AO25" s="125"/>
+      <c r="AP25" s="76"/>
+      <c r="AQ25" s="126"/>
+      <c r="AR25" s="78"/>
       <c r="AS25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT25" s="63"/>
-      <c r="AU25" s="64"/>
-      <c r="AV25" s="59"/>
-      <c r="AW25" s="60"/>
-      <c r="AX25" s="111"/>
-      <c r="AY25" s="112"/>
-      <c r="AZ25" s="59"/>
-      <c r="BA25" s="60"/>
-      <c r="BB25" s="61"/>
-      <c r="BC25" s="62"/>
+      <c r="AT25" s="79"/>
+      <c r="AU25" s="80"/>
+      <c r="AV25" s="75"/>
+      <c r="AW25" s="76"/>
+      <c r="AX25" s="123"/>
+      <c r="AY25" s="124"/>
+      <c r="AZ25" s="75"/>
+      <c r="BA25" s="76"/>
+      <c r="BB25" s="77"/>
+      <c r="BC25" s="78"/>
       <c r="BD25" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE25" s="63"/>
-      <c r="BF25" s="64"/>
-      <c r="BG25" s="59"/>
-      <c r="BH25" s="60"/>
+      <c r="BE25" s="79"/>
+      <c r="BF25" s="80"/>
+      <c r="BG25" s="75"/>
+      <c r="BH25" s="76"/>
     </row>
     <row r="26" spans="2:60">
-      <c r="B26" s="55"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="106"/>
-      <c r="S26" s="107"/>
-      <c r="T26" s="106"/>
-      <c r="U26" s="107"/>
-      <c r="V26" s="108"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="108"/>
-      <c r="Y26" s="109"/>
-      <c r="Z26" s="110"/>
-      <c r="AA26" s="108"/>
-      <c r="AB26" s="109"/>
-      <c r="AC26" s="110"/>
-      <c r="AD26" s="108"/>
-      <c r="AE26" s="109"/>
-      <c r="AF26" s="110"/>
-      <c r="AG26" s="108"/>
-      <c r="AH26" s="109"/>
-      <c r="AI26" s="110"/>
-      <c r="AJ26" s="108"/>
-      <c r="AK26" s="109"/>
-      <c r="AL26" s="110"/>
-      <c r="AM26" s="55"/>
-      <c r="AN26" s="112"/>
-      <c r="AO26" s="113"/>
-      <c r="AP26" s="60"/>
-      <c r="AQ26" s="114"/>
-      <c r="AR26" s="62"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="119"/>
+      <c r="T26" s="118"/>
+      <c r="U26" s="119"/>
+      <c r="V26" s="120"/>
+      <c r="W26" s="122"/>
+      <c r="X26" s="120"/>
+      <c r="Y26" s="121"/>
+      <c r="Z26" s="122"/>
+      <c r="AA26" s="120"/>
+      <c r="AB26" s="121"/>
+      <c r="AC26" s="122"/>
+      <c r="AD26" s="120"/>
+      <c r="AE26" s="121"/>
+      <c r="AF26" s="122"/>
+      <c r="AG26" s="120"/>
+      <c r="AH26" s="121"/>
+      <c r="AI26" s="122"/>
+      <c r="AJ26" s="120"/>
+      <c r="AK26" s="121"/>
+      <c r="AL26" s="122"/>
+      <c r="AM26" s="62"/>
+      <c r="AN26" s="124"/>
+      <c r="AO26" s="125"/>
+      <c r="AP26" s="76"/>
+      <c r="AQ26" s="126"/>
+      <c r="AR26" s="78"/>
       <c r="AS26" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT26" s="63"/>
-      <c r="AU26" s="64"/>
-      <c r="AV26" s="59"/>
-      <c r="AW26" s="60"/>
-      <c r="AX26" s="111"/>
-      <c r="AY26" s="112"/>
-      <c r="AZ26" s="59"/>
-      <c r="BA26" s="60"/>
-      <c r="BB26" s="61"/>
-      <c r="BC26" s="62"/>
+      <c r="AT26" s="79"/>
+      <c r="AU26" s="80"/>
+      <c r="AV26" s="75"/>
+      <c r="AW26" s="76"/>
+      <c r="AX26" s="123"/>
+      <c r="AY26" s="124"/>
+      <c r="AZ26" s="75"/>
+      <c r="BA26" s="76"/>
+      <c r="BB26" s="77"/>
+      <c r="BC26" s="78"/>
       <c r="BD26" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE26" s="63"/>
-      <c r="BF26" s="64"/>
-      <c r="BG26" s="59"/>
-      <c r="BH26" s="60"/>
+      <c r="BE26" s="79"/>
+      <c r="BF26" s="80"/>
+      <c r="BG26" s="75"/>
+      <c r="BH26" s="76"/>
     </row>
     <row r="27" spans="2:60">
-      <c r="B27" s="55"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="106"/>
-      <c r="S27" s="107"/>
-      <c r="T27" s="106"/>
-      <c r="U27" s="107"/>
-      <c r="V27" s="108"/>
-      <c r="W27" s="110"/>
-      <c r="X27" s="108"/>
-      <c r="Y27" s="109"/>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="108"/>
-      <c r="AB27" s="109"/>
-      <c r="AC27" s="110"/>
-      <c r="AD27" s="108"/>
-      <c r="AE27" s="109"/>
-      <c r="AF27" s="110"/>
-      <c r="AG27" s="108"/>
-      <c r="AH27" s="109"/>
-      <c r="AI27" s="110"/>
-      <c r="AJ27" s="108"/>
-      <c r="AK27" s="109"/>
-      <c r="AL27" s="110"/>
-      <c r="AM27" s="55"/>
-      <c r="AN27" s="112"/>
-      <c r="AO27" s="113"/>
-      <c r="AP27" s="60"/>
-      <c r="AQ27" s="114"/>
-      <c r="AR27" s="62"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="118"/>
+      <c r="S27" s="119"/>
+      <c r="T27" s="118"/>
+      <c r="U27" s="119"/>
+      <c r="V27" s="120"/>
+      <c r="W27" s="122"/>
+      <c r="X27" s="120"/>
+      <c r="Y27" s="121"/>
+      <c r="Z27" s="122"/>
+      <c r="AA27" s="120"/>
+      <c r="AB27" s="121"/>
+      <c r="AC27" s="122"/>
+      <c r="AD27" s="120"/>
+      <c r="AE27" s="121"/>
+      <c r="AF27" s="122"/>
+      <c r="AG27" s="120"/>
+      <c r="AH27" s="121"/>
+      <c r="AI27" s="122"/>
+      <c r="AJ27" s="120"/>
+      <c r="AK27" s="121"/>
+      <c r="AL27" s="122"/>
+      <c r="AM27" s="62"/>
+      <c r="AN27" s="124"/>
+      <c r="AO27" s="125"/>
+      <c r="AP27" s="76"/>
+      <c r="AQ27" s="126"/>
+      <c r="AR27" s="78"/>
       <c r="AS27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT27" s="63"/>
-      <c r="AU27" s="64"/>
-      <c r="AV27" s="59"/>
-      <c r="AW27" s="60"/>
-      <c r="AX27" s="111"/>
-      <c r="AY27" s="112"/>
-      <c r="AZ27" s="59"/>
-      <c r="BA27" s="60"/>
-      <c r="BB27" s="61"/>
-      <c r="BC27" s="62"/>
+      <c r="AT27" s="79"/>
+      <c r="AU27" s="80"/>
+      <c r="AV27" s="75"/>
+      <c r="AW27" s="76"/>
+      <c r="AX27" s="123"/>
+      <c r="AY27" s="124"/>
+      <c r="AZ27" s="75"/>
+      <c r="BA27" s="76"/>
+      <c r="BB27" s="77"/>
+      <c r="BC27" s="78"/>
       <c r="BD27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE27" s="63"/>
-      <c r="BF27" s="64"/>
-      <c r="BG27" s="59"/>
-      <c r="BH27" s="60"/>
+      <c r="BE27" s="79"/>
+      <c r="BF27" s="80"/>
+      <c r="BG27" s="75"/>
+      <c r="BH27" s="76"/>
     </row>
     <row r="28" spans="2:60">
-      <c r="B28" s="55"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="106"/>
-      <c r="S28" s="107"/>
-      <c r="T28" s="106"/>
-      <c r="U28" s="107"/>
-      <c r="V28" s="108"/>
-      <c r="W28" s="110"/>
-      <c r="X28" s="108"/>
-      <c r="Y28" s="109"/>
-      <c r="Z28" s="110"/>
-      <c r="AA28" s="108"/>
-      <c r="AB28" s="109"/>
-      <c r="AC28" s="110"/>
-      <c r="AD28" s="108"/>
-      <c r="AE28" s="109"/>
-      <c r="AF28" s="110"/>
-      <c r="AG28" s="108"/>
-      <c r="AH28" s="109"/>
-      <c r="AI28" s="110"/>
-      <c r="AJ28" s="108"/>
-      <c r="AK28" s="109"/>
-      <c r="AL28" s="110"/>
-      <c r="AM28" s="55"/>
-      <c r="AN28" s="112"/>
-      <c r="AO28" s="113"/>
-      <c r="AP28" s="60"/>
-      <c r="AQ28" s="114"/>
-      <c r="AR28" s="62"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="119"/>
+      <c r="T28" s="118"/>
+      <c r="U28" s="119"/>
+      <c r="V28" s="120"/>
+      <c r="W28" s="122"/>
+      <c r="X28" s="120"/>
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="122"/>
+      <c r="AA28" s="120"/>
+      <c r="AB28" s="121"/>
+      <c r="AC28" s="122"/>
+      <c r="AD28" s="120"/>
+      <c r="AE28" s="121"/>
+      <c r="AF28" s="122"/>
+      <c r="AG28" s="120"/>
+      <c r="AH28" s="121"/>
+      <c r="AI28" s="122"/>
+      <c r="AJ28" s="120"/>
+      <c r="AK28" s="121"/>
+      <c r="AL28" s="122"/>
+      <c r="AM28" s="62"/>
+      <c r="AN28" s="124"/>
+      <c r="AO28" s="125"/>
+      <c r="AP28" s="76"/>
+      <c r="AQ28" s="126"/>
+      <c r="AR28" s="78"/>
       <c r="AS28" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT28" s="63"/>
-      <c r="AU28" s="64"/>
-      <c r="AV28" s="59"/>
-      <c r="AW28" s="60"/>
-      <c r="AX28" s="111"/>
-      <c r="AY28" s="112"/>
-      <c r="AZ28" s="59"/>
-      <c r="BA28" s="60"/>
-      <c r="BB28" s="61"/>
-      <c r="BC28" s="62"/>
+      <c r="AT28" s="79"/>
+      <c r="AU28" s="80"/>
+      <c r="AV28" s="75"/>
+      <c r="AW28" s="76"/>
+      <c r="AX28" s="123"/>
+      <c r="AY28" s="124"/>
+      <c r="AZ28" s="75"/>
+      <c r="BA28" s="76"/>
+      <c r="BB28" s="77"/>
+      <c r="BC28" s="78"/>
       <c r="BD28" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE28" s="63"/>
-      <c r="BF28" s="64"/>
-      <c r="BG28" s="59"/>
-      <c r="BH28" s="60"/>
+      <c r="BE28" s="79"/>
+      <c r="BF28" s="80"/>
+      <c r="BG28" s="75"/>
+      <c r="BH28" s="76"/>
     </row>
     <row r="29" spans="2:60" ht="13.2" customHeight="1">
       <c r="B29" s="4" t="s">
@@ -3742,65 +3733,65 @@
       <c r="K29" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="119"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="120"/>
+      <c r="L29" s="129"/>
+      <c r="M29" s="129"/>
+      <c r="N29" s="129"/>
+      <c r="O29" s="129"/>
+      <c r="P29" s="129"/>
+      <c r="Q29" s="130"/>
       <c r="R29" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S29" s="97"/>
-      <c r="T29" s="97"/>
-      <c r="U29" s="97"/>
-      <c r="V29" s="97"/>
-      <c r="W29" s="97"/>
-      <c r="X29" s="98"/>
+      <c r="S29" s="110"/>
+      <c r="T29" s="110"/>
+      <c r="U29" s="110"/>
+      <c r="V29" s="110"/>
+      <c r="W29" s="110"/>
+      <c r="X29" s="111"/>
       <c r="Y29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Z29" s="97"/>
-      <c r="AA29" s="97"/>
-      <c r="AB29" s="97"/>
-      <c r="AC29" s="97"/>
-      <c r="AD29" s="97"/>
-      <c r="AE29" s="98"/>
+      <c r="Z29" s="110"/>
+      <c r="AA29" s="110"/>
+      <c r="AB29" s="110"/>
+      <c r="AC29" s="110"/>
+      <c r="AD29" s="110"/>
+      <c r="AE29" s="111"/>
       <c r="AF29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AG29" s="119"/>
-      <c r="AH29" s="119"/>
-      <c r="AI29" s="119"/>
-      <c r="AJ29" s="119"/>
-      <c r="AK29" s="119"/>
-      <c r="AL29" s="120"/>
-      <c r="AM29" s="55"/>
-      <c r="AN29" s="112"/>
-      <c r="AO29" s="113"/>
-      <c r="AP29" s="60"/>
-      <c r="AQ29" s="114"/>
-      <c r="AR29" s="62"/>
+      <c r="AG29" s="129"/>
+      <c r="AH29" s="129"/>
+      <c r="AI29" s="129"/>
+      <c r="AJ29" s="129"/>
+      <c r="AK29" s="129"/>
+      <c r="AL29" s="130"/>
+      <c r="AM29" s="62"/>
+      <c r="AN29" s="124"/>
+      <c r="AO29" s="125"/>
+      <c r="AP29" s="76"/>
+      <c r="AQ29" s="126"/>
+      <c r="AR29" s="78"/>
       <c r="AS29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT29" s="63"/>
-      <c r="AU29" s="64"/>
-      <c r="AV29" s="59"/>
-      <c r="AW29" s="60"/>
-      <c r="AX29" s="111"/>
-      <c r="AY29" s="112"/>
-      <c r="AZ29" s="59"/>
-      <c r="BA29" s="60"/>
-      <c r="BB29" s="61"/>
-      <c r="BC29" s="62"/>
+      <c r="AT29" s="79"/>
+      <c r="AU29" s="80"/>
+      <c r="AV29" s="75"/>
+      <c r="AW29" s="76"/>
+      <c r="AX29" s="123"/>
+      <c r="AY29" s="124"/>
+      <c r="AZ29" s="75"/>
+      <c r="BA29" s="76"/>
+      <c r="BB29" s="77"/>
+      <c r="BC29" s="78"/>
       <c r="BD29" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE29" s="63"/>
-      <c r="BF29" s="64"/>
-      <c r="BG29" s="59"/>
-      <c r="BH29" s="60"/>
+      <c r="BE29" s="79"/>
+      <c r="BF29" s="80"/>
+      <c r="BG29" s="75"/>
+      <c r="BH29" s="76"/>
     </row>
     <row r="30" spans="2:60" ht="6.6" customHeight="1">
       <c r="B30" s="178"/>
@@ -3812,60 +3803,60 @@
       <c r="H30" s="176"/>
       <c r="I30" s="176"/>
       <c r="J30" s="177"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="103"/>
-      <c r="M30" s="103"/>
-      <c r="N30" s="103"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="104"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="103"/>
-      <c r="T30" s="103"/>
-      <c r="U30" s="103"/>
-      <c r="V30" s="103"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="102"/>
-      <c r="Z30" s="103"/>
-      <c r="AA30" s="103"/>
-      <c r="AB30" s="103"/>
-      <c r="AC30" s="103"/>
-      <c r="AD30" s="103"/>
-      <c r="AE30" s="104"/>
-      <c r="AF30" s="102"/>
-      <c r="AG30" s="103"/>
-      <c r="AH30" s="103"/>
-      <c r="AI30" s="103"/>
-      <c r="AJ30" s="103"/>
-      <c r="AK30" s="103"/>
-      <c r="AL30" s="104"/>
+      <c r="K30" s="115"/>
+      <c r="L30" s="116"/>
+      <c r="M30" s="116"/>
+      <c r="N30" s="116"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="116"/>
+      <c r="Q30" s="117"/>
+      <c r="R30" s="115"/>
+      <c r="S30" s="116"/>
+      <c r="T30" s="116"/>
+      <c r="U30" s="116"/>
+      <c r="V30" s="116"/>
+      <c r="W30" s="116"/>
+      <c r="X30" s="117"/>
+      <c r="Y30" s="115"/>
+      <c r="Z30" s="116"/>
+      <c r="AA30" s="116"/>
+      <c r="AB30" s="116"/>
+      <c r="AC30" s="116"/>
+      <c r="AD30" s="116"/>
+      <c r="AE30" s="117"/>
+      <c r="AF30" s="115"/>
+      <c r="AG30" s="116"/>
+      <c r="AH30" s="116"/>
+      <c r="AI30" s="116"/>
+      <c r="AJ30" s="116"/>
+      <c r="AK30" s="116"/>
+      <c r="AL30" s="117"/>
       <c r="AM30" s="44"/>
-      <c r="AN30" s="48"/>
-      <c r="AO30" s="144"/>
-      <c r="AP30" s="145"/>
-      <c r="AQ30" s="144"/>
-      <c r="AR30" s="148"/>
-      <c r="AS30" s="142" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT30" s="132"/>
-      <c r="AU30" s="133"/>
-      <c r="AV30" s="136"/>
-      <c r="AW30" s="133"/>
-      <c r="AX30" s="138"/>
-      <c r="AY30" s="139"/>
-      <c r="AZ30" s="136"/>
-      <c r="BA30" s="133"/>
-      <c r="BB30" s="136"/>
-      <c r="BC30" s="132"/>
-      <c r="BD30" s="142" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE30" s="132"/>
-      <c r="BF30" s="133"/>
-      <c r="BG30" s="136"/>
-      <c r="BH30" s="133"/>
+      <c r="AN30" s="69"/>
+      <c r="AO30" s="154"/>
+      <c r="AP30" s="155"/>
+      <c r="AQ30" s="154"/>
+      <c r="AR30" s="158"/>
+      <c r="AS30" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="142"/>
+      <c r="AU30" s="143"/>
+      <c r="AV30" s="146"/>
+      <c r="AW30" s="143"/>
+      <c r="AX30" s="148"/>
+      <c r="AY30" s="149"/>
+      <c r="AZ30" s="146"/>
+      <c r="BA30" s="143"/>
+      <c r="BB30" s="146"/>
+      <c r="BC30" s="142"/>
+      <c r="BD30" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE30" s="142"/>
+      <c r="BF30" s="143"/>
+      <c r="BG30" s="146"/>
+      <c r="BH30" s="143"/>
     </row>
     <row r="31" spans="2:60" ht="6.6" customHeight="1">
       <c r="B31" s="180"/>
@@ -3877,1588 +3868,1588 @@
       <c r="H31" s="176"/>
       <c r="I31" s="176"/>
       <c r="J31" s="177"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="100"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="100"/>
-      <c r="Q31" s="101"/>
-      <c r="R31" s="99"/>
-      <c r="S31" s="100"/>
-      <c r="T31" s="100"/>
-      <c r="U31" s="100"/>
-      <c r="V31" s="100"/>
-      <c r="W31" s="100"/>
-      <c r="X31" s="101"/>
-      <c r="Y31" s="99"/>
-      <c r="Z31" s="100"/>
-      <c r="AA31" s="100"/>
-      <c r="AB31" s="100"/>
-      <c r="AC31" s="100"/>
-      <c r="AD31" s="100"/>
-      <c r="AE31" s="101"/>
-      <c r="AF31" s="99"/>
-      <c r="AG31" s="100"/>
-      <c r="AH31" s="100"/>
-      <c r="AI31" s="100"/>
-      <c r="AJ31" s="100"/>
-      <c r="AK31" s="100"/>
-      <c r="AL31" s="101"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="113"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="114"/>
+      <c r="Y31" s="112"/>
+      <c r="Z31" s="113"/>
+      <c r="AA31" s="113"/>
+      <c r="AB31" s="113"/>
+      <c r="AC31" s="113"/>
+      <c r="AD31" s="113"/>
+      <c r="AE31" s="114"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="113"/>
+      <c r="AH31" s="113"/>
+      <c r="AI31" s="113"/>
+      <c r="AJ31" s="113"/>
+      <c r="AK31" s="113"/>
+      <c r="AL31" s="114"/>
       <c r="AM31" s="46"/>
-      <c r="AN31" s="49"/>
-      <c r="AO31" s="146"/>
-      <c r="AP31" s="147"/>
-      <c r="AQ31" s="146"/>
-      <c r="AR31" s="149"/>
-      <c r="AS31" s="143"/>
-      <c r="AT31" s="134"/>
-      <c r="AU31" s="135"/>
-      <c r="AV31" s="137"/>
-      <c r="AW31" s="135"/>
-      <c r="AX31" s="140"/>
-      <c r="AY31" s="141"/>
-      <c r="AZ31" s="137"/>
-      <c r="BA31" s="135"/>
-      <c r="BB31" s="137"/>
-      <c r="BC31" s="134"/>
-      <c r="BD31" s="143"/>
-      <c r="BE31" s="134"/>
-      <c r="BF31" s="135"/>
-      <c r="BG31" s="137"/>
-      <c r="BH31" s="135"/>
+      <c r="AN31" s="70"/>
+      <c r="AO31" s="156"/>
+      <c r="AP31" s="157"/>
+      <c r="AQ31" s="156"/>
+      <c r="AR31" s="159"/>
+      <c r="AS31" s="153"/>
+      <c r="AT31" s="144"/>
+      <c r="AU31" s="145"/>
+      <c r="AV31" s="147"/>
+      <c r="AW31" s="145"/>
+      <c r="AX31" s="150"/>
+      <c r="AY31" s="151"/>
+      <c r="AZ31" s="147"/>
+      <c r="BA31" s="145"/>
+      <c r="BB31" s="147"/>
+      <c r="BC31" s="144"/>
+      <c r="BD31" s="153"/>
+      <c r="BE31" s="144"/>
+      <c r="BF31" s="145"/>
+      <c r="BG31" s="147"/>
+      <c r="BH31" s="145"/>
     </row>
     <row r="32" spans="2:60">
-      <c r="B32" s="65"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="105"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="72"/>
-      <c r="T32" s="72"/>
-      <c r="U32" s="72"/>
-      <c r="V32" s="72"/>
-      <c r="W32" s="72"/>
-      <c r="X32" s="105"/>
-      <c r="Y32" s="71"/>
-      <c r="Z32" s="72"/>
-      <c r="AA32" s="72"/>
-      <c r="AB32" s="72"/>
-      <c r="AC32" s="72"/>
-      <c r="AD32" s="72"/>
-      <c r="AE32" s="105"/>
-      <c r="AF32" s="71"/>
-      <c r="AG32" s="72"/>
-      <c r="AH32" s="72"/>
-      <c r="AI32" s="72"/>
-      <c r="AJ32" s="72"/>
-      <c r="AK32" s="72"/>
-      <c r="AL32" s="105"/>
-      <c r="AM32" s="111"/>
-      <c r="AN32" s="112"/>
-      <c r="AO32" s="59"/>
-      <c r="AP32" s="60"/>
-      <c r="AQ32" s="61"/>
-      <c r="AR32" s="62"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="83"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="59"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="59"/>
+      <c r="Z32" s="60"/>
+      <c r="AA32" s="60"/>
+      <c r="AB32" s="60"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+      <c r="AE32" s="61"/>
+      <c r="AF32" s="59"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="60"/>
+      <c r="AI32" s="60"/>
+      <c r="AJ32" s="60"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="61"/>
+      <c r="AM32" s="123"/>
+      <c r="AN32" s="124"/>
+      <c r="AO32" s="75"/>
+      <c r="AP32" s="76"/>
+      <c r="AQ32" s="77"/>
+      <c r="AR32" s="78"/>
       <c r="AS32" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT32" s="63"/>
-      <c r="AU32" s="64"/>
-      <c r="AV32" s="59"/>
-      <c r="AW32" s="60"/>
-      <c r="AX32" s="111"/>
-      <c r="AY32" s="112"/>
-      <c r="AZ32" s="59"/>
-      <c r="BA32" s="60"/>
-      <c r="BB32" s="61"/>
-      <c r="BC32" s="62"/>
+      <c r="AT32" s="79"/>
+      <c r="AU32" s="80"/>
+      <c r="AV32" s="75"/>
+      <c r="AW32" s="76"/>
+      <c r="AX32" s="123"/>
+      <c r="AY32" s="124"/>
+      <c r="AZ32" s="75"/>
+      <c r="BA32" s="76"/>
+      <c r="BB32" s="77"/>
+      <c r="BC32" s="78"/>
       <c r="BD32" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE32" s="63"/>
-      <c r="BF32" s="64"/>
-      <c r="BG32" s="59"/>
-      <c r="BH32" s="60"/>
+      <c r="BE32" s="79"/>
+      <c r="BF32" s="80"/>
+      <c r="BG32" s="75"/>
+      <c r="BH32" s="76"/>
     </row>
     <row r="33" spans="2:60">
-      <c r="B33" s="167" t="s">
+      <c r="B33" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="168"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="168"/>
-      <c r="H33" s="168"/>
-      <c r="I33" s="168"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="167" t="s">
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="L33" s="168"/>
-      <c r="M33" s="168"/>
-      <c r="N33" s="168"/>
-      <c r="O33" s="168"/>
-      <c r="P33" s="168"/>
-      <c r="Q33" s="169"/>
-      <c r="R33" s="167" t="s">
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="52"/>
+      <c r="P33" s="52"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S33" s="168"/>
-      <c r="T33" s="168"/>
-      <c r="U33" s="168"/>
-      <c r="V33" s="168"/>
-      <c r="W33" s="168"/>
-      <c r="X33" s="169"/>
-      <c r="Y33" s="167" t="s">
+      <c r="S33" s="52"/>
+      <c r="T33" s="52"/>
+      <c r="U33" s="52"/>
+      <c r="V33" s="52"/>
+      <c r="W33" s="52"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Z33" s="168"/>
-      <c r="AA33" s="168"/>
-      <c r="AB33" s="168"/>
-      <c r="AC33" s="168"/>
-      <c r="AD33" s="168"/>
-      <c r="AE33" s="169"/>
-      <c r="AF33" s="167" t="s">
+      <c r="Z33" s="52"/>
+      <c r="AA33" s="52"/>
+      <c r="AB33" s="52"/>
+      <c r="AC33" s="52"/>
+      <c r="AD33" s="52"/>
+      <c r="AE33" s="53"/>
+      <c r="AF33" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AG33" s="168"/>
-      <c r="AH33" s="168"/>
-      <c r="AI33" s="168"/>
-      <c r="AJ33" s="168"/>
-      <c r="AK33" s="168"/>
-      <c r="AL33" s="169"/>
-      <c r="AM33" s="111"/>
-      <c r="AN33" s="112"/>
-      <c r="AO33" s="59"/>
-      <c r="AP33" s="60"/>
-      <c r="AQ33" s="61"/>
-      <c r="AR33" s="62"/>
+      <c r="AG33" s="52"/>
+      <c r="AH33" s="52"/>
+      <c r="AI33" s="52"/>
+      <c r="AJ33" s="52"/>
+      <c r="AK33" s="52"/>
+      <c r="AL33" s="53"/>
+      <c r="AM33" s="123"/>
+      <c r="AN33" s="124"/>
+      <c r="AO33" s="75"/>
+      <c r="AP33" s="76"/>
+      <c r="AQ33" s="77"/>
+      <c r="AR33" s="78"/>
       <c r="AS33" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT33" s="63"/>
-      <c r="AU33" s="64"/>
-      <c r="AV33" s="59"/>
-      <c r="AW33" s="60"/>
-      <c r="AX33" s="111"/>
-      <c r="AY33" s="112"/>
-      <c r="AZ33" s="59"/>
-      <c r="BA33" s="60"/>
-      <c r="BB33" s="61"/>
-      <c r="BC33" s="62"/>
+      <c r="AT33" s="79"/>
+      <c r="AU33" s="80"/>
+      <c r="AV33" s="75"/>
+      <c r="AW33" s="76"/>
+      <c r="AX33" s="123"/>
+      <c r="AY33" s="124"/>
+      <c r="AZ33" s="75"/>
+      <c r="BA33" s="76"/>
+      <c r="BB33" s="77"/>
+      <c r="BC33" s="78"/>
       <c r="BD33" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE33" s="63"/>
-      <c r="BF33" s="64"/>
-      <c r="BG33" s="59"/>
-      <c r="BH33" s="60"/>
+      <c r="BE33" s="79"/>
+      <c r="BF33" s="80"/>
+      <c r="BG33" s="75"/>
+      <c r="BH33" s="76"/>
     </row>
     <row r="34" spans="2:60">
-      <c r="B34" s="170"/>
-      <c r="C34" s="171"/>
-      <c r="D34" s="171"/>
-      <c r="E34" s="171"/>
-      <c r="F34" s="171"/>
-      <c r="G34" s="171"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="171"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="170"/>
-      <c r="L34" s="171"/>
-      <c r="M34" s="171"/>
-      <c r="N34" s="171"/>
-      <c r="O34" s="171"/>
-      <c r="P34" s="171"/>
-      <c r="Q34" s="172"/>
-      <c r="R34" s="170"/>
-      <c r="S34" s="171"/>
-      <c r="T34" s="171"/>
-      <c r="U34" s="171"/>
-      <c r="V34" s="171"/>
-      <c r="W34" s="171"/>
-      <c r="X34" s="172"/>
-      <c r="Y34" s="170"/>
-      <c r="Z34" s="171"/>
-      <c r="AA34" s="171"/>
-      <c r="AB34" s="171"/>
-      <c r="AC34" s="171"/>
-      <c r="AD34" s="171"/>
-      <c r="AE34" s="172"/>
-      <c r="AF34" s="170"/>
-      <c r="AG34" s="171"/>
-      <c r="AH34" s="171"/>
-      <c r="AI34" s="171"/>
-      <c r="AJ34" s="171"/>
-      <c r="AK34" s="171"/>
-      <c r="AL34" s="172"/>
-      <c r="AM34" s="111"/>
-      <c r="AN34" s="112"/>
-      <c r="AO34" s="59"/>
-      <c r="AP34" s="60"/>
-      <c r="AQ34" s="61"/>
-      <c r="AR34" s="62"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="56"/>
+      <c r="R34" s="54"/>
+      <c r="S34" s="55"/>
+      <c r="T34" s="55"/>
+      <c r="U34" s="55"/>
+      <c r="V34" s="55"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="56"/>
+      <c r="Y34" s="54"/>
+      <c r="Z34" s="55"/>
+      <c r="AA34" s="55"/>
+      <c r="AB34" s="55"/>
+      <c r="AC34" s="55"/>
+      <c r="AD34" s="55"/>
+      <c r="AE34" s="56"/>
+      <c r="AF34" s="54"/>
+      <c r="AG34" s="55"/>
+      <c r="AH34" s="55"/>
+      <c r="AI34" s="55"/>
+      <c r="AJ34" s="55"/>
+      <c r="AK34" s="55"/>
+      <c r="AL34" s="56"/>
+      <c r="AM34" s="123"/>
+      <c r="AN34" s="124"/>
+      <c r="AO34" s="75"/>
+      <c r="AP34" s="76"/>
+      <c r="AQ34" s="77"/>
+      <c r="AR34" s="78"/>
       <c r="AS34" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT34" s="63"/>
-      <c r="AU34" s="64"/>
-      <c r="AV34" s="59"/>
-      <c r="AW34" s="60"/>
-      <c r="AX34" s="111"/>
-      <c r="AY34" s="112"/>
-      <c r="AZ34" s="59"/>
-      <c r="BA34" s="60"/>
-      <c r="BB34" s="61"/>
-      <c r="BC34" s="62"/>
+      <c r="AT34" s="79"/>
+      <c r="AU34" s="80"/>
+      <c r="AV34" s="75"/>
+      <c r="AW34" s="76"/>
+      <c r="AX34" s="123"/>
+      <c r="AY34" s="124"/>
+      <c r="AZ34" s="75"/>
+      <c r="BA34" s="76"/>
+      <c r="BB34" s="77"/>
+      <c r="BC34" s="78"/>
       <c r="BD34" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE34" s="63"/>
-      <c r="BF34" s="64"/>
-      <c r="BG34" s="59"/>
-      <c r="BH34" s="60"/>
+      <c r="BE34" s="79"/>
+      <c r="BF34" s="80"/>
+      <c r="BG34" s="75"/>
+      <c r="BH34" s="76"/>
     </row>
     <row r="35" spans="2:60">
-      <c r="B35" s="163" t="s">
+      <c r="B35" s="87" t="s">
         <v>27</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="161">
+      <c r="E35" s="171">
         <f>D7</f>
         <v>0</v>
       </c>
-      <c r="F35" s="161"/>
-      <c r="G35" s="161"/>
-      <c r="H35" s="161"/>
-      <c r="I35" s="161"/>
-      <c r="J35" s="161"/>
-      <c r="K35" s="161"/>
-      <c r="L35" s="161"/>
-      <c r="M35" s="161"/>
-      <c r="N35" s="161"/>
-      <c r="O35" s="161"/>
-      <c r="P35" s="161"/>
-      <c r="Q35" s="161"/>
-      <c r="R35" s="161"/>
-      <c r="S35" s="161"/>
-      <c r="T35" s="161"/>
-      <c r="U35" s="162"/>
-      <c r="V35" s="116" t="s">
+      <c r="F35" s="171"/>
+      <c r="G35" s="171"/>
+      <c r="H35" s="171"/>
+      <c r="I35" s="171"/>
+      <c r="J35" s="171"/>
+      <c r="K35" s="171"/>
+      <c r="L35" s="171"/>
+      <c r="M35" s="171"/>
+      <c r="N35" s="171"/>
+      <c r="O35" s="171"/>
+      <c r="P35" s="171"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="171"/>
+      <c r="S35" s="171"/>
+      <c r="T35" s="171"/>
+      <c r="U35" s="172"/>
+      <c r="V35" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="W35" s="117"/>
-      <c r="X35" s="117"/>
-      <c r="Y35" s="117"/>
-      <c r="Z35" s="117"/>
-      <c r="AA35" s="117"/>
-      <c r="AB35" s="117"/>
-      <c r="AC35" s="117"/>
-      <c r="AD35" s="117"/>
-      <c r="AE35" s="117"/>
-      <c r="AF35" s="117"/>
-      <c r="AG35" s="117"/>
-      <c r="AH35" s="117"/>
-      <c r="AI35" s="117"/>
-      <c r="AJ35" s="117"/>
-      <c r="AK35" s="117"/>
-      <c r="AL35" s="118"/>
-      <c r="AM35" s="111"/>
-      <c r="AN35" s="112"/>
-      <c r="AO35" s="59"/>
-      <c r="AP35" s="60"/>
-      <c r="AQ35" s="61"/>
-      <c r="AR35" s="62"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="57"/>
+      <c r="AJ35" s="57"/>
+      <c r="AK35" s="57"/>
+      <c r="AL35" s="58"/>
+      <c r="AM35" s="123"/>
+      <c r="AN35" s="124"/>
+      <c r="AO35" s="75"/>
+      <c r="AP35" s="76"/>
+      <c r="AQ35" s="77"/>
+      <c r="AR35" s="78"/>
       <c r="AS35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT35" s="63"/>
-      <c r="AU35" s="64"/>
-      <c r="AV35" s="59"/>
-      <c r="AW35" s="60"/>
-      <c r="AX35" s="111"/>
-      <c r="AY35" s="112"/>
-      <c r="AZ35" s="59"/>
-      <c r="BA35" s="60"/>
-      <c r="BB35" s="61"/>
-      <c r="BC35" s="62"/>
+      <c r="AT35" s="79"/>
+      <c r="AU35" s="80"/>
+      <c r="AV35" s="75"/>
+      <c r="AW35" s="76"/>
+      <c r="AX35" s="123"/>
+      <c r="AY35" s="124"/>
+      <c r="AZ35" s="75"/>
+      <c r="BA35" s="76"/>
+      <c r="BB35" s="77"/>
+      <c r="BC35" s="78"/>
       <c r="BD35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE35" s="63"/>
-      <c r="BF35" s="64"/>
-      <c r="BG35" s="59"/>
-      <c r="BH35" s="60"/>
+      <c r="BE35" s="79"/>
+      <c r="BF35" s="80"/>
+      <c r="BG35" s="75"/>
+      <c r="BH35" s="76"/>
     </row>
     <row r="36" spans="2:60">
-      <c r="B36" s="116" t="s">
+      <c r="B36" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="118"/>
-      <c r="D36" s="116" t="s">
+      <c r="C36" s="58"/>
+      <c r="D36" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117"/>
-      <c r="H36" s="117"/>
-      <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="117"/>
-      <c r="N36" s="117"/>
-      <c r="O36" s="117"/>
-      <c r="P36" s="117"/>
-      <c r="Q36" s="118"/>
-      <c r="R36" s="116" t="s">
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="S36" s="118"/>
-      <c r="T36" s="116" t="s">
+      <c r="S36" s="58"/>
+      <c r="T36" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="U36" s="118"/>
-      <c r="V36" s="116" t="s">
+      <c r="U36" s="58"/>
+      <c r="V36" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="W36" s="118"/>
-      <c r="X36" s="116" t="s">
+      <c r="W36" s="58"/>
+      <c r="X36" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="Y36" s="117"/>
-      <c r="Z36" s="118"/>
-      <c r="AA36" s="116" t="s">
+      <c r="Y36" s="57"/>
+      <c r="Z36" s="58"/>
+      <c r="AA36" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AB36" s="117"/>
-      <c r="AC36" s="118"/>
-      <c r="AD36" s="116" t="s">
+      <c r="AB36" s="57"/>
+      <c r="AC36" s="58"/>
+      <c r="AD36" s="128" t="s">
         <v>52</v>
       </c>
-      <c r="AE36" s="117"/>
-      <c r="AF36" s="118"/>
-      <c r="AG36" s="116" t="s">
+      <c r="AE36" s="57"/>
+      <c r="AF36" s="58"/>
+      <c r="AG36" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="AH36" s="117"/>
-      <c r="AI36" s="118"/>
-      <c r="AJ36" s="116" t="s">
+      <c r="AH36" s="57"/>
+      <c r="AI36" s="58"/>
+      <c r="AJ36" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="AK36" s="117"/>
-      <c r="AL36" s="118"/>
-      <c r="AM36" s="111"/>
-      <c r="AN36" s="112"/>
-      <c r="AO36" s="59"/>
-      <c r="AP36" s="60"/>
-      <c r="AQ36" s="61"/>
-      <c r="AR36" s="62"/>
+      <c r="AK36" s="57"/>
+      <c r="AL36" s="58"/>
+      <c r="AM36" s="123"/>
+      <c r="AN36" s="124"/>
+      <c r="AO36" s="75"/>
+      <c r="AP36" s="76"/>
+      <c r="AQ36" s="77"/>
+      <c r="AR36" s="78"/>
       <c r="AS36" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT36" s="63"/>
-      <c r="AU36" s="64"/>
-      <c r="AV36" s="59"/>
-      <c r="AW36" s="60"/>
-      <c r="AX36" s="111"/>
-      <c r="AY36" s="112"/>
-      <c r="AZ36" s="59"/>
-      <c r="BA36" s="60"/>
-      <c r="BB36" s="61"/>
-      <c r="BC36" s="62"/>
+      <c r="AT36" s="79"/>
+      <c r="AU36" s="80"/>
+      <c r="AV36" s="75"/>
+      <c r="AW36" s="76"/>
+      <c r="AX36" s="123"/>
+      <c r="AY36" s="124"/>
+      <c r="AZ36" s="75"/>
+      <c r="BA36" s="76"/>
+      <c r="BB36" s="77"/>
+      <c r="BC36" s="78"/>
       <c r="BD36" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE36" s="63"/>
-      <c r="BF36" s="64"/>
-      <c r="BG36" s="59"/>
-      <c r="BH36" s="60"/>
+      <c r="BE36" s="79"/>
+      <c r="BF36" s="80"/>
+      <c r="BG36" s="75"/>
+      <c r="BH36" s="76"/>
     </row>
     <row r="37" spans="2:60">
-      <c r="B37" s="55"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="91"/>
-      <c r="S37" s="92"/>
-      <c r="T37" s="91"/>
-      <c r="U37" s="92"/>
-      <c r="V37" s="52"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="52"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="54"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="54"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="54"/>
-      <c r="AG37" s="52"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="54"/>
-      <c r="AJ37" s="52"/>
-      <c r="AK37" s="53"/>
-      <c r="AL37" s="54"/>
-      <c r="AM37" s="111"/>
-      <c r="AN37" s="112"/>
-      <c r="AO37" s="59"/>
-      <c r="AP37" s="60"/>
-      <c r="AQ37" s="61"/>
-      <c r="AR37" s="62"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="68"/>
+      <c r="T37" s="67"/>
+      <c r="U37" s="68"/>
+      <c r="V37" s="72"/>
+      <c r="W37" s="74"/>
+      <c r="X37" s="72"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="74"/>
+      <c r="AA37" s="72"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="74"/>
+      <c r="AD37" s="72"/>
+      <c r="AE37" s="73"/>
+      <c r="AF37" s="74"/>
+      <c r="AG37" s="72"/>
+      <c r="AH37" s="73"/>
+      <c r="AI37" s="74"/>
+      <c r="AJ37" s="72"/>
+      <c r="AK37" s="73"/>
+      <c r="AL37" s="74"/>
+      <c r="AM37" s="123"/>
+      <c r="AN37" s="124"/>
+      <c r="AO37" s="75"/>
+      <c r="AP37" s="76"/>
+      <c r="AQ37" s="77"/>
+      <c r="AR37" s="78"/>
       <c r="AS37" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT37" s="63"/>
-      <c r="AU37" s="64"/>
-      <c r="AV37" s="59"/>
-      <c r="AW37" s="60"/>
-      <c r="AX37" s="111"/>
-      <c r="AY37" s="112"/>
-      <c r="AZ37" s="59"/>
-      <c r="BA37" s="60"/>
-      <c r="BB37" s="61"/>
-      <c r="BC37" s="62"/>
+      <c r="AT37" s="79"/>
+      <c r="AU37" s="80"/>
+      <c r="AV37" s="75"/>
+      <c r="AW37" s="76"/>
+      <c r="AX37" s="123"/>
+      <c r="AY37" s="124"/>
+      <c r="AZ37" s="75"/>
+      <c r="BA37" s="76"/>
+      <c r="BB37" s="77"/>
+      <c r="BC37" s="78"/>
       <c r="BD37" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE37" s="63"/>
-      <c r="BF37" s="64"/>
-      <c r="BG37" s="59"/>
-      <c r="BH37" s="60"/>
+      <c r="BE37" s="79"/>
+      <c r="BF37" s="80"/>
+      <c r="BG37" s="75"/>
+      <c r="BH37" s="76"/>
     </row>
     <row r="38" spans="2:60">
-      <c r="B38" s="55"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
-      <c r="K38" s="57"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="57"/>
-      <c r="N38" s="57"/>
-      <c r="O38" s="57"/>
-      <c r="P38" s="57"/>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="91"/>
-      <c r="S38" s="92"/>
-      <c r="T38" s="91"/>
-      <c r="U38" s="92"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="54"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="53"/>
-      <c r="Z38" s="54"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="53"/>
-      <c r="AC38" s="54"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="53"/>
-      <c r="AF38" s="54"/>
-      <c r="AG38" s="52"/>
-      <c r="AH38" s="53"/>
-      <c r="AI38" s="54"/>
-      <c r="AJ38" s="52"/>
-      <c r="AK38" s="53"/>
-      <c r="AL38" s="54"/>
-      <c r="AM38" s="111"/>
-      <c r="AN38" s="112"/>
-      <c r="AO38" s="59"/>
-      <c r="AP38" s="60"/>
-      <c r="AQ38" s="61"/>
-      <c r="AR38" s="62"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="68"/>
+      <c r="T38" s="67"/>
+      <c r="U38" s="68"/>
+      <c r="V38" s="72"/>
+      <c r="W38" s="74"/>
+      <c r="X38" s="72"/>
+      <c r="Y38" s="73"/>
+      <c r="Z38" s="74"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
+      <c r="AC38" s="74"/>
+      <c r="AD38" s="72"/>
+      <c r="AE38" s="73"/>
+      <c r="AF38" s="74"/>
+      <c r="AG38" s="72"/>
+      <c r="AH38" s="73"/>
+      <c r="AI38" s="74"/>
+      <c r="AJ38" s="72"/>
+      <c r="AK38" s="73"/>
+      <c r="AL38" s="74"/>
+      <c r="AM38" s="123"/>
+      <c r="AN38" s="124"/>
+      <c r="AO38" s="75"/>
+      <c r="AP38" s="76"/>
+      <c r="AQ38" s="77"/>
+      <c r="AR38" s="78"/>
       <c r="AS38" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT38" s="63"/>
-      <c r="AU38" s="64"/>
-      <c r="AV38" s="59"/>
-      <c r="AW38" s="60"/>
-      <c r="AX38" s="111"/>
-      <c r="AY38" s="112"/>
-      <c r="AZ38" s="59"/>
-      <c r="BA38" s="60"/>
-      <c r="BB38" s="61"/>
-      <c r="BC38" s="62"/>
+      <c r="AT38" s="79"/>
+      <c r="AU38" s="80"/>
+      <c r="AV38" s="75"/>
+      <c r="AW38" s="76"/>
+      <c r="AX38" s="123"/>
+      <c r="AY38" s="124"/>
+      <c r="AZ38" s="75"/>
+      <c r="BA38" s="76"/>
+      <c r="BB38" s="77"/>
+      <c r="BC38" s="78"/>
       <c r="BD38" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE38" s="63"/>
-      <c r="BF38" s="64"/>
-      <c r="BG38" s="59"/>
-      <c r="BH38" s="60"/>
+      <c r="BE38" s="79"/>
+      <c r="BF38" s="80"/>
+      <c r="BG38" s="75"/>
+      <c r="BH38" s="76"/>
     </row>
     <row r="39" spans="2:60">
-      <c r="B39" s="55"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
-      <c r="N39" s="57"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="57"/>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="92"/>
-      <c r="T39" s="91"/>
-      <c r="U39" s="92"/>
-      <c r="V39" s="52"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="53"/>
-      <c r="Z39" s="54"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="54"/>
-      <c r="AG39" s="52"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="54"/>
-      <c r="AJ39" s="52"/>
-      <c r="AK39" s="53"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="111"/>
-      <c r="AN39" s="112"/>
-      <c r="AO39" s="59"/>
-      <c r="AP39" s="60"/>
-      <c r="AQ39" s="61"/>
-      <c r="AR39" s="62"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
+      <c r="N39" s="65"/>
+      <c r="O39" s="65"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="66"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="68"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="68"/>
+      <c r="V39" s="72"/>
+      <c r="W39" s="74"/>
+      <c r="X39" s="72"/>
+      <c r="Y39" s="73"/>
+      <c r="Z39" s="74"/>
+      <c r="AA39" s="72"/>
+      <c r="AB39" s="73"/>
+      <c r="AC39" s="74"/>
+      <c r="AD39" s="72"/>
+      <c r="AE39" s="73"/>
+      <c r="AF39" s="74"/>
+      <c r="AG39" s="72"/>
+      <c r="AH39" s="73"/>
+      <c r="AI39" s="74"/>
+      <c r="AJ39" s="72"/>
+      <c r="AK39" s="73"/>
+      <c r="AL39" s="74"/>
+      <c r="AM39" s="123"/>
+      <c r="AN39" s="124"/>
+      <c r="AO39" s="75"/>
+      <c r="AP39" s="76"/>
+      <c r="AQ39" s="77"/>
+      <c r="AR39" s="78"/>
       <c r="AS39" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT39" s="63"/>
-      <c r="AU39" s="64"/>
-      <c r="AV39" s="59"/>
-      <c r="AW39" s="60"/>
-      <c r="AX39" s="111"/>
-      <c r="AY39" s="112"/>
-      <c r="AZ39" s="59"/>
-      <c r="BA39" s="60"/>
-      <c r="BB39" s="61"/>
-      <c r="BC39" s="62"/>
+      <c r="AT39" s="79"/>
+      <c r="AU39" s="80"/>
+      <c r="AV39" s="75"/>
+      <c r="AW39" s="76"/>
+      <c r="AX39" s="123"/>
+      <c r="AY39" s="124"/>
+      <c r="AZ39" s="75"/>
+      <c r="BA39" s="76"/>
+      <c r="BB39" s="77"/>
+      <c r="BC39" s="78"/>
       <c r="BD39" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE39" s="63"/>
-      <c r="BF39" s="64"/>
-      <c r="BG39" s="59"/>
-      <c r="BH39" s="60"/>
+      <c r="BE39" s="79"/>
+      <c r="BF39" s="80"/>
+      <c r="BG39" s="75"/>
+      <c r="BH39" s="76"/>
     </row>
     <row r="40" spans="2:60">
-      <c r="B40" s="55"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-      <c r="N40" s="57"/>
-      <c r="O40" s="57"/>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="91"/>
-      <c r="S40" s="92"/>
-      <c r="T40" s="91"/>
-      <c r="U40" s="92"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="54"/>
-      <c r="X40" s="52"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="54"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="53"/>
-      <c r="AC40" s="54"/>
-      <c r="AD40" s="52"/>
-      <c r="AE40" s="53"/>
-      <c r="AF40" s="54"/>
-      <c r="AG40" s="52"/>
-      <c r="AH40" s="53"/>
-      <c r="AI40" s="54"/>
-      <c r="AJ40" s="52"/>
-      <c r="AK40" s="53"/>
-      <c r="AL40" s="54"/>
-      <c r="AM40" s="111"/>
-      <c r="AN40" s="112"/>
-      <c r="AO40" s="59"/>
-      <c r="AP40" s="60"/>
-      <c r="AQ40" s="61"/>
-      <c r="AR40" s="62"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="63"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65"/>
+      <c r="L40" s="65"/>
+      <c r="M40" s="65"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="68"/>
+      <c r="T40" s="67"/>
+      <c r="U40" s="68"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="74"/>
+      <c r="X40" s="72"/>
+      <c r="Y40" s="73"/>
+      <c r="Z40" s="74"/>
+      <c r="AA40" s="72"/>
+      <c r="AB40" s="73"/>
+      <c r="AC40" s="74"/>
+      <c r="AD40" s="72"/>
+      <c r="AE40" s="73"/>
+      <c r="AF40" s="74"/>
+      <c r="AG40" s="72"/>
+      <c r="AH40" s="73"/>
+      <c r="AI40" s="74"/>
+      <c r="AJ40" s="72"/>
+      <c r="AK40" s="73"/>
+      <c r="AL40" s="74"/>
+      <c r="AM40" s="123"/>
+      <c r="AN40" s="124"/>
+      <c r="AO40" s="75"/>
+      <c r="AP40" s="76"/>
+      <c r="AQ40" s="77"/>
+      <c r="AR40" s="78"/>
       <c r="AS40" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT40" s="63"/>
-      <c r="AU40" s="64"/>
-      <c r="AV40" s="59"/>
-      <c r="AW40" s="60"/>
-      <c r="AX40" s="111"/>
-      <c r="AY40" s="112"/>
-      <c r="AZ40" s="59"/>
-      <c r="BA40" s="60"/>
-      <c r="BB40" s="61"/>
-      <c r="BC40" s="62"/>
+      <c r="AT40" s="79"/>
+      <c r="AU40" s="80"/>
+      <c r="AV40" s="75"/>
+      <c r="AW40" s="76"/>
+      <c r="AX40" s="123"/>
+      <c r="AY40" s="124"/>
+      <c r="AZ40" s="75"/>
+      <c r="BA40" s="76"/>
+      <c r="BB40" s="77"/>
+      <c r="BC40" s="78"/>
       <c r="BD40" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE40" s="63"/>
-      <c r="BF40" s="64"/>
-      <c r="BG40" s="59"/>
-      <c r="BH40" s="60"/>
+      <c r="BE40" s="79"/>
+      <c r="BF40" s="80"/>
+      <c r="BG40" s="75"/>
+      <c r="BH40" s="76"/>
     </row>
     <row r="41" spans="2:60">
-      <c r="B41" s="55"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
-      <c r="K41" s="57"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="57"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="57"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="91"/>
-      <c r="S41" s="92"/>
-      <c r="T41" s="91"/>
-      <c r="U41" s="92"/>
-      <c r="V41" s="52"/>
-      <c r="W41" s="54"/>
-      <c r="X41" s="52"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="54"/>
-      <c r="AA41" s="52"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="54"/>
-      <c r="AD41" s="52"/>
-      <c r="AE41" s="53"/>
-      <c r="AF41" s="54"/>
-      <c r="AG41" s="52"/>
-      <c r="AH41" s="53"/>
-      <c r="AI41" s="54"/>
-      <c r="AJ41" s="52"/>
-      <c r="AK41" s="53"/>
-      <c r="AL41" s="54"/>
-      <c r="AM41" s="111"/>
-      <c r="AN41" s="112"/>
-      <c r="AO41" s="59"/>
-      <c r="AP41" s="60"/>
-      <c r="AQ41" s="61"/>
-      <c r="AR41" s="62"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="67"/>
+      <c r="S41" s="68"/>
+      <c r="T41" s="67"/>
+      <c r="U41" s="68"/>
+      <c r="V41" s="72"/>
+      <c r="W41" s="74"/>
+      <c r="X41" s="72"/>
+      <c r="Y41" s="73"/>
+      <c r="Z41" s="74"/>
+      <c r="AA41" s="72"/>
+      <c r="AB41" s="73"/>
+      <c r="AC41" s="74"/>
+      <c r="AD41" s="72"/>
+      <c r="AE41" s="73"/>
+      <c r="AF41" s="74"/>
+      <c r="AG41" s="72"/>
+      <c r="AH41" s="73"/>
+      <c r="AI41" s="74"/>
+      <c r="AJ41" s="72"/>
+      <c r="AK41" s="73"/>
+      <c r="AL41" s="74"/>
+      <c r="AM41" s="123"/>
+      <c r="AN41" s="124"/>
+      <c r="AO41" s="75"/>
+      <c r="AP41" s="76"/>
+      <c r="AQ41" s="77"/>
+      <c r="AR41" s="78"/>
       <c r="AS41" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT41" s="63"/>
-      <c r="AU41" s="64"/>
-      <c r="AV41" s="59"/>
-      <c r="AW41" s="60"/>
-      <c r="AX41" s="111"/>
-      <c r="AY41" s="112"/>
-      <c r="AZ41" s="59"/>
-      <c r="BA41" s="60"/>
-      <c r="BB41" s="61"/>
-      <c r="BC41" s="62"/>
+      <c r="AT41" s="79"/>
+      <c r="AU41" s="80"/>
+      <c r="AV41" s="75"/>
+      <c r="AW41" s="76"/>
+      <c r="AX41" s="123"/>
+      <c r="AY41" s="124"/>
+      <c r="AZ41" s="75"/>
+      <c r="BA41" s="76"/>
+      <c r="BB41" s="77"/>
+      <c r="BC41" s="78"/>
       <c r="BD41" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE41" s="63"/>
-      <c r="BF41" s="64"/>
-      <c r="BG41" s="59"/>
-      <c r="BH41" s="60"/>
+      <c r="BE41" s="79"/>
+      <c r="BF41" s="80"/>
+      <c r="BG41" s="75"/>
+      <c r="BH41" s="76"/>
     </row>
     <row r="42" spans="2:60">
-      <c r="B42" s="55"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="91"/>
-      <c r="S42" s="92"/>
-      <c r="T42" s="91"/>
-      <c r="U42" s="92"/>
-      <c r="V42" s="52"/>
-      <c r="W42" s="54"/>
-      <c r="X42" s="52"/>
-      <c r="Y42" s="53"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="53"/>
-      <c r="AC42" s="54"/>
-      <c r="AD42" s="52"/>
-      <c r="AE42" s="53"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="52"/>
-      <c r="AH42" s="53"/>
-      <c r="AI42" s="54"/>
-      <c r="AJ42" s="52"/>
-      <c r="AK42" s="53"/>
-      <c r="AL42" s="54"/>
-      <c r="AM42" s="111"/>
-      <c r="AN42" s="112"/>
-      <c r="AO42" s="59"/>
-      <c r="AP42" s="60"/>
-      <c r="AQ42" s="61"/>
-      <c r="AR42" s="62"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="68"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="68"/>
+      <c r="V42" s="72"/>
+      <c r="W42" s="74"/>
+      <c r="X42" s="72"/>
+      <c r="Y42" s="73"/>
+      <c r="Z42" s="74"/>
+      <c r="AA42" s="72"/>
+      <c r="AB42" s="73"/>
+      <c r="AC42" s="74"/>
+      <c r="AD42" s="72"/>
+      <c r="AE42" s="73"/>
+      <c r="AF42" s="74"/>
+      <c r="AG42" s="72"/>
+      <c r="AH42" s="73"/>
+      <c r="AI42" s="74"/>
+      <c r="AJ42" s="72"/>
+      <c r="AK42" s="73"/>
+      <c r="AL42" s="74"/>
+      <c r="AM42" s="123"/>
+      <c r="AN42" s="124"/>
+      <c r="AO42" s="75"/>
+      <c r="AP42" s="76"/>
+      <c r="AQ42" s="77"/>
+      <c r="AR42" s="78"/>
       <c r="AS42" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT42" s="63"/>
-      <c r="AU42" s="64"/>
-      <c r="AV42" s="59"/>
-      <c r="AW42" s="60"/>
-      <c r="AX42" s="111"/>
-      <c r="AY42" s="112"/>
-      <c r="AZ42" s="59"/>
-      <c r="BA42" s="60"/>
-      <c r="BB42" s="61"/>
-      <c r="BC42" s="62"/>
+      <c r="AT42" s="79"/>
+      <c r="AU42" s="80"/>
+      <c r="AV42" s="75"/>
+      <c r="AW42" s="76"/>
+      <c r="AX42" s="123"/>
+      <c r="AY42" s="124"/>
+      <c r="AZ42" s="75"/>
+      <c r="BA42" s="76"/>
+      <c r="BB42" s="77"/>
+      <c r="BC42" s="78"/>
       <c r="BD42" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE42" s="63"/>
-      <c r="BF42" s="64"/>
-      <c r="BG42" s="59"/>
-      <c r="BH42" s="60"/>
+      <c r="BE42" s="79"/>
+      <c r="BF42" s="80"/>
+      <c r="BG42" s="75"/>
+      <c r="BH42" s="76"/>
     </row>
     <row r="43" spans="2:60">
-      <c r="B43" s="55"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="57"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="57"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="91"/>
-      <c r="S43" s="92"/>
-      <c r="T43" s="91"/>
-      <c r="U43" s="92"/>
-      <c r="V43" s="52"/>
-      <c r="W43" s="54"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="52"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="54"/>
-      <c r="AD43" s="52"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="52"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="54"/>
-      <c r="AJ43" s="52"/>
-      <c r="AK43" s="53"/>
-      <c r="AL43" s="54"/>
-      <c r="AM43" s="111"/>
-      <c r="AN43" s="112"/>
-      <c r="AO43" s="59"/>
-      <c r="AP43" s="60"/>
-      <c r="AQ43" s="61"/>
-      <c r="AR43" s="62"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="68"/>
+      <c r="T43" s="67"/>
+      <c r="U43" s="68"/>
+      <c r="V43" s="72"/>
+      <c r="W43" s="74"/>
+      <c r="X43" s="72"/>
+      <c r="Y43" s="73"/>
+      <c r="Z43" s="74"/>
+      <c r="AA43" s="72"/>
+      <c r="AB43" s="73"/>
+      <c r="AC43" s="74"/>
+      <c r="AD43" s="72"/>
+      <c r="AE43" s="73"/>
+      <c r="AF43" s="74"/>
+      <c r="AG43" s="72"/>
+      <c r="AH43" s="73"/>
+      <c r="AI43" s="74"/>
+      <c r="AJ43" s="72"/>
+      <c r="AK43" s="73"/>
+      <c r="AL43" s="74"/>
+      <c r="AM43" s="123"/>
+      <c r="AN43" s="124"/>
+      <c r="AO43" s="75"/>
+      <c r="AP43" s="76"/>
+      <c r="AQ43" s="77"/>
+      <c r="AR43" s="78"/>
       <c r="AS43" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT43" s="63"/>
-      <c r="AU43" s="64"/>
-      <c r="AV43" s="59"/>
-      <c r="AW43" s="60"/>
-      <c r="AX43" s="111"/>
-      <c r="AY43" s="112"/>
-      <c r="AZ43" s="59"/>
-      <c r="BA43" s="60"/>
-      <c r="BB43" s="61"/>
-      <c r="BC43" s="62"/>
+      <c r="AT43" s="79"/>
+      <c r="AU43" s="80"/>
+      <c r="AV43" s="75"/>
+      <c r="AW43" s="76"/>
+      <c r="AX43" s="123"/>
+      <c r="AY43" s="124"/>
+      <c r="AZ43" s="75"/>
+      <c r="BA43" s="76"/>
+      <c r="BB43" s="77"/>
+      <c r="BC43" s="78"/>
       <c r="BD43" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE43" s="63"/>
-      <c r="BF43" s="64"/>
-      <c r="BG43" s="59"/>
-      <c r="BH43" s="60"/>
+      <c r="BE43" s="79"/>
+      <c r="BF43" s="80"/>
+      <c r="BG43" s="75"/>
+      <c r="BH43" s="76"/>
     </row>
     <row r="44" spans="2:60">
-      <c r="B44" s="55"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="58"/>
-      <c r="R44" s="91"/>
-      <c r="S44" s="92"/>
-      <c r="T44" s="91"/>
-      <c r="U44" s="92"/>
-      <c r="V44" s="52"/>
-      <c r="W44" s="54"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="53"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="52"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="54"/>
-      <c r="AD44" s="52"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="54"/>
-      <c r="AG44" s="52"/>
-      <c r="AH44" s="53"/>
-      <c r="AI44" s="54"/>
-      <c r="AJ44" s="52"/>
-      <c r="AK44" s="53"/>
-      <c r="AL44" s="54"/>
-      <c r="AM44" s="111"/>
-      <c r="AN44" s="112"/>
-      <c r="AO44" s="59"/>
-      <c r="AP44" s="60"/>
-      <c r="AQ44" s="61"/>
-      <c r="AR44" s="62"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="67"/>
+      <c r="S44" s="68"/>
+      <c r="T44" s="67"/>
+      <c r="U44" s="68"/>
+      <c r="V44" s="72"/>
+      <c r="W44" s="74"/>
+      <c r="X44" s="72"/>
+      <c r="Y44" s="73"/>
+      <c r="Z44" s="74"/>
+      <c r="AA44" s="72"/>
+      <c r="AB44" s="73"/>
+      <c r="AC44" s="74"/>
+      <c r="AD44" s="72"/>
+      <c r="AE44" s="73"/>
+      <c r="AF44" s="74"/>
+      <c r="AG44" s="72"/>
+      <c r="AH44" s="73"/>
+      <c r="AI44" s="74"/>
+      <c r="AJ44" s="72"/>
+      <c r="AK44" s="73"/>
+      <c r="AL44" s="74"/>
+      <c r="AM44" s="123"/>
+      <c r="AN44" s="124"/>
+      <c r="AO44" s="75"/>
+      <c r="AP44" s="76"/>
+      <c r="AQ44" s="77"/>
+      <c r="AR44" s="78"/>
       <c r="AS44" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT44" s="63"/>
-      <c r="AU44" s="64"/>
-      <c r="AV44" s="59"/>
-      <c r="AW44" s="60"/>
-      <c r="AX44" s="111"/>
-      <c r="AY44" s="112"/>
-      <c r="AZ44" s="59"/>
-      <c r="BA44" s="60"/>
-      <c r="BB44" s="61"/>
-      <c r="BC44" s="62"/>
+      <c r="AT44" s="79"/>
+      <c r="AU44" s="80"/>
+      <c r="AV44" s="75"/>
+      <c r="AW44" s="76"/>
+      <c r="AX44" s="123"/>
+      <c r="AY44" s="124"/>
+      <c r="AZ44" s="75"/>
+      <c r="BA44" s="76"/>
+      <c r="BB44" s="77"/>
+      <c r="BC44" s="78"/>
       <c r="BD44" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE44" s="63"/>
-      <c r="BF44" s="64"/>
-      <c r="BG44" s="59"/>
-      <c r="BH44" s="60"/>
+      <c r="BE44" s="79"/>
+      <c r="BF44" s="80"/>
+      <c r="BG44" s="75"/>
+      <c r="BH44" s="76"/>
     </row>
     <row r="45" spans="2:60">
-      <c r="B45" s="55"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
-      <c r="K45" s="57"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="57"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="91"/>
-      <c r="S45" s="92"/>
-      <c r="T45" s="91"/>
-      <c r="U45" s="92"/>
-      <c r="V45" s="52"/>
-      <c r="W45" s="54"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="53"/>
-      <c r="Z45" s="54"/>
-      <c r="AA45" s="52"/>
-      <c r="AB45" s="53"/>
-      <c r="AC45" s="54"/>
-      <c r="AD45" s="52"/>
-      <c r="AE45" s="53"/>
-      <c r="AF45" s="54"/>
-      <c r="AG45" s="52"/>
-      <c r="AH45" s="53"/>
-      <c r="AI45" s="54"/>
-      <c r="AJ45" s="52"/>
-      <c r="AK45" s="53"/>
-      <c r="AL45" s="54"/>
-      <c r="AM45" s="111"/>
-      <c r="AN45" s="112"/>
-      <c r="AO45" s="59"/>
-      <c r="AP45" s="60"/>
-      <c r="AQ45" s="61"/>
-      <c r="AR45" s="62"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="67"/>
+      <c r="S45" s="68"/>
+      <c r="T45" s="67"/>
+      <c r="U45" s="68"/>
+      <c r="V45" s="72"/>
+      <c r="W45" s="74"/>
+      <c r="X45" s="72"/>
+      <c r="Y45" s="73"/>
+      <c r="Z45" s="74"/>
+      <c r="AA45" s="72"/>
+      <c r="AB45" s="73"/>
+      <c r="AC45" s="74"/>
+      <c r="AD45" s="72"/>
+      <c r="AE45" s="73"/>
+      <c r="AF45" s="74"/>
+      <c r="AG45" s="72"/>
+      <c r="AH45" s="73"/>
+      <c r="AI45" s="74"/>
+      <c r="AJ45" s="72"/>
+      <c r="AK45" s="73"/>
+      <c r="AL45" s="74"/>
+      <c r="AM45" s="123"/>
+      <c r="AN45" s="124"/>
+      <c r="AO45" s="75"/>
+      <c r="AP45" s="76"/>
+      <c r="AQ45" s="77"/>
+      <c r="AR45" s="78"/>
       <c r="AS45" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT45" s="63"/>
-      <c r="AU45" s="64"/>
-      <c r="AV45" s="59"/>
-      <c r="AW45" s="60"/>
-      <c r="AX45" s="111"/>
-      <c r="AY45" s="112"/>
-      <c r="AZ45" s="59"/>
-      <c r="BA45" s="60"/>
-      <c r="BB45" s="61"/>
-      <c r="BC45" s="62"/>
+      <c r="AT45" s="79"/>
+      <c r="AU45" s="80"/>
+      <c r="AV45" s="75"/>
+      <c r="AW45" s="76"/>
+      <c r="AX45" s="123"/>
+      <c r="AY45" s="124"/>
+      <c r="AZ45" s="75"/>
+      <c r="BA45" s="76"/>
+      <c r="BB45" s="77"/>
+      <c r="BC45" s="78"/>
       <c r="BD45" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE45" s="63"/>
-      <c r="BF45" s="64"/>
-      <c r="BG45" s="59"/>
-      <c r="BH45" s="60"/>
+      <c r="BE45" s="79"/>
+      <c r="BF45" s="80"/>
+      <c r="BG45" s="75"/>
+      <c r="BH45" s="76"/>
     </row>
     <row r="46" spans="2:60">
-      <c r="B46" s="55"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="57"/>
-      <c r="O46" s="57"/>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="58"/>
-      <c r="R46" s="91"/>
-      <c r="S46" s="92"/>
-      <c r="T46" s="91"/>
-      <c r="U46" s="92"/>
-      <c r="V46" s="52"/>
-      <c r="W46" s="54"/>
-      <c r="X46" s="52"/>
-      <c r="Y46" s="53"/>
-      <c r="Z46" s="54"/>
-      <c r="AA46" s="52"/>
-      <c r="AB46" s="53"/>
-      <c r="AC46" s="54"/>
-      <c r="AD46" s="52"/>
-      <c r="AE46" s="53"/>
-      <c r="AF46" s="54"/>
-      <c r="AG46" s="52"/>
-      <c r="AH46" s="53"/>
-      <c r="AI46" s="54"/>
-      <c r="AJ46" s="52"/>
-      <c r="AK46" s="53"/>
-      <c r="AL46" s="54"/>
-      <c r="AM46" s="111"/>
-      <c r="AN46" s="112"/>
-      <c r="AO46" s="59"/>
-      <c r="AP46" s="60"/>
-      <c r="AQ46" s="61"/>
-      <c r="AR46" s="62"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="65"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="66"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="67"/>
+      <c r="U46" s="68"/>
+      <c r="V46" s="72"/>
+      <c r="W46" s="74"/>
+      <c r="X46" s="72"/>
+      <c r="Y46" s="73"/>
+      <c r="Z46" s="74"/>
+      <c r="AA46" s="72"/>
+      <c r="AB46" s="73"/>
+      <c r="AC46" s="74"/>
+      <c r="AD46" s="72"/>
+      <c r="AE46" s="73"/>
+      <c r="AF46" s="74"/>
+      <c r="AG46" s="72"/>
+      <c r="AH46" s="73"/>
+      <c r="AI46" s="74"/>
+      <c r="AJ46" s="72"/>
+      <c r="AK46" s="73"/>
+      <c r="AL46" s="74"/>
+      <c r="AM46" s="123"/>
+      <c r="AN46" s="124"/>
+      <c r="AO46" s="75"/>
+      <c r="AP46" s="76"/>
+      <c r="AQ46" s="77"/>
+      <c r="AR46" s="78"/>
       <c r="AS46" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT46" s="63"/>
-      <c r="AU46" s="64"/>
-      <c r="AV46" s="59"/>
-      <c r="AW46" s="60"/>
-      <c r="AX46" s="111"/>
-      <c r="AY46" s="112"/>
-      <c r="AZ46" s="59"/>
-      <c r="BA46" s="60"/>
-      <c r="BB46" s="61"/>
-      <c r="BC46" s="62"/>
+      <c r="AT46" s="79"/>
+      <c r="AU46" s="80"/>
+      <c r="AV46" s="75"/>
+      <c r="AW46" s="76"/>
+      <c r="AX46" s="123"/>
+      <c r="AY46" s="124"/>
+      <c r="AZ46" s="75"/>
+      <c r="BA46" s="76"/>
+      <c r="BB46" s="77"/>
+      <c r="BC46" s="78"/>
       <c r="BD46" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE46" s="63"/>
-      <c r="BF46" s="64"/>
-      <c r="BG46" s="59"/>
-      <c r="BH46" s="60"/>
+      <c r="BE46" s="79"/>
+      <c r="BF46" s="80"/>
+      <c r="BG46" s="75"/>
+      <c r="BH46" s="76"/>
     </row>
     <row r="47" spans="2:60">
-      <c r="B47" s="55"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="57"/>
-      <c r="N47" s="57"/>
-      <c r="O47" s="57"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="91"/>
-      <c r="S47" s="92"/>
-      <c r="T47" s="91"/>
-      <c r="U47" s="92"/>
-      <c r="V47" s="52"/>
-      <c r="W47" s="54"/>
-      <c r="X47" s="52"/>
-      <c r="Y47" s="53"/>
-      <c r="Z47" s="54"/>
-      <c r="AA47" s="52"/>
-      <c r="AB47" s="53"/>
-      <c r="AC47" s="54"/>
-      <c r="AD47" s="52"/>
-      <c r="AE47" s="53"/>
-      <c r="AF47" s="54"/>
-      <c r="AG47" s="52"/>
-      <c r="AH47" s="53"/>
-      <c r="AI47" s="54"/>
-      <c r="AJ47" s="52"/>
-      <c r="AK47" s="53"/>
-      <c r="AL47" s="54"/>
-      <c r="AM47" s="111"/>
-      <c r="AN47" s="112"/>
-      <c r="AO47" s="59"/>
-      <c r="AP47" s="60"/>
-      <c r="AQ47" s="61"/>
-      <c r="AR47" s="62"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="68"/>
+      <c r="T47" s="67"/>
+      <c r="U47" s="68"/>
+      <c r="V47" s="72"/>
+      <c r="W47" s="74"/>
+      <c r="X47" s="72"/>
+      <c r="Y47" s="73"/>
+      <c r="Z47" s="74"/>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="73"/>
+      <c r="AC47" s="74"/>
+      <c r="AD47" s="72"/>
+      <c r="AE47" s="73"/>
+      <c r="AF47" s="74"/>
+      <c r="AG47" s="72"/>
+      <c r="AH47" s="73"/>
+      <c r="AI47" s="74"/>
+      <c r="AJ47" s="72"/>
+      <c r="AK47" s="73"/>
+      <c r="AL47" s="74"/>
+      <c r="AM47" s="123"/>
+      <c r="AN47" s="124"/>
+      <c r="AO47" s="75"/>
+      <c r="AP47" s="76"/>
+      <c r="AQ47" s="77"/>
+      <c r="AR47" s="78"/>
       <c r="AS47" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT47" s="63"/>
-      <c r="AU47" s="64"/>
-      <c r="AV47" s="59"/>
-      <c r="AW47" s="60"/>
-      <c r="AX47" s="111"/>
-      <c r="AY47" s="112"/>
-      <c r="AZ47" s="59"/>
-      <c r="BA47" s="60"/>
-      <c r="BB47" s="61"/>
-      <c r="BC47" s="62"/>
+      <c r="AT47" s="79"/>
+      <c r="AU47" s="80"/>
+      <c r="AV47" s="75"/>
+      <c r="AW47" s="76"/>
+      <c r="AX47" s="123"/>
+      <c r="AY47" s="124"/>
+      <c r="AZ47" s="75"/>
+      <c r="BA47" s="76"/>
+      <c r="BB47" s="77"/>
+      <c r="BC47" s="78"/>
       <c r="BD47" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE47" s="63"/>
-      <c r="BF47" s="64"/>
-      <c r="BG47" s="59"/>
-      <c r="BH47" s="60"/>
+      <c r="BE47" s="79"/>
+      <c r="BF47" s="80"/>
+      <c r="BG47" s="75"/>
+      <c r="BH47" s="76"/>
     </row>
     <row r="48" spans="2:60">
-      <c r="B48" s="55"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="57"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-      <c r="N48" s="57"/>
-      <c r="O48" s="57"/>
-      <c r="P48" s="57"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="91"/>
-      <c r="S48" s="92"/>
-      <c r="T48" s="91"/>
-      <c r="U48" s="92"/>
-      <c r="V48" s="52"/>
-      <c r="W48" s="54"/>
-      <c r="X48" s="52"/>
-      <c r="Y48" s="53"/>
-      <c r="Z48" s="54"/>
-      <c r="AA48" s="52"/>
-      <c r="AB48" s="53"/>
-      <c r="AC48" s="54"/>
-      <c r="AD48" s="52"/>
-      <c r="AE48" s="53"/>
-      <c r="AF48" s="54"/>
-      <c r="AG48" s="52"/>
-      <c r="AH48" s="53"/>
-      <c r="AI48" s="54"/>
-      <c r="AJ48" s="52"/>
-      <c r="AK48" s="53"/>
-      <c r="AL48" s="54"/>
-      <c r="AM48" s="111"/>
-      <c r="AN48" s="112"/>
-      <c r="AO48" s="59"/>
-      <c r="AP48" s="60"/>
-      <c r="AQ48" s="61"/>
-      <c r="AR48" s="62"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="66"/>
+      <c r="R48" s="67"/>
+      <c r="S48" s="68"/>
+      <c r="T48" s="67"/>
+      <c r="U48" s="68"/>
+      <c r="V48" s="72"/>
+      <c r="W48" s="74"/>
+      <c r="X48" s="72"/>
+      <c r="Y48" s="73"/>
+      <c r="Z48" s="74"/>
+      <c r="AA48" s="72"/>
+      <c r="AB48" s="73"/>
+      <c r="AC48" s="74"/>
+      <c r="AD48" s="72"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="74"/>
+      <c r="AG48" s="72"/>
+      <c r="AH48" s="73"/>
+      <c r="AI48" s="74"/>
+      <c r="AJ48" s="72"/>
+      <c r="AK48" s="73"/>
+      <c r="AL48" s="74"/>
+      <c r="AM48" s="123"/>
+      <c r="AN48" s="124"/>
+      <c r="AO48" s="75"/>
+      <c r="AP48" s="76"/>
+      <c r="AQ48" s="77"/>
+      <c r="AR48" s="78"/>
       <c r="AS48" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT48" s="63"/>
-      <c r="AU48" s="64"/>
-      <c r="AV48" s="59"/>
-      <c r="AW48" s="60"/>
-      <c r="AX48" s="111"/>
-      <c r="AY48" s="112"/>
-      <c r="AZ48" s="59"/>
-      <c r="BA48" s="60"/>
-      <c r="BB48" s="61"/>
-      <c r="BC48" s="62"/>
+      <c r="AT48" s="79"/>
+      <c r="AU48" s="80"/>
+      <c r="AV48" s="75"/>
+      <c r="AW48" s="76"/>
+      <c r="AX48" s="123"/>
+      <c r="AY48" s="124"/>
+      <c r="AZ48" s="75"/>
+      <c r="BA48" s="76"/>
+      <c r="BB48" s="77"/>
+      <c r="BC48" s="78"/>
       <c r="BD48" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE48" s="63"/>
-      <c r="BF48" s="64"/>
-      <c r="BG48" s="59"/>
-      <c r="BH48" s="60"/>
+      <c r="BE48" s="79"/>
+      <c r="BF48" s="80"/>
+      <c r="BG48" s="75"/>
+      <c r="BH48" s="76"/>
     </row>
     <row r="49" spans="2:60">
-      <c r="B49" s="55"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="57"/>
-      <c r="N49" s="57"/>
-      <c r="O49" s="57"/>
-      <c r="P49" s="57"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="91"/>
-      <c r="S49" s="92"/>
-      <c r="T49" s="91"/>
-      <c r="U49" s="92"/>
-      <c r="V49" s="52"/>
-      <c r="W49" s="54"/>
-      <c r="X49" s="52"/>
-      <c r="Y49" s="53"/>
-      <c r="Z49" s="54"/>
-      <c r="AA49" s="52"/>
-      <c r="AB49" s="53"/>
-      <c r="AC49" s="54"/>
-      <c r="AD49" s="52"/>
-      <c r="AE49" s="53"/>
-      <c r="AF49" s="54"/>
-      <c r="AG49" s="52"/>
-      <c r="AH49" s="53"/>
-      <c r="AI49" s="54"/>
-      <c r="AJ49" s="52"/>
-      <c r="AK49" s="53"/>
-      <c r="AL49" s="54"/>
-      <c r="AM49" s="111"/>
-      <c r="AN49" s="112"/>
-      <c r="AO49" s="59"/>
-      <c r="AP49" s="60"/>
-      <c r="AQ49" s="61"/>
-      <c r="AR49" s="62"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="66"/>
+      <c r="R49" s="67"/>
+      <c r="S49" s="68"/>
+      <c r="T49" s="67"/>
+      <c r="U49" s="68"/>
+      <c r="V49" s="72"/>
+      <c r="W49" s="74"/>
+      <c r="X49" s="72"/>
+      <c r="Y49" s="73"/>
+      <c r="Z49" s="74"/>
+      <c r="AA49" s="72"/>
+      <c r="AB49" s="73"/>
+      <c r="AC49" s="74"/>
+      <c r="AD49" s="72"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="74"/>
+      <c r="AG49" s="72"/>
+      <c r="AH49" s="73"/>
+      <c r="AI49" s="74"/>
+      <c r="AJ49" s="72"/>
+      <c r="AK49" s="73"/>
+      <c r="AL49" s="74"/>
+      <c r="AM49" s="123"/>
+      <c r="AN49" s="124"/>
+      <c r="AO49" s="75"/>
+      <c r="AP49" s="76"/>
+      <c r="AQ49" s="77"/>
+      <c r="AR49" s="78"/>
       <c r="AS49" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT49" s="63"/>
-      <c r="AU49" s="64"/>
-      <c r="AV49" s="59"/>
-      <c r="AW49" s="60"/>
-      <c r="AX49" s="111"/>
-      <c r="AY49" s="112"/>
-      <c r="AZ49" s="59"/>
-      <c r="BA49" s="60"/>
-      <c r="BB49" s="61"/>
-      <c r="BC49" s="62"/>
+      <c r="AT49" s="79"/>
+      <c r="AU49" s="80"/>
+      <c r="AV49" s="75"/>
+      <c r="AW49" s="76"/>
+      <c r="AX49" s="123"/>
+      <c r="AY49" s="124"/>
+      <c r="AZ49" s="75"/>
+      <c r="BA49" s="76"/>
+      <c r="BB49" s="77"/>
+      <c r="BC49" s="78"/>
       <c r="BD49" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE49" s="63"/>
-      <c r="BF49" s="64"/>
-      <c r="BG49" s="59"/>
-      <c r="BH49" s="60"/>
+      <c r="BE49" s="79"/>
+      <c r="BF49" s="80"/>
+      <c r="BG49" s="75"/>
+      <c r="BH49" s="76"/>
     </row>
     <row r="50" spans="2:60">
-      <c r="B50" s="55"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="57"/>
-      <c r="N50" s="57"/>
-      <c r="O50" s="57"/>
-      <c r="P50" s="57"/>
-      <c r="Q50" s="58"/>
-      <c r="R50" s="91"/>
-      <c r="S50" s="92"/>
-      <c r="T50" s="91"/>
-      <c r="U50" s="92"/>
-      <c r="V50" s="52"/>
-      <c r="W50" s="54"/>
-      <c r="X50" s="52"/>
-      <c r="Y50" s="53"/>
-      <c r="Z50" s="54"/>
-      <c r="AA50" s="52"/>
-      <c r="AB50" s="53"/>
-      <c r="AC50" s="54"/>
-      <c r="AD50" s="52"/>
-      <c r="AE50" s="53"/>
-      <c r="AF50" s="54"/>
-      <c r="AG50" s="52"/>
-      <c r="AH50" s="53"/>
-      <c r="AI50" s="54"/>
-      <c r="AJ50" s="52"/>
-      <c r="AK50" s="53"/>
-      <c r="AL50" s="54"/>
-      <c r="AM50" s="111"/>
-      <c r="AN50" s="112"/>
-      <c r="AO50" s="59"/>
-      <c r="AP50" s="60"/>
-      <c r="AQ50" s="61"/>
-      <c r="AR50" s="62"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="65"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="66"/>
+      <c r="R50" s="67"/>
+      <c r="S50" s="68"/>
+      <c r="T50" s="67"/>
+      <c r="U50" s="68"/>
+      <c r="V50" s="72"/>
+      <c r="W50" s="74"/>
+      <c r="X50" s="72"/>
+      <c r="Y50" s="73"/>
+      <c r="Z50" s="74"/>
+      <c r="AA50" s="72"/>
+      <c r="AB50" s="73"/>
+      <c r="AC50" s="74"/>
+      <c r="AD50" s="72"/>
+      <c r="AE50" s="73"/>
+      <c r="AF50" s="74"/>
+      <c r="AG50" s="72"/>
+      <c r="AH50" s="73"/>
+      <c r="AI50" s="74"/>
+      <c r="AJ50" s="72"/>
+      <c r="AK50" s="73"/>
+      <c r="AL50" s="74"/>
+      <c r="AM50" s="123"/>
+      <c r="AN50" s="124"/>
+      <c r="AO50" s="75"/>
+      <c r="AP50" s="76"/>
+      <c r="AQ50" s="77"/>
+      <c r="AR50" s="78"/>
       <c r="AS50" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT50" s="63"/>
-      <c r="AU50" s="64"/>
-      <c r="AV50" s="59"/>
-      <c r="AW50" s="60"/>
-      <c r="AX50" s="111"/>
-      <c r="AY50" s="112"/>
-      <c r="AZ50" s="59"/>
-      <c r="BA50" s="60"/>
-      <c r="BB50" s="61"/>
-      <c r="BC50" s="62"/>
+      <c r="AT50" s="79"/>
+      <c r="AU50" s="80"/>
+      <c r="AV50" s="75"/>
+      <c r="AW50" s="76"/>
+      <c r="AX50" s="123"/>
+      <c r="AY50" s="124"/>
+      <c r="AZ50" s="75"/>
+      <c r="BA50" s="76"/>
+      <c r="BB50" s="77"/>
+      <c r="BC50" s="78"/>
       <c r="BD50" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE50" s="63"/>
-      <c r="BF50" s="64"/>
-      <c r="BG50" s="59"/>
-      <c r="BH50" s="60"/>
+      <c r="BE50" s="79"/>
+      <c r="BF50" s="80"/>
+      <c r="BG50" s="75"/>
+      <c r="BH50" s="76"/>
     </row>
     <row r="51" spans="2:60">
-      <c r="B51" s="55"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="57"/>
-      <c r="L51" s="57"/>
-      <c r="M51" s="57"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="58"/>
-      <c r="R51" s="91"/>
-      <c r="S51" s="92"/>
-      <c r="T51" s="91"/>
-      <c r="U51" s="92"/>
-      <c r="V51" s="52"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="52"/>
-      <c r="Y51" s="53"/>
-      <c r="Z51" s="54"/>
-      <c r="AA51" s="52"/>
-      <c r="AB51" s="53"/>
-      <c r="AC51" s="54"/>
-      <c r="AD51" s="52"/>
-      <c r="AE51" s="53"/>
-      <c r="AF51" s="54"/>
-      <c r="AG51" s="52"/>
-      <c r="AH51" s="53"/>
-      <c r="AI51" s="54"/>
-      <c r="AJ51" s="52"/>
-      <c r="AK51" s="53"/>
-      <c r="AL51" s="54"/>
-      <c r="AM51" s="111"/>
-      <c r="AN51" s="112"/>
-      <c r="AO51" s="59"/>
-      <c r="AP51" s="60"/>
-      <c r="AQ51" s="61"/>
-      <c r="AR51" s="62"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="65"/>
+      <c r="K51" s="65"/>
+      <c r="L51" s="65"/>
+      <c r="M51" s="65"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="65"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="68"/>
+      <c r="T51" s="67"/>
+      <c r="U51" s="68"/>
+      <c r="V51" s="72"/>
+      <c r="W51" s="74"/>
+      <c r="X51" s="72"/>
+      <c r="Y51" s="73"/>
+      <c r="Z51" s="74"/>
+      <c r="AA51" s="72"/>
+      <c r="AB51" s="73"/>
+      <c r="AC51" s="74"/>
+      <c r="AD51" s="72"/>
+      <c r="AE51" s="73"/>
+      <c r="AF51" s="74"/>
+      <c r="AG51" s="72"/>
+      <c r="AH51" s="73"/>
+      <c r="AI51" s="74"/>
+      <c r="AJ51" s="72"/>
+      <c r="AK51" s="73"/>
+      <c r="AL51" s="74"/>
+      <c r="AM51" s="123"/>
+      <c r="AN51" s="124"/>
+      <c r="AO51" s="75"/>
+      <c r="AP51" s="76"/>
+      <c r="AQ51" s="77"/>
+      <c r="AR51" s="78"/>
       <c r="AS51" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT51" s="63"/>
-      <c r="AU51" s="64"/>
-      <c r="AV51" s="59"/>
-      <c r="AW51" s="60"/>
-      <c r="AX51" s="111"/>
-      <c r="AY51" s="112"/>
-      <c r="AZ51" s="59"/>
-      <c r="BA51" s="60"/>
-      <c r="BB51" s="61"/>
-      <c r="BC51" s="62"/>
+      <c r="AT51" s="79"/>
+      <c r="AU51" s="80"/>
+      <c r="AV51" s="75"/>
+      <c r="AW51" s="76"/>
+      <c r="AX51" s="123"/>
+      <c r="AY51" s="124"/>
+      <c r="AZ51" s="75"/>
+      <c r="BA51" s="76"/>
+      <c r="BB51" s="77"/>
+      <c r="BC51" s="78"/>
       <c r="BD51" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE51" s="63"/>
-      <c r="BF51" s="64"/>
-      <c r="BG51" s="59"/>
-      <c r="BH51" s="60"/>
+      <c r="BE51" s="79"/>
+      <c r="BF51" s="80"/>
+      <c r="BG51" s="75"/>
+      <c r="BH51" s="76"/>
     </row>
     <row r="52" spans="2:60">
-      <c r="B52" s="55"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="57"/>
-      <c r="L52" s="57"/>
-      <c r="M52" s="57"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="58"/>
-      <c r="R52" s="91"/>
-      <c r="S52" s="92"/>
-      <c r="T52" s="91"/>
-      <c r="U52" s="92"/>
-      <c r="V52" s="52"/>
-      <c r="W52" s="54"/>
-      <c r="X52" s="52"/>
-      <c r="Y52" s="53"/>
-      <c r="Z52" s="54"/>
-      <c r="AA52" s="52"/>
-      <c r="AB52" s="53"/>
-      <c r="AC52" s="54"/>
-      <c r="AD52" s="52"/>
-      <c r="AE52" s="53"/>
-      <c r="AF52" s="54"/>
-      <c r="AG52" s="52"/>
-      <c r="AH52" s="53"/>
-      <c r="AI52" s="54"/>
-      <c r="AJ52" s="52"/>
-      <c r="AK52" s="53"/>
-      <c r="AL52" s="54"/>
-      <c r="AM52" s="111"/>
-      <c r="AN52" s="112"/>
-      <c r="AO52" s="59"/>
-      <c r="AP52" s="60"/>
-      <c r="AQ52" s="61"/>
-      <c r="AR52" s="62"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="65"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
+      <c r="O52" s="65"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="66"/>
+      <c r="R52" s="67"/>
+      <c r="S52" s="68"/>
+      <c r="T52" s="67"/>
+      <c r="U52" s="68"/>
+      <c r="V52" s="72"/>
+      <c r="W52" s="74"/>
+      <c r="X52" s="72"/>
+      <c r="Y52" s="73"/>
+      <c r="Z52" s="74"/>
+      <c r="AA52" s="72"/>
+      <c r="AB52" s="73"/>
+      <c r="AC52" s="74"/>
+      <c r="AD52" s="72"/>
+      <c r="AE52" s="73"/>
+      <c r="AF52" s="74"/>
+      <c r="AG52" s="72"/>
+      <c r="AH52" s="73"/>
+      <c r="AI52" s="74"/>
+      <c r="AJ52" s="72"/>
+      <c r="AK52" s="73"/>
+      <c r="AL52" s="74"/>
+      <c r="AM52" s="123"/>
+      <c r="AN52" s="124"/>
+      <c r="AO52" s="75"/>
+      <c r="AP52" s="76"/>
+      <c r="AQ52" s="77"/>
+      <c r="AR52" s="78"/>
       <c r="AS52" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT52" s="63"/>
-      <c r="AU52" s="64"/>
-      <c r="AV52" s="59"/>
-      <c r="AW52" s="60"/>
-      <c r="AX52" s="111"/>
-      <c r="AY52" s="112"/>
-      <c r="AZ52" s="59"/>
-      <c r="BA52" s="60"/>
-      <c r="BB52" s="61"/>
-      <c r="BC52" s="62"/>
+      <c r="AT52" s="79"/>
+      <c r="AU52" s="80"/>
+      <c r="AV52" s="75"/>
+      <c r="AW52" s="76"/>
+      <c r="AX52" s="123"/>
+      <c r="AY52" s="124"/>
+      <c r="AZ52" s="75"/>
+      <c r="BA52" s="76"/>
+      <c r="BB52" s="77"/>
+      <c r="BC52" s="78"/>
       <c r="BD52" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE52" s="63"/>
-      <c r="BF52" s="64"/>
-      <c r="BG52" s="59"/>
-      <c r="BH52" s="60"/>
+      <c r="BE52" s="79"/>
+      <c r="BF52" s="80"/>
+      <c r="BG52" s="75"/>
+      <c r="BH52" s="76"/>
     </row>
     <row r="53" spans="2:60">
-      <c r="B53" s="55"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="57"/>
-      <c r="L53" s="57"/>
-      <c r="M53" s="57"/>
-      <c r="N53" s="57"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="91"/>
-      <c r="S53" s="92"/>
-      <c r="T53" s="91"/>
-      <c r="U53" s="92"/>
-      <c r="V53" s="52"/>
-      <c r="W53" s="54"/>
-      <c r="X53" s="52"/>
-      <c r="Y53" s="53"/>
-      <c r="Z53" s="54"/>
-      <c r="AA53" s="52"/>
-      <c r="AB53" s="53"/>
-      <c r="AC53" s="54"/>
-      <c r="AD53" s="52"/>
-      <c r="AE53" s="53"/>
-      <c r="AF53" s="54"/>
-      <c r="AG53" s="52"/>
-      <c r="AH53" s="53"/>
-      <c r="AI53" s="54"/>
-      <c r="AJ53" s="52"/>
-      <c r="AK53" s="53"/>
-      <c r="AL53" s="54"/>
-      <c r="AM53" s="111"/>
-      <c r="AN53" s="112"/>
-      <c r="AO53" s="59"/>
-      <c r="AP53" s="60"/>
-      <c r="AQ53" s="61"/>
-      <c r="AR53" s="62"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="65"/>
+      <c r="L53" s="65"/>
+      <c r="M53" s="65"/>
+      <c r="N53" s="65"/>
+      <c r="O53" s="65"/>
+      <c r="P53" s="65"/>
+      <c r="Q53" s="66"/>
+      <c r="R53" s="67"/>
+      <c r="S53" s="68"/>
+      <c r="T53" s="67"/>
+      <c r="U53" s="68"/>
+      <c r="V53" s="72"/>
+      <c r="W53" s="74"/>
+      <c r="X53" s="72"/>
+      <c r="Y53" s="73"/>
+      <c r="Z53" s="74"/>
+      <c r="AA53" s="72"/>
+      <c r="AB53" s="73"/>
+      <c r="AC53" s="74"/>
+      <c r="AD53" s="72"/>
+      <c r="AE53" s="73"/>
+      <c r="AF53" s="74"/>
+      <c r="AG53" s="72"/>
+      <c r="AH53" s="73"/>
+      <c r="AI53" s="74"/>
+      <c r="AJ53" s="72"/>
+      <c r="AK53" s="73"/>
+      <c r="AL53" s="74"/>
+      <c r="AM53" s="123"/>
+      <c r="AN53" s="124"/>
+      <c r="AO53" s="75"/>
+      <c r="AP53" s="76"/>
+      <c r="AQ53" s="77"/>
+      <c r="AR53" s="78"/>
       <c r="AS53" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT53" s="63"/>
-      <c r="AU53" s="64"/>
-      <c r="AV53" s="59"/>
-      <c r="AW53" s="60"/>
-      <c r="AX53" s="111"/>
-      <c r="AY53" s="112"/>
-      <c r="AZ53" s="59"/>
-      <c r="BA53" s="60"/>
-      <c r="BB53" s="61"/>
-      <c r="BC53" s="62"/>
+      <c r="AT53" s="79"/>
+      <c r="AU53" s="80"/>
+      <c r="AV53" s="75"/>
+      <c r="AW53" s="76"/>
+      <c r="AX53" s="123"/>
+      <c r="AY53" s="124"/>
+      <c r="AZ53" s="75"/>
+      <c r="BA53" s="76"/>
+      <c r="BB53" s="77"/>
+      <c r="BC53" s="78"/>
       <c r="BD53" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE53" s="63"/>
-      <c r="BF53" s="64"/>
-      <c r="BG53" s="59"/>
-      <c r="BH53" s="60"/>
+      <c r="BE53" s="79"/>
+      <c r="BF53" s="80"/>
+      <c r="BG53" s="75"/>
+      <c r="BH53" s="76"/>
     </row>
     <row r="54" spans="2:60">
-      <c r="B54" s="55"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="57"/>
-      <c r="K54" s="57"/>
-      <c r="L54" s="57"/>
-      <c r="M54" s="57"/>
-      <c r="N54" s="57"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="57"/>
-      <c r="Q54" s="58"/>
-      <c r="R54" s="91"/>
-      <c r="S54" s="92"/>
-      <c r="T54" s="91"/>
-      <c r="U54" s="92"/>
-      <c r="V54" s="52"/>
-      <c r="W54" s="54"/>
-      <c r="X54" s="52"/>
-      <c r="Y54" s="53"/>
-      <c r="Z54" s="54"/>
-      <c r="AA54" s="52"/>
-      <c r="AB54" s="53"/>
-      <c r="AC54" s="54"/>
-      <c r="AD54" s="52"/>
-      <c r="AE54" s="53"/>
-      <c r="AF54" s="54"/>
-      <c r="AG54" s="52"/>
-      <c r="AH54" s="53"/>
-      <c r="AI54" s="54"/>
-      <c r="AJ54" s="52"/>
-      <c r="AK54" s="53"/>
-      <c r="AL54" s="54"/>
-      <c r="AM54" s="111"/>
-      <c r="AN54" s="112"/>
-      <c r="AO54" s="59"/>
-      <c r="AP54" s="60"/>
-      <c r="AQ54" s="61"/>
-      <c r="AR54" s="62"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="65"/>
+      <c r="M54" s="65"/>
+      <c r="N54" s="65"/>
+      <c r="O54" s="65"/>
+      <c r="P54" s="65"/>
+      <c r="Q54" s="66"/>
+      <c r="R54" s="67"/>
+      <c r="S54" s="68"/>
+      <c r="T54" s="67"/>
+      <c r="U54" s="68"/>
+      <c r="V54" s="72"/>
+      <c r="W54" s="74"/>
+      <c r="X54" s="72"/>
+      <c r="Y54" s="73"/>
+      <c r="Z54" s="74"/>
+      <c r="AA54" s="72"/>
+      <c r="AB54" s="73"/>
+      <c r="AC54" s="74"/>
+      <c r="AD54" s="72"/>
+      <c r="AE54" s="73"/>
+      <c r="AF54" s="74"/>
+      <c r="AG54" s="72"/>
+      <c r="AH54" s="73"/>
+      <c r="AI54" s="74"/>
+      <c r="AJ54" s="72"/>
+      <c r="AK54" s="73"/>
+      <c r="AL54" s="74"/>
+      <c r="AM54" s="123"/>
+      <c r="AN54" s="124"/>
+      <c r="AO54" s="75"/>
+      <c r="AP54" s="76"/>
+      <c r="AQ54" s="77"/>
+      <c r="AR54" s="78"/>
       <c r="AS54" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT54" s="63"/>
-      <c r="AU54" s="64"/>
-      <c r="AV54" s="59"/>
-      <c r="AW54" s="60"/>
-      <c r="AX54" s="111"/>
-      <c r="AY54" s="112"/>
-      <c r="AZ54" s="59"/>
-      <c r="BA54" s="60"/>
-      <c r="BB54" s="61"/>
-      <c r="BC54" s="62"/>
+      <c r="AT54" s="79"/>
+      <c r="AU54" s="80"/>
+      <c r="AV54" s="75"/>
+      <c r="AW54" s="76"/>
+      <c r="AX54" s="123"/>
+      <c r="AY54" s="124"/>
+      <c r="AZ54" s="75"/>
+      <c r="BA54" s="76"/>
+      <c r="BB54" s="77"/>
+      <c r="BC54" s="78"/>
       <c r="BD54" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE54" s="63"/>
-      <c r="BF54" s="64"/>
-      <c r="BG54" s="59"/>
-      <c r="BH54" s="60"/>
+      <c r="BE54" s="79"/>
+      <c r="BF54" s="80"/>
+      <c r="BG54" s="75"/>
+      <c r="BH54" s="76"/>
     </row>
     <row r="55" spans="2:60" ht="13.95" customHeight="1">
       <c r="B55" s="4" t="s">
@@ -5475,65 +5466,65 @@
       <c r="K55" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L55" s="97"/>
-      <c r="M55" s="97"/>
-      <c r="N55" s="97"/>
-      <c r="O55" s="97"/>
-      <c r="P55" s="97"/>
-      <c r="Q55" s="98"/>
+      <c r="L55" s="110"/>
+      <c r="M55" s="110"/>
+      <c r="N55" s="110"/>
+      <c r="O55" s="110"/>
+      <c r="P55" s="110"/>
+      <c r="Q55" s="111"/>
       <c r="R55" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S55" s="97"/>
-      <c r="T55" s="97"/>
-      <c r="U55" s="97"/>
-      <c r="V55" s="97"/>
-      <c r="W55" s="97"/>
-      <c r="X55" s="98"/>
+      <c r="S55" s="110"/>
+      <c r="T55" s="110"/>
+      <c r="U55" s="110"/>
+      <c r="V55" s="110"/>
+      <c r="W55" s="110"/>
+      <c r="X55" s="111"/>
       <c r="Y55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Z55" s="97"/>
-      <c r="AA55" s="97"/>
-      <c r="AB55" s="97"/>
-      <c r="AC55" s="97"/>
-      <c r="AD55" s="97"/>
-      <c r="AE55" s="98"/>
+      <c r="Z55" s="110"/>
+      <c r="AA55" s="110"/>
+      <c r="AB55" s="110"/>
+      <c r="AC55" s="110"/>
+      <c r="AD55" s="110"/>
+      <c r="AE55" s="111"/>
       <c r="AF55" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AG55" s="97"/>
-      <c r="AH55" s="97"/>
-      <c r="AI55" s="97"/>
-      <c r="AJ55" s="97"/>
-      <c r="AK55" s="97"/>
-      <c r="AL55" s="98"/>
-      <c r="AM55" s="111"/>
-      <c r="AN55" s="112"/>
-      <c r="AO55" s="59"/>
-      <c r="AP55" s="60"/>
-      <c r="AQ55" s="61"/>
-      <c r="AR55" s="62"/>
+      <c r="AG55" s="110"/>
+      <c r="AH55" s="110"/>
+      <c r="AI55" s="110"/>
+      <c r="AJ55" s="110"/>
+      <c r="AK55" s="110"/>
+      <c r="AL55" s="111"/>
+      <c r="AM55" s="123"/>
+      <c r="AN55" s="124"/>
+      <c r="AO55" s="75"/>
+      <c r="AP55" s="76"/>
+      <c r="AQ55" s="77"/>
+      <c r="AR55" s="78"/>
       <c r="AS55" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT55" s="63"/>
-      <c r="AU55" s="64"/>
-      <c r="AV55" s="59"/>
-      <c r="AW55" s="60"/>
-      <c r="AX55" s="111"/>
-      <c r="AY55" s="112"/>
-      <c r="AZ55" s="59"/>
-      <c r="BA55" s="60"/>
-      <c r="BB55" s="61"/>
-      <c r="BC55" s="62"/>
+      <c r="AT55" s="79"/>
+      <c r="AU55" s="80"/>
+      <c r="AV55" s="75"/>
+      <c r="AW55" s="76"/>
+      <c r="AX55" s="123"/>
+      <c r="AY55" s="124"/>
+      <c r="AZ55" s="75"/>
+      <c r="BA55" s="76"/>
+      <c r="BB55" s="77"/>
+      <c r="BC55" s="78"/>
       <c r="BD55" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE55" s="63"/>
-      <c r="BF55" s="64"/>
-      <c r="BG55" s="59"/>
-      <c r="BH55" s="60"/>
+      <c r="BE55" s="79"/>
+      <c r="BF55" s="80"/>
+      <c r="BG55" s="75"/>
+      <c r="BH55" s="76"/>
     </row>
     <row r="56" spans="2:60" ht="6.6" customHeight="1">
       <c r="B56" s="178"/>
@@ -5545,60 +5536,60 @@
       <c r="H56" s="176"/>
       <c r="I56" s="176"/>
       <c r="J56" s="177"/>
-      <c r="K56" s="102"/>
-      <c r="L56" s="103"/>
-      <c r="M56" s="103"/>
-      <c r="N56" s="103"/>
-      <c r="O56" s="103"/>
-      <c r="P56" s="103"/>
-      <c r="Q56" s="104"/>
-      <c r="R56" s="102"/>
-      <c r="S56" s="103"/>
-      <c r="T56" s="103"/>
-      <c r="U56" s="103"/>
-      <c r="V56" s="103"/>
-      <c r="W56" s="103"/>
-      <c r="X56" s="104"/>
-      <c r="Y56" s="102"/>
-      <c r="Z56" s="103"/>
-      <c r="AA56" s="103"/>
-      <c r="AB56" s="103"/>
-      <c r="AC56" s="103"/>
-      <c r="AD56" s="103"/>
-      <c r="AE56" s="104"/>
-      <c r="AF56" s="102"/>
-      <c r="AG56" s="103"/>
-      <c r="AH56" s="103"/>
-      <c r="AI56" s="103"/>
-      <c r="AJ56" s="103"/>
-      <c r="AK56" s="103"/>
-      <c r="AL56" s="104"/>
+      <c r="K56" s="115"/>
+      <c r="L56" s="116"/>
+      <c r="M56" s="116"/>
+      <c r="N56" s="116"/>
+      <c r="O56" s="116"/>
+      <c r="P56" s="116"/>
+      <c r="Q56" s="117"/>
+      <c r="R56" s="115"/>
+      <c r="S56" s="116"/>
+      <c r="T56" s="116"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="116"/>
+      <c r="W56" s="116"/>
+      <c r="X56" s="117"/>
+      <c r="Y56" s="115"/>
+      <c r="Z56" s="116"/>
+      <c r="AA56" s="116"/>
+      <c r="AB56" s="116"/>
+      <c r="AC56" s="116"/>
+      <c r="AD56" s="116"/>
+      <c r="AE56" s="117"/>
+      <c r="AF56" s="115"/>
+      <c r="AG56" s="116"/>
+      <c r="AH56" s="116"/>
+      <c r="AI56" s="116"/>
+      <c r="AJ56" s="116"/>
+      <c r="AK56" s="116"/>
+      <c r="AL56" s="117"/>
       <c r="AM56" s="44"/>
-      <c r="AN56" s="48"/>
-      <c r="AO56" s="144"/>
-      <c r="AP56" s="145"/>
-      <c r="AQ56" s="144"/>
-      <c r="AR56" s="148"/>
-      <c r="AS56" s="142" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT56" s="132"/>
-      <c r="AU56" s="133"/>
-      <c r="AV56" s="136"/>
-      <c r="AW56" s="133"/>
-      <c r="AX56" s="138"/>
-      <c r="AY56" s="139"/>
-      <c r="AZ56" s="136"/>
-      <c r="BA56" s="133"/>
-      <c r="BB56" s="136"/>
-      <c r="BC56" s="132"/>
-      <c r="BD56" s="142" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE56" s="132"/>
-      <c r="BF56" s="133"/>
-      <c r="BG56" s="136"/>
-      <c r="BH56" s="133"/>
+      <c r="AN56" s="69"/>
+      <c r="AO56" s="154"/>
+      <c r="AP56" s="155"/>
+      <c r="AQ56" s="154"/>
+      <c r="AR56" s="158"/>
+      <c r="AS56" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT56" s="142"/>
+      <c r="AU56" s="143"/>
+      <c r="AV56" s="146"/>
+      <c r="AW56" s="143"/>
+      <c r="AX56" s="148"/>
+      <c r="AY56" s="149"/>
+      <c r="AZ56" s="146"/>
+      <c r="BA56" s="143"/>
+      <c r="BB56" s="146"/>
+      <c r="BC56" s="142"/>
+      <c r="BD56" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE56" s="142"/>
+      <c r="BF56" s="143"/>
+      <c r="BG56" s="146"/>
+      <c r="BH56" s="143"/>
     </row>
     <row r="57" spans="2:60" ht="6.6" customHeight="1">
       <c r="B57" s="180"/>
@@ -5610,289 +5601,289 @@
       <c r="H57" s="176"/>
       <c r="I57" s="176"/>
       <c r="J57" s="177"/>
-      <c r="K57" s="99"/>
-      <c r="L57" s="100"/>
-      <c r="M57" s="100"/>
-      <c r="N57" s="100"/>
-      <c r="O57" s="100"/>
-      <c r="P57" s="100"/>
-      <c r="Q57" s="101"/>
-      <c r="R57" s="99"/>
-      <c r="S57" s="100"/>
-      <c r="T57" s="100"/>
-      <c r="U57" s="100"/>
-      <c r="V57" s="100"/>
-      <c r="W57" s="100"/>
-      <c r="X57" s="101"/>
-      <c r="Y57" s="99"/>
-      <c r="Z57" s="100"/>
-      <c r="AA57" s="100"/>
-      <c r="AB57" s="100"/>
-      <c r="AC57" s="100"/>
-      <c r="AD57" s="100"/>
-      <c r="AE57" s="101"/>
-      <c r="AF57" s="99"/>
-      <c r="AG57" s="100"/>
-      <c r="AH57" s="100"/>
-      <c r="AI57" s="100"/>
-      <c r="AJ57" s="100"/>
-      <c r="AK57" s="100"/>
-      <c r="AL57" s="101"/>
+      <c r="K57" s="112"/>
+      <c r="L57" s="113"/>
+      <c r="M57" s="113"/>
+      <c r="N57" s="113"/>
+      <c r="O57" s="113"/>
+      <c r="P57" s="113"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="112"/>
+      <c r="S57" s="113"/>
+      <c r="T57" s="113"/>
+      <c r="U57" s="113"/>
+      <c r="V57" s="113"/>
+      <c r="W57" s="113"/>
+      <c r="X57" s="114"/>
+      <c r="Y57" s="112"/>
+      <c r="Z57" s="113"/>
+      <c r="AA57" s="113"/>
+      <c r="AB57" s="113"/>
+      <c r="AC57" s="113"/>
+      <c r="AD57" s="113"/>
+      <c r="AE57" s="114"/>
+      <c r="AF57" s="112"/>
+      <c r="AG57" s="113"/>
+      <c r="AH57" s="113"/>
+      <c r="AI57" s="113"/>
+      <c r="AJ57" s="113"/>
+      <c r="AK57" s="113"/>
+      <c r="AL57" s="114"/>
       <c r="AM57" s="46"/>
-      <c r="AN57" s="49"/>
-      <c r="AO57" s="146"/>
-      <c r="AP57" s="147"/>
-      <c r="AQ57" s="146"/>
-      <c r="AR57" s="149"/>
-      <c r="AS57" s="143"/>
-      <c r="AT57" s="134"/>
-      <c r="AU57" s="135"/>
-      <c r="AV57" s="137"/>
-      <c r="AW57" s="135"/>
-      <c r="AX57" s="140"/>
-      <c r="AY57" s="141"/>
-      <c r="AZ57" s="137"/>
-      <c r="BA57" s="135"/>
-      <c r="BB57" s="137"/>
-      <c r="BC57" s="134"/>
-      <c r="BD57" s="143"/>
-      <c r="BE57" s="134"/>
-      <c r="BF57" s="135"/>
-      <c r="BG57" s="137"/>
-      <c r="BH57" s="135"/>
+      <c r="AN57" s="70"/>
+      <c r="AO57" s="156"/>
+      <c r="AP57" s="157"/>
+      <c r="AQ57" s="156"/>
+      <c r="AR57" s="159"/>
+      <c r="AS57" s="153"/>
+      <c r="AT57" s="144"/>
+      <c r="AU57" s="145"/>
+      <c r="AV57" s="147"/>
+      <c r="AW57" s="145"/>
+      <c r="AX57" s="150"/>
+      <c r="AY57" s="151"/>
+      <c r="AZ57" s="147"/>
+      <c r="BA57" s="145"/>
+      <c r="BB57" s="147"/>
+      <c r="BC57" s="144"/>
+      <c r="BD57" s="153"/>
+      <c r="BE57" s="144"/>
+      <c r="BF57" s="145"/>
+      <c r="BG57" s="147"/>
+      <c r="BH57" s="145"/>
     </row>
     <row r="58" spans="2:60">
-      <c r="B58" s="65"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="66"/>
-      <c r="G58" s="66"/>
-      <c r="H58" s="66"/>
-      <c r="I58" s="66"/>
-      <c r="J58" s="67"/>
-      <c r="K58" s="71"/>
-      <c r="L58" s="72"/>
-      <c r="M58" s="72"/>
-      <c r="N58" s="72"/>
-      <c r="O58" s="72"/>
-      <c r="P58" s="72"/>
-      <c r="Q58" s="105"/>
-      <c r="R58" s="71"/>
-      <c r="S58" s="72"/>
-      <c r="T58" s="72"/>
-      <c r="U58" s="72"/>
-      <c r="V58" s="72"/>
-      <c r="W58" s="72"/>
-      <c r="X58" s="105"/>
-      <c r="Y58" s="71"/>
-      <c r="Z58" s="72"/>
-      <c r="AA58" s="72"/>
-      <c r="AB58" s="72"/>
-      <c r="AC58" s="72"/>
-      <c r="AD58" s="72"/>
-      <c r="AE58" s="105"/>
-      <c r="AF58" s="71"/>
-      <c r="AG58" s="72"/>
-      <c r="AH58" s="72"/>
-      <c r="AI58" s="72"/>
-      <c r="AJ58" s="72"/>
-      <c r="AK58" s="72"/>
-      <c r="AL58" s="105"/>
-      <c r="AM58" s="111"/>
-      <c r="AN58" s="112"/>
-      <c r="AO58" s="59"/>
-      <c r="AP58" s="60"/>
-      <c r="AQ58" s="61"/>
-      <c r="AR58" s="62"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
+      <c r="I58" s="82"/>
+      <c r="J58" s="83"/>
+      <c r="K58" s="59"/>
+      <c r="L58" s="60"/>
+      <c r="M58" s="60"/>
+      <c r="N58" s="60"/>
+      <c r="O58" s="60"/>
+      <c r="P58" s="60"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="59"/>
+      <c r="S58" s="60"/>
+      <c r="T58" s="60"/>
+      <c r="U58" s="60"/>
+      <c r="V58" s="60"/>
+      <c r="W58" s="60"/>
+      <c r="X58" s="61"/>
+      <c r="Y58" s="59"/>
+      <c r="Z58" s="60"/>
+      <c r="AA58" s="60"/>
+      <c r="AB58" s="60"/>
+      <c r="AC58" s="60"/>
+      <c r="AD58" s="60"/>
+      <c r="AE58" s="61"/>
+      <c r="AF58" s="59"/>
+      <c r="AG58" s="60"/>
+      <c r="AH58" s="60"/>
+      <c r="AI58" s="60"/>
+      <c r="AJ58" s="60"/>
+      <c r="AK58" s="60"/>
+      <c r="AL58" s="61"/>
+      <c r="AM58" s="123"/>
+      <c r="AN58" s="124"/>
+      <c r="AO58" s="75"/>
+      <c r="AP58" s="76"/>
+      <c r="AQ58" s="77"/>
+      <c r="AR58" s="78"/>
       <c r="AS58" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT58" s="63"/>
-      <c r="AU58" s="64"/>
-      <c r="AV58" s="59"/>
-      <c r="AW58" s="60"/>
-      <c r="AX58" s="111"/>
-      <c r="AY58" s="112"/>
-      <c r="AZ58" s="59"/>
-      <c r="BA58" s="60"/>
-      <c r="BB58" s="61"/>
-      <c r="BC58" s="62"/>
+      <c r="AT58" s="79"/>
+      <c r="AU58" s="80"/>
+      <c r="AV58" s="75"/>
+      <c r="AW58" s="76"/>
+      <c r="AX58" s="123"/>
+      <c r="AY58" s="124"/>
+      <c r="AZ58" s="75"/>
+      <c r="BA58" s="76"/>
+      <c r="BB58" s="77"/>
+      <c r="BC58" s="78"/>
       <c r="BD58" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE58" s="63"/>
-      <c r="BF58" s="64"/>
-      <c r="BG58" s="59"/>
-      <c r="BH58" s="60"/>
+      <c r="BE58" s="79"/>
+      <c r="BF58" s="80"/>
+      <c r="BG58" s="75"/>
+      <c r="BH58" s="76"/>
     </row>
     <row r="59" spans="2:60">
-      <c r="B59" s="167" t="s">
+      <c r="B59" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C59" s="168"/>
-      <c r="D59" s="168"/>
-      <c r="E59" s="168"/>
-      <c r="F59" s="168"/>
-      <c r="G59" s="168"/>
-      <c r="H59" s="168"/>
-      <c r="I59" s="168"/>
-      <c r="J59" s="169"/>
-      <c r="K59" s="167" t="s">
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="L59" s="168"/>
-      <c r="M59" s="168"/>
-      <c r="N59" s="168"/>
-      <c r="O59" s="168"/>
-      <c r="P59" s="168"/>
-      <c r="Q59" s="169"/>
-      <c r="R59" s="167" t="s">
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="53"/>
+      <c r="R59" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S59" s="168"/>
-      <c r="T59" s="168"/>
-      <c r="U59" s="168"/>
-      <c r="V59" s="168"/>
-      <c r="W59" s="168"/>
-      <c r="X59" s="169"/>
-      <c r="Y59" s="167" t="s">
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="52"/>
+      <c r="X59" s="53"/>
+      <c r="Y59" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Z59" s="168"/>
-      <c r="AA59" s="168"/>
-      <c r="AB59" s="168"/>
-      <c r="AC59" s="168"/>
-      <c r="AD59" s="168"/>
-      <c r="AE59" s="169"/>
-      <c r="AF59" s="167" t="s">
+      <c r="Z59" s="52"/>
+      <c r="AA59" s="52"/>
+      <c r="AB59" s="52"/>
+      <c r="AC59" s="52"/>
+      <c r="AD59" s="52"/>
+      <c r="AE59" s="53"/>
+      <c r="AF59" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AG59" s="168"/>
-      <c r="AH59" s="168"/>
-      <c r="AI59" s="168"/>
-      <c r="AJ59" s="168"/>
-      <c r="AK59" s="168"/>
-      <c r="AL59" s="169"/>
-      <c r="AM59" s="111"/>
-      <c r="AN59" s="112"/>
-      <c r="AO59" s="59"/>
-      <c r="AP59" s="60"/>
-      <c r="AQ59" s="61"/>
-      <c r="AR59" s="62"/>
+      <c r="AG59" s="52"/>
+      <c r="AH59" s="52"/>
+      <c r="AI59" s="52"/>
+      <c r="AJ59" s="52"/>
+      <c r="AK59" s="52"/>
+      <c r="AL59" s="53"/>
+      <c r="AM59" s="123"/>
+      <c r="AN59" s="124"/>
+      <c r="AO59" s="75"/>
+      <c r="AP59" s="76"/>
+      <c r="AQ59" s="77"/>
+      <c r="AR59" s="78"/>
       <c r="AS59" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT59" s="63"/>
-      <c r="AU59" s="64"/>
-      <c r="AV59" s="59"/>
-      <c r="AW59" s="60"/>
-      <c r="AX59" s="111"/>
-      <c r="AY59" s="112"/>
-      <c r="AZ59" s="59"/>
-      <c r="BA59" s="60"/>
-      <c r="BB59" s="61"/>
-      <c r="BC59" s="62"/>
+      <c r="AT59" s="79"/>
+      <c r="AU59" s="80"/>
+      <c r="AV59" s="75"/>
+      <c r="AW59" s="76"/>
+      <c r="AX59" s="123"/>
+      <c r="AY59" s="124"/>
+      <c r="AZ59" s="75"/>
+      <c r="BA59" s="76"/>
+      <c r="BB59" s="77"/>
+      <c r="BC59" s="78"/>
       <c r="BD59" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE59" s="63"/>
-      <c r="BF59" s="64"/>
-      <c r="BG59" s="59"/>
-      <c r="BH59" s="60"/>
+      <c r="BE59" s="79"/>
+      <c r="BF59" s="80"/>
+      <c r="BG59" s="75"/>
+      <c r="BH59" s="76"/>
     </row>
     <row r="60" spans="2:60">
-      <c r="B60" s="170"/>
-      <c r="C60" s="171"/>
-      <c r="D60" s="171"/>
-      <c r="E60" s="171"/>
-      <c r="F60" s="171"/>
-      <c r="G60" s="171"/>
-      <c r="H60" s="171"/>
-      <c r="I60" s="171"/>
-      <c r="J60" s="172"/>
-      <c r="K60" s="170"/>
-      <c r="L60" s="171"/>
-      <c r="M60" s="171"/>
-      <c r="N60" s="171"/>
-      <c r="O60" s="171"/>
-      <c r="P60" s="171"/>
-      <c r="Q60" s="172"/>
-      <c r="R60" s="170"/>
-      <c r="S60" s="171"/>
-      <c r="T60" s="171"/>
-      <c r="U60" s="171"/>
-      <c r="V60" s="171"/>
-      <c r="W60" s="171"/>
-      <c r="X60" s="172"/>
-      <c r="Y60" s="170"/>
-      <c r="Z60" s="171"/>
-      <c r="AA60" s="171"/>
-      <c r="AB60" s="171"/>
-      <c r="AC60" s="171"/>
-      <c r="AD60" s="171"/>
-      <c r="AE60" s="172"/>
-      <c r="AF60" s="170"/>
-      <c r="AG60" s="171"/>
-      <c r="AH60" s="171"/>
-      <c r="AI60" s="171"/>
-      <c r="AJ60" s="171"/>
-      <c r="AK60" s="171"/>
-      <c r="AL60" s="172"/>
-      <c r="AM60" s="111"/>
-      <c r="AN60" s="112"/>
-      <c r="AO60" s="59"/>
-      <c r="AP60" s="60"/>
-      <c r="AQ60" s="61"/>
-      <c r="AR60" s="62"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="55"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="55"/>
+      <c r="M60" s="55"/>
+      <c r="N60" s="55"/>
+      <c r="O60" s="55"/>
+      <c r="P60" s="55"/>
+      <c r="Q60" s="56"/>
+      <c r="R60" s="54"/>
+      <c r="S60" s="55"/>
+      <c r="T60" s="55"/>
+      <c r="U60" s="55"/>
+      <c r="V60" s="55"/>
+      <c r="W60" s="55"/>
+      <c r="X60" s="56"/>
+      <c r="Y60" s="54"/>
+      <c r="Z60" s="55"/>
+      <c r="AA60" s="55"/>
+      <c r="AB60" s="55"/>
+      <c r="AC60" s="55"/>
+      <c r="AD60" s="55"/>
+      <c r="AE60" s="56"/>
+      <c r="AF60" s="54"/>
+      <c r="AG60" s="55"/>
+      <c r="AH60" s="55"/>
+      <c r="AI60" s="55"/>
+      <c r="AJ60" s="55"/>
+      <c r="AK60" s="55"/>
+      <c r="AL60" s="56"/>
+      <c r="AM60" s="123"/>
+      <c r="AN60" s="124"/>
+      <c r="AO60" s="75"/>
+      <c r="AP60" s="76"/>
+      <c r="AQ60" s="77"/>
+      <c r="AR60" s="78"/>
       <c r="AS60" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT60" s="63"/>
-      <c r="AU60" s="64"/>
-      <c r="AV60" s="59"/>
-      <c r="AW60" s="60"/>
-      <c r="AX60" s="111"/>
-      <c r="AY60" s="112"/>
-      <c r="AZ60" s="59"/>
-      <c r="BA60" s="60"/>
-      <c r="BB60" s="61"/>
-      <c r="BC60" s="62"/>
+      <c r="AT60" s="79"/>
+      <c r="AU60" s="80"/>
+      <c r="AV60" s="75"/>
+      <c r="AW60" s="76"/>
+      <c r="AX60" s="123"/>
+      <c r="AY60" s="124"/>
+      <c r="AZ60" s="75"/>
+      <c r="BA60" s="76"/>
+      <c r="BB60" s="77"/>
+      <c r="BC60" s="78"/>
       <c r="BD60" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE60" s="63"/>
-      <c r="BF60" s="64"/>
-      <c r="BG60" s="59"/>
-      <c r="BH60" s="60"/>
+      <c r="BE60" s="79"/>
+      <c r="BF60" s="80"/>
+      <c r="BG60" s="75"/>
+      <c r="BH60" s="76"/>
     </row>
     <row r="61" spans="2:60">
-      <c r="B61" s="164" t="s">
+      <c r="B61" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C61" s="165"/>
-      <c r="D61" s="165"/>
-      <c r="E61" s="165"/>
-      <c r="F61" s="165"/>
-      <c r="G61" s="165"/>
-      <c r="H61" s="165"/>
-      <c r="I61" s="165"/>
-      <c r="J61" s="165"/>
-      <c r="K61" s="165"/>
-      <c r="L61" s="165"/>
-      <c r="M61" s="166"/>
-      <c r="N61" s="76" t="s">
+      <c r="C61" s="49"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
+      <c r="L61" s="49"/>
+      <c r="M61" s="50"/>
+      <c r="N61" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="O61" s="77"/>
-      <c r="P61" s="73"/>
-      <c r="Q61" s="73"/>
-      <c r="R61" s="82" t="s">
+      <c r="O61" s="92"/>
+      <c r="P61" s="88"/>
+      <c r="Q61" s="88"/>
+      <c r="R61" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="S61" s="83"/>
-      <c r="T61" s="74"/>
-      <c r="U61" s="74"/>
+      <c r="S61" s="98"/>
+      <c r="T61" s="89"/>
+      <c r="U61" s="89"/>
       <c r="V61" s="243"/>
       <c r="W61" s="244"/>
       <c r="X61" s="244"/>
@@ -5910,32 +5901,32 @@
       <c r="AJ61" s="244"/>
       <c r="AK61" s="244"/>
       <c r="AL61" s="245"/>
-      <c r="AM61" s="111"/>
-      <c r="AN61" s="112"/>
-      <c r="AO61" s="59"/>
-      <c r="AP61" s="60"/>
-      <c r="AQ61" s="61"/>
-      <c r="AR61" s="62"/>
+      <c r="AM61" s="123"/>
+      <c r="AN61" s="124"/>
+      <c r="AO61" s="75"/>
+      <c r="AP61" s="76"/>
+      <c r="AQ61" s="77"/>
+      <c r="AR61" s="78"/>
       <c r="AS61" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT61" s="63"/>
-      <c r="AU61" s="64"/>
-      <c r="AV61" s="59"/>
-      <c r="AW61" s="60"/>
-      <c r="AX61" s="111"/>
-      <c r="AY61" s="112"/>
-      <c r="AZ61" s="59"/>
-      <c r="BA61" s="60"/>
-      <c r="BB61" s="61"/>
-      <c r="BC61" s="62"/>
+      <c r="AT61" s="79"/>
+      <c r="AU61" s="80"/>
+      <c r="AV61" s="75"/>
+      <c r="AW61" s="76"/>
+      <c r="AX61" s="123"/>
+      <c r="AY61" s="124"/>
+      <c r="AZ61" s="75"/>
+      <c r="BA61" s="76"/>
+      <c r="BB61" s="77"/>
+      <c r="BC61" s="78"/>
       <c r="BD61" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE61" s="63"/>
-      <c r="BF61" s="64"/>
-      <c r="BG61" s="59"/>
-      <c r="BH61" s="60"/>
+      <c r="BE61" s="79"/>
+      <c r="BF61" s="80"/>
+      <c r="BG61" s="75"/>
+      <c r="BH61" s="76"/>
     </row>
     <row r="62" spans="2:60">
       <c r="B62" s="1" t="s">
@@ -5946,22 +5937,22 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="15"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
-      <c r="J62" s="118"/>
-      <c r="K62" s="86" t="s">
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="L62" s="87"/>
-      <c r="M62" s="87"/>
-      <c r="N62" s="87"/>
-      <c r="O62" s="87"/>
-      <c r="P62" s="87"/>
-      <c r="Q62" s="87"/>
-      <c r="R62" s="84"/>
-      <c r="S62" s="84"/>
-      <c r="T62" s="84"/>
-      <c r="U62" s="85"/>
+      <c r="L62" s="102"/>
+      <c r="M62" s="102"/>
+      <c r="N62" s="102"/>
+      <c r="O62" s="102"/>
+      <c r="P62" s="102"/>
+      <c r="Q62" s="102"/>
+      <c r="R62" s="99"/>
+      <c r="S62" s="99"/>
+      <c r="T62" s="99"/>
+      <c r="U62" s="100"/>
       <c r="V62" s="246"/>
       <c r="W62" s="247"/>
       <c r="X62" s="247"/>
@@ -5979,60 +5970,60 @@
       <c r="AJ62" s="247"/>
       <c r="AK62" s="247"/>
       <c r="AL62" s="248"/>
-      <c r="AM62" s="111"/>
-      <c r="AN62" s="112"/>
-      <c r="AO62" s="59"/>
-      <c r="AP62" s="60"/>
-      <c r="AQ62" s="61"/>
-      <c r="AR62" s="62"/>
+      <c r="AM62" s="123"/>
+      <c r="AN62" s="124"/>
+      <c r="AO62" s="75"/>
+      <c r="AP62" s="76"/>
+      <c r="AQ62" s="77"/>
+      <c r="AR62" s="78"/>
       <c r="AS62" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT62" s="63"/>
-      <c r="AU62" s="64"/>
-      <c r="AV62" s="59"/>
-      <c r="AW62" s="60"/>
-      <c r="AX62" s="111"/>
-      <c r="AY62" s="112"/>
-      <c r="AZ62" s="59"/>
-      <c r="BA62" s="60"/>
-      <c r="BB62" s="61"/>
-      <c r="BC62" s="62"/>
+      <c r="AT62" s="79"/>
+      <c r="AU62" s="80"/>
+      <c r="AV62" s="75"/>
+      <c r="AW62" s="76"/>
+      <c r="AX62" s="123"/>
+      <c r="AY62" s="124"/>
+      <c r="AZ62" s="75"/>
+      <c r="BA62" s="76"/>
+      <c r="BB62" s="77"/>
+      <c r="BC62" s="78"/>
       <c r="BD62" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE62" s="63"/>
-      <c r="BF62" s="64"/>
-      <c r="BG62" s="59"/>
-      <c r="BH62" s="60"/>
+      <c r="BE62" s="79"/>
+      <c r="BF62" s="80"/>
+      <c r="BG62" s="75"/>
+      <c r="BH62" s="76"/>
     </row>
     <row r="63" spans="2:60">
-      <c r="B63" s="164" t="s">
+      <c r="B63" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C63" s="165"/>
-      <c r="D63" s="165"/>
-      <c r="E63" s="165"/>
-      <c r="F63" s="165"/>
-      <c r="G63" s="165"/>
-      <c r="H63" s="165"/>
-      <c r="I63" s="165"/>
-      <c r="J63" s="165"/>
-      <c r="K63" s="165"/>
-      <c r="L63" s="165"/>
-      <c r="M63" s="166"/>
-      <c r="N63" s="78" t="s">
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="50"/>
+      <c r="N63" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="O63" s="79"/>
-      <c r="P63" s="73"/>
-      <c r="Q63" s="73"/>
-      <c r="R63" s="80" t="s">
+      <c r="O63" s="94"/>
+      <c r="P63" s="88"/>
+      <c r="Q63" s="88"/>
+      <c r="R63" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="S63" s="81"/>
-      <c r="T63" s="75"/>
-      <c r="U63" s="75"/>
+      <c r="S63" s="96"/>
+      <c r="T63" s="90"/>
+      <c r="U63" s="90"/>
       <c r="V63" s="246"/>
       <c r="W63" s="247"/>
       <c r="X63" s="247"/>
@@ -6050,60 +6041,60 @@
       <c r="AJ63" s="247"/>
       <c r="AK63" s="247"/>
       <c r="AL63" s="248"/>
-      <c r="AM63" s="111"/>
-      <c r="AN63" s="112"/>
-      <c r="AO63" s="59"/>
-      <c r="AP63" s="60"/>
-      <c r="AQ63" s="61"/>
-      <c r="AR63" s="62"/>
+      <c r="AM63" s="123"/>
+      <c r="AN63" s="124"/>
+      <c r="AO63" s="75"/>
+      <c r="AP63" s="76"/>
+      <c r="AQ63" s="77"/>
+      <c r="AR63" s="78"/>
       <c r="AS63" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="AT63" s="63"/>
-      <c r="AU63" s="64"/>
-      <c r="AV63" s="59"/>
-      <c r="AW63" s="60"/>
-      <c r="AX63" s="111"/>
-      <c r="AY63" s="112"/>
-      <c r="AZ63" s="59"/>
-      <c r="BA63" s="60"/>
-      <c r="BB63" s="61"/>
-      <c r="BC63" s="62"/>
+      <c r="AT63" s="79"/>
+      <c r="AU63" s="80"/>
+      <c r="AV63" s="75"/>
+      <c r="AW63" s="76"/>
+      <c r="AX63" s="123"/>
+      <c r="AY63" s="124"/>
+      <c r="AZ63" s="75"/>
+      <c r="BA63" s="76"/>
+      <c r="BB63" s="77"/>
+      <c r="BC63" s="78"/>
       <c r="BD63" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="BE63" s="63"/>
-      <c r="BF63" s="64"/>
-      <c r="BG63" s="59"/>
-      <c r="BH63" s="60"/>
+      <c r="BE63" s="79"/>
+      <c r="BF63" s="80"/>
+      <c r="BG63" s="75"/>
+      <c r="BH63" s="76"/>
     </row>
     <row r="64" spans="2:60">
-      <c r="B64" s="88" t="s">
+      <c r="B64" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="89"/>
-      <c r="I64" s="89"/>
-      <c r="J64" s="89"/>
-      <c r="K64" s="89"/>
-      <c r="L64" s="89"/>
-      <c r="M64" s="90"/>
-      <c r="N64" s="78" t="s">
+      <c r="C64" s="104"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="104"/>
+      <c r="K64" s="104"/>
+      <c r="L64" s="104"/>
+      <c r="M64" s="105"/>
+      <c r="N64" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="O64" s="79"/>
-      <c r="P64" s="73"/>
-      <c r="Q64" s="73"/>
-      <c r="R64" s="78" t="s">
+      <c r="O64" s="94"/>
+      <c r="P64" s="88"/>
+      <c r="Q64" s="88"/>
+      <c r="R64" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="S64" s="79"/>
-      <c r="T64" s="73"/>
-      <c r="U64" s="73"/>
+      <c r="S64" s="94"/>
+      <c r="T64" s="88"/>
+      <c r="U64" s="88"/>
       <c r="V64" s="256"/>
       <c r="W64" s="255"/>
       <c r="X64" s="255"/>
@@ -6121,63 +6112,63 @@
       <c r="AJ64" s="255"/>
       <c r="AK64" s="255"/>
       <c r="AL64" s="257"/>
-      <c r="AM64" s="160" t="s">
+      <c r="AM64" s="170" t="s">
         <v>44</v>
       </c>
-      <c r="AN64" s="160"/>
-      <c r="AO64" s="160" t="s">
+      <c r="AN64" s="170"/>
+      <c r="AO64" s="170" t="s">
         <v>45</v>
       </c>
-      <c r="AP64" s="160"/>
-      <c r="AQ64" s="160"/>
-      <c r="AR64" s="160"/>
-      <c r="AS64" s="160" t="s">
+      <c r="AP64" s="170"/>
+      <c r="AQ64" s="170"/>
+      <c r="AR64" s="170"/>
+      <c r="AS64" s="170" t="s">
         <v>46</v>
       </c>
-      <c r="AT64" s="160"/>
-      <c r="AU64" s="160"/>
-      <c r="AV64" s="160"/>
-      <c r="AW64" s="160"/>
-      <c r="AX64" s="160" t="s">
+      <c r="AT64" s="170"/>
+      <c r="AU64" s="170"/>
+      <c r="AV64" s="170"/>
+      <c r="AW64" s="170"/>
+      <c r="AX64" s="170" t="s">
         <v>15</v>
       </c>
-      <c r="AY64" s="160"/>
-      <c r="AZ64" s="160" t="s">
+      <c r="AY64" s="170"/>
+      <c r="AZ64" s="170" t="s">
         <v>45</v>
       </c>
-      <c r="BA64" s="160"/>
-      <c r="BB64" s="160"/>
-      <c r="BC64" s="160"/>
-      <c r="BD64" s="160" t="s">
+      <c r="BA64" s="170"/>
+      <c r="BB64" s="170"/>
+      <c r="BC64" s="170"/>
+      <c r="BD64" s="170" t="s">
         <v>46</v>
       </c>
-      <c r="BE64" s="160"/>
-      <c r="BF64" s="160"/>
-      <c r="BG64" s="160"/>
-      <c r="BH64" s="160"/>
+      <c r="BE64" s="170"/>
+      <c r="BF64" s="170"/>
+      <c r="BG64" s="170"/>
+      <c r="BH64" s="170"/>
     </row>
     <row r="65" spans="2:60" ht="14.4" customHeight="1">
-      <c r="B65" s="68"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="69"/>
-      <c r="J65" s="69"/>
-      <c r="K65" s="69"/>
-      <c r="L65" s="69"/>
-      <c r="M65" s="69"/>
-      <c r="N65" s="69"/>
-      <c r="O65" s="69"/>
-      <c r="P65" s="69"/>
-      <c r="Q65" s="69"/>
-      <c r="R65" s="69"/>
-      <c r="S65" s="69"/>
-      <c r="T65" s="69"/>
-      <c r="U65" s="70"/>
-      <c r="V65" s="163" t="s">
+      <c r="B65" s="84"/>
+      <c r="C65" s="85"/>
+      <c r="D65" s="85"/>
+      <c r="E65" s="85"/>
+      <c r="F65" s="85"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="85"/>
+      <c r="I65" s="85"/>
+      <c r="J65" s="85"/>
+      <c r="K65" s="85"/>
+      <c r="L65" s="85"/>
+      <c r="M65" s="85"/>
+      <c r="N65" s="85"/>
+      <c r="O65" s="85"/>
+      <c r="P65" s="85"/>
+      <c r="Q65" s="85"/>
+      <c r="R65" s="85"/>
+      <c r="S65" s="85"/>
+      <c r="T65" s="85"/>
+      <c r="U65" s="86"/>
+      <c r="V65" s="87" t="s">
         <v>36</v>
       </c>
       <c r="W65" s="28"/>
@@ -6196,10 +6187,10 @@
       <c r="AJ65" s="28"/>
       <c r="AK65" s="28"/>
       <c r="AL65" s="29"/>
-      <c r="AM65" s="159" t="s">
+      <c r="AM65" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="AN65" s="159"/>
+      <c r="AN65" s="169"/>
       <c r="AO65" s="208"/>
       <c r="AP65" s="208"/>
       <c r="AQ65" s="208"/>
@@ -6209,10 +6200,10 @@
       <c r="AU65" s="208"/>
       <c r="AV65" s="208"/>
       <c r="AW65" s="208"/>
-      <c r="AX65" s="159" t="s">
+      <c r="AX65" s="169" t="s">
         <v>47</v>
       </c>
-      <c r="AY65" s="159"/>
+      <c r="AY65" s="169"/>
       <c r="AZ65" s="208"/>
       <c r="BA65" s="208"/>
       <c r="BB65" s="208"/>
@@ -6258,19 +6249,19 @@
       <c r="AA66" s="26"/>
       <c r="AB66" s="26"/>
       <c r="AC66" s="27"/>
-      <c r="AD66" s="258" t="s">
+      <c r="AD66" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="AE66" s="259"/>
-      <c r="AF66" s="259"/>
-      <c r="AG66" s="259"/>
+      <c r="AE66" s="37"/>
+      <c r="AF66" s="37"/>
+      <c r="AG66" s="38"/>
       <c r="AH66" s="28"/>
       <c r="AI66" s="28"/>
       <c r="AJ66" s="28"/>
       <c r="AK66" s="28"/>
       <c r="AL66" s="29"/>
-      <c r="AM66" s="159"/>
-      <c r="AN66" s="159"/>
+      <c r="AM66" s="169"/>
+      <c r="AN66" s="169"/>
       <c r="AO66" s="208"/>
       <c r="AP66" s="208"/>
       <c r="AQ66" s="208"/>
@@ -6280,8 +6271,8 @@
       <c r="AU66" s="208"/>
       <c r="AV66" s="208"/>
       <c r="AW66" s="208"/>
-      <c r="AX66" s="159"/>
-      <c r="AY66" s="159"/>
+      <c r="AX66" s="169"/>
+      <c r="AY66" s="169"/>
       <c r="AZ66" s="208"/>
       <c r="BA66" s="208"/>
       <c r="BB66" s="208"/>
@@ -6325,12 +6316,12 @@
       <c r="AA67" s="26"/>
       <c r="AB67" s="26"/>
       <c r="AC67" s="27"/>
-      <c r="AD67" s="260" t="s">
+      <c r="AD67" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="AE67" s="261"/>
-      <c r="AF67" s="261"/>
-      <c r="AG67" s="261"/>
+      <c r="AE67" s="37"/>
+      <c r="AF67" s="37"/>
+      <c r="AG67" s="38"/>
       <c r="AH67" s="28"/>
       <c r="AI67" s="28"/>
       <c r="AJ67" s="28"/>
@@ -6347,19 +6338,19 @@
       <c r="AS67" s="22"/>
       <c r="AT67" s="22"/>
       <c r="AU67" s="23"/>
-      <c r="AV67" s="50"/>
-      <c r="AW67" s="50"/>
-      <c r="AX67" s="50"/>
-      <c r="AY67" s="50"/>
-      <c r="AZ67" s="50"/>
-      <c r="BA67" s="50"/>
-      <c r="BB67" s="50"/>
-      <c r="BC67" s="50"/>
-      <c r="BD67" s="50"/>
-      <c r="BE67" s="50"/>
-      <c r="BF67" s="50"/>
-      <c r="BG67" s="50"/>
-      <c r="BH67" s="51"/>
+      <c r="AV67" s="71"/>
+      <c r="AW67" s="71"/>
+      <c r="AX67" s="71"/>
+      <c r="AY67" s="71"/>
+      <c r="AZ67" s="71"/>
+      <c r="BA67" s="71"/>
+      <c r="BB67" s="71"/>
+      <c r="BC67" s="71"/>
+      <c r="BD67" s="71"/>
+      <c r="BE67" s="71"/>
+      <c r="BF67" s="71"/>
+      <c r="BG67" s="71"/>
+      <c r="BH67" s="63"/>
     </row>
     <row r="68" spans="2:60" ht="13.8">
       <c r="B68" s="32"/>
@@ -6394,12 +6385,12 @@
       <c r="AA68" s="26"/>
       <c r="AB68" s="26"/>
       <c r="AC68" s="27"/>
-      <c r="AD68" s="260" t="s">
+      <c r="AD68" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="AE68" s="261"/>
-      <c r="AF68" s="261"/>
-      <c r="AG68" s="261"/>
+      <c r="AE68" s="37"/>
+      <c r="AF68" s="37"/>
+      <c r="AG68" s="38"/>
       <c r="AH68" s="28"/>
       <c r="AI68" s="28"/>
       <c r="AJ68" s="28"/>
@@ -6469,18 +6460,18 @@
       <c r="AA69" s="26"/>
       <c r="AB69" s="26"/>
       <c r="AC69" s="27"/>
-      <c r="AD69" s="260" t="s">
+      <c r="AD69" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="AE69" s="261"/>
-      <c r="AF69" s="261"/>
-      <c r="AG69" s="261"/>
+      <c r="AE69" s="259"/>
+      <c r="AF69" s="259"/>
+      <c r="AG69" s="260"/>
       <c r="AH69" s="28"/>
       <c r="AI69" s="28"/>
       <c r="AJ69" s="28"/>
       <c r="AK69" s="28"/>
       <c r="AL69" s="29"/>
-      <c r="AM69" s="163" t="s">
+      <c r="AM69" s="87" t="s">
         <v>48</v>
       </c>
       <c r="AN69" s="28"/>
@@ -6538,12 +6529,12 @@
       <c r="AA70" s="26"/>
       <c r="AB70" s="26"/>
       <c r="AC70" s="27"/>
-      <c r="AD70" s="262" t="s">
+      <c r="AD70" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="AE70" s="263"/>
-      <c r="AF70" s="263"/>
-      <c r="AG70" s="263"/>
+      <c r="AE70" s="259"/>
+      <c r="AF70" s="259"/>
+      <c r="AG70" s="260"/>
       <c r="AH70" s="28"/>
       <c r="AI70" s="28"/>
       <c r="AJ70" s="28"/>
@@ -6572,7 +6563,7 @@
       <c r="BE70" s="45"/>
       <c r="BF70" s="45"/>
       <c r="BG70" s="45"/>
-      <c r="BH70" s="48"/>
+      <c r="BH70" s="69"/>
     </row>
     <row r="71" spans="2:60">
       <c r="B71" s="34"/>
@@ -6612,7 +6603,7 @@
       </c>
       <c r="AE71" s="37"/>
       <c r="AF71" s="37"/>
-      <c r="AG71" s="37"/>
+      <c r="AG71" s="38"/>
       <c r="AH71" s="28"/>
       <c r="AI71" s="28"/>
       <c r="AJ71" s="28"/>
@@ -6639,73 +6630,75 @@
       <c r="BE71" s="47"/>
       <c r="BF71" s="47"/>
       <c r="BG71" s="47"/>
-      <c r="BH71" s="49"/>
+      <c r="BH71" s="70"/>
     </row>
     <row r="72" spans="2:60">
-      <c r="B72" s="86" t="s">
+      <c r="B72" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="87"/>
-      <c r="D72" s="87"/>
-      <c r="E72" s="87"/>
-      <c r="F72" s="87"/>
-      <c r="G72" s="87"/>
-      <c r="H72" s="87"/>
-      <c r="I72" s="87"/>
-      <c r="J72" s="87"/>
-      <c r="K72" s="87"/>
-      <c r="L72" s="87"/>
-      <c r="M72" s="87"/>
-      <c r="N72" s="87"/>
-      <c r="O72" s="87"/>
-      <c r="P72" s="87"/>
-      <c r="Q72" s="87"/>
-      <c r="R72" s="87"/>
-      <c r="S72" s="87"/>
-      <c r="T72" s="87"/>
-      <c r="U72" s="87"/>
-      <c r="V72" s="87"/>
-      <c r="W72" s="87"/>
-      <c r="X72" s="87"/>
-      <c r="Y72" s="87"/>
-      <c r="Z72" s="87"/>
-      <c r="AA72" s="87"/>
-      <c r="AB72" s="87"/>
-      <c r="AC72" s="87"/>
-      <c r="AD72" s="87"/>
-      <c r="AE72" s="87"/>
-      <c r="AF72" s="87"/>
-      <c r="AG72" s="87"/>
-      <c r="AH72" s="87"/>
-      <c r="AI72" s="87"/>
-      <c r="AJ72" s="87"/>
-      <c r="AK72" s="87"/>
-      <c r="AL72" s="87"/>
-      <c r="AM72" s="87"/>
-      <c r="AN72" s="87"/>
-      <c r="AO72" s="87"/>
-      <c r="AP72" s="87"/>
-      <c r="AQ72" s="87"/>
-      <c r="AR72" s="87"/>
-      <c r="AS72" s="87"/>
-      <c r="AT72" s="87"/>
-      <c r="AU72" s="87"/>
-      <c r="AV72" s="87"/>
-      <c r="AW72" s="87"/>
-      <c r="AX72" s="87"/>
-      <c r="AY72" s="87"/>
-      <c r="AZ72" s="87"/>
-      <c r="BA72" s="87"/>
-      <c r="BB72" s="87"/>
-      <c r="BC72" s="87"/>
-      <c r="BD72" s="87"/>
-      <c r="BE72" s="87"/>
-      <c r="BF72" s="87"/>
-      <c r="BG72" s="87"/>
-      <c r="BH72" s="154"/>
+      <c r="C72" s="102"/>
+      <c r="D72" s="102"/>
+      <c r="E72" s="102"/>
+      <c r="F72" s="102"/>
+      <c r="G72" s="102"/>
+      <c r="H72" s="102"/>
+      <c r="I72" s="102"/>
+      <c r="J72" s="102"/>
+      <c r="K72" s="102"/>
+      <c r="L72" s="102"/>
+      <c r="M72" s="102"/>
+      <c r="N72" s="102"/>
+      <c r="O72" s="102"/>
+      <c r="P72" s="102"/>
+      <c r="Q72" s="102"/>
+      <c r="R72" s="102"/>
+      <c r="S72" s="102"/>
+      <c r="T72" s="102"/>
+      <c r="U72" s="102"/>
+      <c r="V72" s="102"/>
+      <c r="W72" s="102"/>
+      <c r="X72" s="102"/>
+      <c r="Y72" s="102"/>
+      <c r="Z72" s="102"/>
+      <c r="AA72" s="102"/>
+      <c r="AB72" s="102"/>
+      <c r="AC72" s="102"/>
+      <c r="AD72" s="102"/>
+      <c r="AE72" s="102"/>
+      <c r="AF72" s="102"/>
+      <c r="AG72" s="102"/>
+      <c r="AH72" s="102"/>
+      <c r="AI72" s="102"/>
+      <c r="AJ72" s="102"/>
+      <c r="AK72" s="102"/>
+      <c r="AL72" s="102"/>
+      <c r="AM72" s="102"/>
+      <c r="AN72" s="102"/>
+      <c r="AO72" s="102"/>
+      <c r="AP72" s="102"/>
+      <c r="AQ72" s="102"/>
+      <c r="AR72" s="102"/>
+      <c r="AS72" s="102"/>
+      <c r="AT72" s="102"/>
+      <c r="AU72" s="102"/>
+      <c r="AV72" s="102"/>
+      <c r="AW72" s="102"/>
+      <c r="AX72" s="102"/>
+      <c r="AY72" s="102"/>
+      <c r="AZ72" s="102"/>
+      <c r="BA72" s="102"/>
+      <c r="BB72" s="102"/>
+      <c r="BC72" s="102"/>
+      <c r="BD72" s="102"/>
+      <c r="BE72" s="102"/>
+      <c r="BF72" s="102"/>
+      <c r="BG72" s="102"/>
+      <c r="BH72" s="164"/>
     </row>
   </sheetData>
-  <mergeCells count="1081">
+  <mergeCells count="1080">
+    <mergeCell ref="V63:AE64"/>
+    <mergeCell ref="AF63:AL64"/>
     <mergeCell ref="AZ65:BC66"/>
     <mergeCell ref="BD65:BH66"/>
     <mergeCell ref="AS64:AW64"/>
@@ -6725,9 +6718,6 @@
     <mergeCell ref="J70:S70"/>
     <mergeCell ref="AQ12:AU14"/>
     <mergeCell ref="AV12:AW14"/>
-    <mergeCell ref="AA63:AG64"/>
-    <mergeCell ref="V63:Z64"/>
-    <mergeCell ref="AH63:AL64"/>
     <mergeCell ref="AX12:AY14"/>
     <mergeCell ref="BG15:BH15"/>
     <mergeCell ref="AM16:AN16"/>
@@ -6738,15 +6728,6 @@
     <mergeCell ref="AD68:AG68"/>
     <mergeCell ref="AD69:AG69"/>
     <mergeCell ref="AD70:AG70"/>
-    <mergeCell ref="AX65:AY66"/>
-    <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="AD12:AF12"/>
-    <mergeCell ref="AD17:AF17"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="AJ17:AL17"/>
-    <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="AJ22:AL22"/>
-    <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="V61:AL61"/>
     <mergeCell ref="V62:AL62"/>
     <mergeCell ref="AM61:AN61"/>
@@ -6770,8 +6751,6 @@
     <mergeCell ref="AD37:AF37"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="V10:W10"/>
     <mergeCell ref="AW68:BC68"/>
     <mergeCell ref="BD68:BE68"/>
     <mergeCell ref="BG68:BH68"/>
@@ -6802,6 +6781,8 @@
     <mergeCell ref="BB23:BC23"/>
     <mergeCell ref="AH6:AL6"/>
     <mergeCell ref="T10:U10"/>
+    <mergeCell ref="AX65:AY66"/>
+    <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="BD64:BH64"/>
     <mergeCell ref="AH7:AL7"/>
     <mergeCell ref="AR68:AS68"/>
@@ -6834,10 +6815,6 @@
     <mergeCell ref="AJ12:AL12"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="V9:AL9"/>
-    <mergeCell ref="AA11:AC11"/>
-    <mergeCell ref="AD11:AF11"/>
     <mergeCell ref="AT62:AU62"/>
     <mergeCell ref="AQ63:AR63"/>
     <mergeCell ref="B1:P2"/>
@@ -6866,10 +6843,10 @@
     <mergeCell ref="V4:Z4"/>
     <mergeCell ref="BE15:BF15"/>
     <mergeCell ref="BB16:BC16"/>
-    <mergeCell ref="BB19:BC19"/>
-    <mergeCell ref="BE19:BF19"/>
-    <mergeCell ref="BB20:BC20"/>
-    <mergeCell ref="BE20:BF20"/>
+    <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="AD12:AF12"/>
+    <mergeCell ref="AD17:AF17"/>
     <mergeCell ref="BB21:BC21"/>
     <mergeCell ref="BE21:BF21"/>
     <mergeCell ref="R11:S11"/>
@@ -6896,10 +6873,12 @@
     <mergeCell ref="R20:S20"/>
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="T11:U11"/>
-    <mergeCell ref="V5:Z5"/>
-    <mergeCell ref="V6:Z6"/>
-    <mergeCell ref="V7:Z7"/>
-    <mergeCell ref="V8:Z8"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="BG10:BH10"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="AJ24:AL24"/>
@@ -6928,25 +6907,10 @@
     <mergeCell ref="V15:W15"/>
     <mergeCell ref="V16:W16"/>
     <mergeCell ref="AG15:AI15"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="D23:Q23"/>
-    <mergeCell ref="D24:Q24"/>
-    <mergeCell ref="D25:Q25"/>
-    <mergeCell ref="D26:Q26"/>
-    <mergeCell ref="D27:Q27"/>
-    <mergeCell ref="D28:Q28"/>
-    <mergeCell ref="D17:Q17"/>
-    <mergeCell ref="D18:Q18"/>
-    <mergeCell ref="D19:Q19"/>
-    <mergeCell ref="D20:Q20"/>
-    <mergeCell ref="D21:Q21"/>
-    <mergeCell ref="D22:Q22"/>
-    <mergeCell ref="D11:Q11"/>
-    <mergeCell ref="D12:Q12"/>
-    <mergeCell ref="D13:Q13"/>
-    <mergeCell ref="D14:Q14"/>
-    <mergeCell ref="D15:Q15"/>
+    <mergeCell ref="BB19:BC19"/>
+    <mergeCell ref="BE19:BF19"/>
+    <mergeCell ref="BB20:BC20"/>
+    <mergeCell ref="BE20:BF20"/>
     <mergeCell ref="D16:Q16"/>
     <mergeCell ref="V28:W28"/>
     <mergeCell ref="T23:U23"/>
@@ -6960,15 +6924,15 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AD25:AF25"/>
-    <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J31"/>
-    <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="AD20:AF20"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="V5:Z5"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="V7:Z7"/>
+    <mergeCell ref="V8:Z8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="V9:AL9"/>
+    <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="AA19:AC19"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -6984,17 +6948,23 @@
     <mergeCell ref="V24:W24"/>
     <mergeCell ref="AA26:AC26"/>
     <mergeCell ref="AD26:AF26"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="AA17:AC17"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="D23:Q23"/>
+    <mergeCell ref="D24:Q24"/>
+    <mergeCell ref="D25:Q25"/>
+    <mergeCell ref="D26:Q26"/>
+    <mergeCell ref="D17:Q17"/>
+    <mergeCell ref="D18:Q18"/>
+    <mergeCell ref="D19:Q19"/>
+    <mergeCell ref="D20:Q20"/>
+    <mergeCell ref="D21:Q21"/>
+    <mergeCell ref="D22:Q22"/>
+    <mergeCell ref="D11:Q11"/>
+    <mergeCell ref="D12:Q12"/>
+    <mergeCell ref="D13:Q13"/>
+    <mergeCell ref="D14:Q14"/>
+    <mergeCell ref="D15:Q15"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
@@ -7005,6 +6975,16 @@
     <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="X25:Z25"/>
     <mergeCell ref="AA25:AC25"/>
+    <mergeCell ref="Y32:Z32"/>
+    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="AD25:AF25"/>
+    <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J31"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="D27:Q27"/>
+    <mergeCell ref="D28:Q28"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D37:Q37"/>
     <mergeCell ref="R37:S37"/>
@@ -7109,10 +7089,6 @@
     <mergeCell ref="AD42:AF42"/>
     <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="AJ42:AL42"/>
-    <mergeCell ref="AA46:AC46"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AG46:AI46"/>
-    <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="D43:Q43"/>
     <mergeCell ref="R43:S43"/>
@@ -7196,6 +7172,7 @@
     <mergeCell ref="X51:Z51"/>
     <mergeCell ref="AA51:AC51"/>
     <mergeCell ref="AD51:AF51"/>
+    <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="AV16:AW16"/>
     <mergeCell ref="AX16:AY16"/>
     <mergeCell ref="BG16:BH16"/>
@@ -7505,6 +7482,10 @@
     <mergeCell ref="BE49:BF49"/>
     <mergeCell ref="AZ48:BA48"/>
     <mergeCell ref="AZ49:BA49"/>
+    <mergeCell ref="BB53:BC53"/>
+    <mergeCell ref="BE53:BF53"/>
+    <mergeCell ref="AZ52:BA52"/>
+    <mergeCell ref="AZ53:BA53"/>
     <mergeCell ref="BG50:BH50"/>
     <mergeCell ref="AM51:AN51"/>
     <mergeCell ref="AO51:AP51"/>
@@ -7525,26 +7506,6 @@
     <mergeCell ref="BE51:BF51"/>
     <mergeCell ref="AZ50:BA50"/>
     <mergeCell ref="AZ51:BA51"/>
-    <mergeCell ref="BG52:BH52"/>
-    <mergeCell ref="AM53:AN53"/>
-    <mergeCell ref="AO53:AP53"/>
-    <mergeCell ref="AV53:AW53"/>
-    <mergeCell ref="AX53:AY53"/>
-    <mergeCell ref="BG53:BH53"/>
-    <mergeCell ref="AM52:AN52"/>
-    <mergeCell ref="AO52:AP52"/>
-    <mergeCell ref="AV52:AW52"/>
-    <mergeCell ref="AX52:AY52"/>
-    <mergeCell ref="AQ52:AR52"/>
-    <mergeCell ref="AT52:AU52"/>
-    <mergeCell ref="AQ53:AR53"/>
-    <mergeCell ref="AT53:AU53"/>
-    <mergeCell ref="BB52:BC52"/>
-    <mergeCell ref="BE52:BF52"/>
-    <mergeCell ref="BB53:BC53"/>
-    <mergeCell ref="BE53:BF53"/>
-    <mergeCell ref="AZ52:BA52"/>
-    <mergeCell ref="AZ53:BA53"/>
     <mergeCell ref="B72:BH72"/>
     <mergeCell ref="AA8:AB8"/>
     <mergeCell ref="AC8:AF8"/>
@@ -7577,7 +7538,6 @@
     <mergeCell ref="AO54:AP54"/>
     <mergeCell ref="AV54:AW54"/>
     <mergeCell ref="AX54:AY54"/>
-    <mergeCell ref="AM4:BH5"/>
     <mergeCell ref="AR1:AY1"/>
     <mergeCell ref="AZ1:BH1"/>
     <mergeCell ref="AR2:BH2"/>
@@ -7609,6 +7569,51 @@
     <mergeCell ref="AM58:AN58"/>
     <mergeCell ref="AO58:AP58"/>
     <mergeCell ref="AX58:AY58"/>
+    <mergeCell ref="BG52:BH52"/>
+    <mergeCell ref="BE59:BF59"/>
+    <mergeCell ref="AZ59:BA59"/>
+    <mergeCell ref="AQ58:AR58"/>
+    <mergeCell ref="AT58:AU58"/>
+    <mergeCell ref="BB58:BC58"/>
+    <mergeCell ref="AG29:AL29"/>
+    <mergeCell ref="AF31:AL31"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AD54:AF54"/>
+    <mergeCell ref="AG54:AI54"/>
+    <mergeCell ref="AJ54:AL54"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AF32:AH32"/>
+    <mergeCell ref="AD28:AF28"/>
+    <mergeCell ref="AG28:AI28"/>
+    <mergeCell ref="AM4:BH5"/>
+    <mergeCell ref="AM53:AN53"/>
+    <mergeCell ref="AO53:AP53"/>
+    <mergeCell ref="AV53:AW53"/>
+    <mergeCell ref="AX53:AY53"/>
+    <mergeCell ref="BG53:BH53"/>
+    <mergeCell ref="AM52:AN52"/>
+    <mergeCell ref="AO52:AP52"/>
+    <mergeCell ref="AV52:AW52"/>
+    <mergeCell ref="AX52:AY52"/>
+    <mergeCell ref="AQ52:AR52"/>
+    <mergeCell ref="AT52:AU52"/>
+    <mergeCell ref="AQ53:AR53"/>
+    <mergeCell ref="AT53:AU53"/>
+    <mergeCell ref="BB52:BC52"/>
+    <mergeCell ref="BE52:BF52"/>
+    <mergeCell ref="AM28:AN28"/>
+    <mergeCell ref="AO28:AP28"/>
+    <mergeCell ref="AV28:AW28"/>
+    <mergeCell ref="AX28:AY28"/>
+    <mergeCell ref="AM25:AN25"/>
+    <mergeCell ref="AO25:AP25"/>
+    <mergeCell ref="AV25:AW25"/>
+    <mergeCell ref="AX25:AY25"/>
+    <mergeCell ref="AQ25:AR25"/>
+    <mergeCell ref="AT25:AU25"/>
+    <mergeCell ref="AT18:AU18"/>
+    <mergeCell ref="AI32:AJ32"/>
     <mergeCell ref="AK32:AL32"/>
     <mergeCell ref="AG52:AI52"/>
     <mergeCell ref="AJ52:AL52"/>
@@ -7625,25 +7630,8 @@
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="AJ28:AL28"/>
-    <mergeCell ref="BE59:BF59"/>
-    <mergeCell ref="AZ59:BA59"/>
-    <mergeCell ref="AQ58:AR58"/>
-    <mergeCell ref="AT58:AU58"/>
-    <mergeCell ref="BB58:BC58"/>
-    <mergeCell ref="AG29:AL29"/>
-    <mergeCell ref="AF31:AL31"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AG54:AI54"/>
-    <mergeCell ref="AJ54:AL54"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AF32:AH32"/>
-    <mergeCell ref="AD28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="AG46:AI46"/>
+    <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AV59:AW59"/>
     <mergeCell ref="AX59:AY59"/>
     <mergeCell ref="AQ59:AR59"/>
@@ -7661,18 +7649,53 @@
     <mergeCell ref="AD52:AF52"/>
     <mergeCell ref="AQ55:AR55"/>
     <mergeCell ref="AT55:AU55"/>
-    <mergeCell ref="AM28:AN28"/>
-    <mergeCell ref="AO28:AP28"/>
-    <mergeCell ref="AV28:AW28"/>
-    <mergeCell ref="AX28:AY28"/>
-    <mergeCell ref="AM25:AN25"/>
-    <mergeCell ref="AO25:AP25"/>
-    <mergeCell ref="AV25:AW25"/>
-    <mergeCell ref="AX25:AY25"/>
-    <mergeCell ref="AQ25:AR25"/>
-    <mergeCell ref="AT25:AU25"/>
-    <mergeCell ref="AT18:AU18"/>
-    <mergeCell ref="AI32:AJ32"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="X49:Z49"/>
+    <mergeCell ref="AA49:AC49"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AA48:AC48"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="AA46:AC46"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="AA17:AC17"/>
+    <mergeCell ref="AD20:AF20"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="R62:U62"/>
+    <mergeCell ref="K62:Q62"/>
+    <mergeCell ref="B64:M64"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:Q53"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T54:U54"/>
     <mergeCell ref="AG8:AH8"/>
     <mergeCell ref="AI8:AL8"/>
     <mergeCell ref="L55:Q55"/>
@@ -7690,45 +7713,6 @@
     <mergeCell ref="K56:Q56"/>
     <mergeCell ref="R56:X56"/>
     <mergeCell ref="D51:Q51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="V49:W49"/>
-    <mergeCell ref="X49:Z49"/>
-    <mergeCell ref="AA49:AC49"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AA48:AC48"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="AJ51:AL51"/>
-    <mergeCell ref="AA32:AC32"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="T64:U64"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="R62:U62"/>
-    <mergeCell ref="K62:Q62"/>
-    <mergeCell ref="B64:M64"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T54:U54"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="D52:Q52"/>
     <mergeCell ref="R52:S52"/>
@@ -7761,6 +7745,14 @@
     <mergeCell ref="D66:H66"/>
     <mergeCell ref="D67:H67"/>
     <mergeCell ref="D68:H68"/>
+    <mergeCell ref="X71:AC71"/>
+    <mergeCell ref="AH71:AL71"/>
+    <mergeCell ref="B66:C71"/>
+    <mergeCell ref="D71:H71"/>
+    <mergeCell ref="J71:S71"/>
+    <mergeCell ref="T71:W71"/>
+    <mergeCell ref="AM70:AQ71"/>
+    <mergeCell ref="AD71:AG71"/>
     <mergeCell ref="D69:H69"/>
     <mergeCell ref="D70:H70"/>
     <mergeCell ref="B63:M63"/>
@@ -7779,14 +7771,12 @@
     <mergeCell ref="AH69:AL69"/>
     <mergeCell ref="X70:AC70"/>
     <mergeCell ref="AH70:AL70"/>
-    <mergeCell ref="X71:AC71"/>
-    <mergeCell ref="AH71:AL71"/>
-    <mergeCell ref="B66:C71"/>
-    <mergeCell ref="D71:H71"/>
-    <mergeCell ref="J71:S71"/>
-    <mergeCell ref="T71:W71"/>
-    <mergeCell ref="AM70:AQ71"/>
-    <mergeCell ref="AD71:AG71"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="T63:U63"/>
+    <mergeCell ref="T64:U64"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="9.3503937007874127E-3" right="0.19685039370078741" top="0.31496062992125984" bottom="0" header="0" footer="0"/>

--- a/app/templates/protocol_template_2.xlsx
+++ b/app/templates/protocol_template_2.xlsx
@@ -16,7 +16,7 @@
     <sheet name="protokół" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">protokół!$A$1:$BH$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">protokół!$A$1:$BH$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1820,7 +1820,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067EC097-671F-4825-B7F3-5CC1B353F4A8}">
   <sheetPr codeName="Arkusz1"/>
-  <dimension ref="B1:BN72"/>
+  <dimension ref="B1:BN68"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -2543,7 +2543,7 @@
       <c r="BG10" s="188"/>
       <c r="BH10" s="189"/>
     </row>
-    <row r="11" spans="2:62">
+    <row r="11" spans="2:62" ht="14.85" customHeight="1">
       <c r="B11" s="123"/>
       <c r="C11" s="124"/>
       <c r="D11" s="64"/>
@@ -2609,7 +2609,7 @@
       <c r="BH11" s="189"/>
       <c r="BJ11" s="11"/>
     </row>
-    <row r="12" spans="2:62">
+    <row r="12" spans="2:62" ht="14.85" customHeight="1">
       <c r="B12" s="62"/>
       <c r="C12" s="63"/>
       <c r="D12" s="64"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="BH12" s="232"/>
     </row>
-    <row r="13" spans="2:62">
+    <row r="13" spans="2:62" ht="14.85" customHeight="1">
       <c r="B13" s="62"/>
       <c r="C13" s="63"/>
       <c r="D13" s="64"/>
@@ -2747,7 +2747,7 @@
       <c r="BG13" s="233"/>
       <c r="BH13" s="234"/>
     </row>
-    <row r="14" spans="2:62">
+    <row r="14" spans="2:62" ht="14.85" customHeight="1">
       <c r="B14" s="62"/>
       <c r="C14" s="63"/>
       <c r="D14" s="64"/>
@@ -2808,7 +2808,7 @@
       <c r="BG14" s="235"/>
       <c r="BH14" s="236"/>
     </row>
-    <row r="15" spans="2:62">
+    <row r="15" spans="2:62" ht="14.85" customHeight="1">
       <c r="B15" s="62"/>
       <c r="C15" s="63"/>
       <c r="D15" s="64"/>
@@ -2873,7 +2873,7 @@
       <c r="BG15" s="75"/>
       <c r="BH15" s="76"/>
     </row>
-    <row r="16" spans="2:62">
+    <row r="16" spans="2:62" ht="14.85" customHeight="1">
       <c r="B16" s="62"/>
       <c r="C16" s="63"/>
       <c r="D16" s="64"/>
@@ -2938,7 +2938,7 @@
       <c r="BG16" s="125"/>
       <c r="BH16" s="76"/>
     </row>
-    <row r="17" spans="2:60">
+    <row r="17" spans="2:60" ht="14.85" customHeight="1">
       <c r="B17" s="62"/>
       <c r="C17" s="63"/>
       <c r="D17" s="64"/>
@@ -3003,7 +3003,7 @@
       <c r="BG17" s="75"/>
       <c r="BH17" s="76"/>
     </row>
-    <row r="18" spans="2:60">
+    <row r="18" spans="2:60" ht="14.85" customHeight="1">
       <c r="B18" s="62"/>
       <c r="C18" s="63"/>
       <c r="D18" s="64"/>
@@ -3068,7 +3068,7 @@
       <c r="BG18" s="75"/>
       <c r="BH18" s="76"/>
     </row>
-    <row r="19" spans="2:60">
+    <row r="19" spans="2:60" ht="14.85" customHeight="1">
       <c r="B19" s="62"/>
       <c r="C19" s="63"/>
       <c r="D19" s="64"/>
@@ -3133,7 +3133,7 @@
       <c r="BG19" s="75"/>
       <c r="BH19" s="76"/>
     </row>
-    <row r="20" spans="2:60">
+    <row r="20" spans="2:60" ht="14.85" customHeight="1">
       <c r="B20" s="62"/>
       <c r="C20" s="63"/>
       <c r="D20" s="64"/>
@@ -3198,7 +3198,7 @@
       <c r="BG20" s="75"/>
       <c r="BH20" s="76"/>
     </row>
-    <row r="21" spans="2:60">
+    <row r="21" spans="2:60" ht="14.85" customHeight="1">
       <c r="B21" s="62"/>
       <c r="C21" s="63"/>
       <c r="D21" s="64"/>
@@ -3263,7 +3263,7 @@
       <c r="BG21" s="75"/>
       <c r="BH21" s="76"/>
     </row>
-    <row r="22" spans="2:60">
+    <row r="22" spans="2:60" ht="14.85" customHeight="1">
       <c r="B22" s="62"/>
       <c r="C22" s="63"/>
       <c r="D22" s="64"/>
@@ -3328,7 +3328,7 @@
       <c r="BG22" s="75"/>
       <c r="BH22" s="76"/>
     </row>
-    <row r="23" spans="2:60">
+    <row r="23" spans="2:60" ht="14.85" customHeight="1">
       <c r="B23" s="62"/>
       <c r="C23" s="63"/>
       <c r="D23" s="64"/>
@@ -3393,7 +3393,7 @@
       <c r="BG23" s="75"/>
       <c r="BH23" s="76"/>
     </row>
-    <row r="24" spans="2:60">
+    <row r="24" spans="2:60" ht="14.85" customHeight="1">
       <c r="B24" s="62"/>
       <c r="C24" s="63"/>
       <c r="D24" s="64"/>
@@ -3458,7 +3458,7 @@
       <c r="BG24" s="75"/>
       <c r="BH24" s="76"/>
     </row>
-    <row r="25" spans="2:60">
+    <row r="25" spans="2:60" ht="14.85" customHeight="1">
       <c r="B25" s="62"/>
       <c r="C25" s="63"/>
       <c r="D25" s="64"/>
@@ -3523,7 +3523,7 @@
       <c r="BG25" s="75"/>
       <c r="BH25" s="76"/>
     </row>
-    <row r="26" spans="2:60">
+    <row r="26" spans="2:60" ht="14.85" customHeight="1">
       <c r="B26" s="62"/>
       <c r="C26" s="63"/>
       <c r="D26" s="64"/>
@@ -3588,44 +3588,54 @@
       <c r="BG26" s="75"/>
       <c r="BH26" s="76"/>
     </row>
-    <row r="27" spans="2:60">
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="65"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="119"/>
-      <c r="T27" s="118"/>
-      <c r="U27" s="119"/>
-      <c r="V27" s="120"/>
-      <c r="W27" s="122"/>
-      <c r="X27" s="120"/>
-      <c r="Y27" s="121"/>
-      <c r="Z27" s="122"/>
-      <c r="AA27" s="120"/>
-      <c r="AB27" s="121"/>
-      <c r="AC27" s="122"/>
-      <c r="AD27" s="120"/>
-      <c r="AE27" s="121"/>
-      <c r="AF27" s="122"/>
-      <c r="AG27" s="120"/>
-      <c r="AH27" s="121"/>
-      <c r="AI27" s="122"/>
-      <c r="AJ27" s="120"/>
-      <c r="AK27" s="121"/>
-      <c r="AL27" s="122"/>
+    <row r="27" spans="2:60" ht="13.2" customHeight="1">
+      <c r="B27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="173"/>
+      <c r="D27" s="173"/>
+      <c r="E27" s="173"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" s="129"/>
+      <c r="M27" s="129"/>
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+      <c r="P27" s="129"/>
+      <c r="Q27" s="130"/>
+      <c r="R27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S27" s="110"/>
+      <c r="T27" s="110"/>
+      <c r="U27" s="110"/>
+      <c r="V27" s="110"/>
+      <c r="W27" s="110"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z27" s="110"/>
+      <c r="AA27" s="110"/>
+      <c r="AB27" s="110"/>
+      <c r="AC27" s="110"/>
+      <c r="AD27" s="110"/>
+      <c r="AE27" s="111"/>
+      <c r="AF27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG27" s="129"/>
+      <c r="AH27" s="129"/>
+      <c r="AI27" s="129"/>
+      <c r="AJ27" s="129"/>
+      <c r="AK27" s="129"/>
+      <c r="AL27" s="130"/>
       <c r="AM27" s="62"/>
       <c r="AN27" s="124"/>
       <c r="AO27" s="125"/>
@@ -3653,310 +3663,310 @@
       <c r="BG27" s="75"/>
       <c r="BH27" s="76"/>
     </row>
-    <row r="28" spans="2:60">
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="65"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="119"/>
-      <c r="T28" s="118"/>
-      <c r="U28" s="119"/>
-      <c r="V28" s="120"/>
-      <c r="W28" s="122"/>
-      <c r="X28" s="120"/>
-      <c r="Y28" s="121"/>
-      <c r="Z28" s="122"/>
-      <c r="AA28" s="120"/>
-      <c r="AB28" s="121"/>
-      <c r="AC28" s="122"/>
-      <c r="AD28" s="120"/>
-      <c r="AE28" s="121"/>
-      <c r="AF28" s="122"/>
-      <c r="AG28" s="120"/>
-      <c r="AH28" s="121"/>
-      <c r="AI28" s="122"/>
-      <c r="AJ28" s="120"/>
-      <c r="AK28" s="121"/>
-      <c r="AL28" s="122"/>
-      <c r="AM28" s="62"/>
-      <c r="AN28" s="124"/>
-      <c r="AO28" s="125"/>
-      <c r="AP28" s="76"/>
-      <c r="AQ28" s="126"/>
-      <c r="AR28" s="78"/>
-      <c r="AS28" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT28" s="79"/>
-      <c r="AU28" s="80"/>
-      <c r="AV28" s="75"/>
-      <c r="AW28" s="76"/>
-      <c r="AX28" s="123"/>
-      <c r="AY28" s="124"/>
-      <c r="AZ28" s="75"/>
-      <c r="BA28" s="76"/>
-      <c r="BB28" s="77"/>
-      <c r="BC28" s="78"/>
-      <c r="BD28" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE28" s="79"/>
-      <c r="BF28" s="80"/>
-      <c r="BG28" s="75"/>
-      <c r="BH28" s="76"/>
+    <row r="28" spans="2:60" ht="6.6" customHeight="1">
+      <c r="B28" s="178"/>
+      <c r="C28" s="179"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="176"/>
+      <c r="H28" s="176"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="177"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="117"/>
+      <c r="R28" s="115"/>
+      <c r="S28" s="116"/>
+      <c r="T28" s="116"/>
+      <c r="U28" s="116"/>
+      <c r="V28" s="116"/>
+      <c r="W28" s="116"/>
+      <c r="X28" s="117"/>
+      <c r="Y28" s="115"/>
+      <c r="Z28" s="116"/>
+      <c r="AA28" s="116"/>
+      <c r="AB28" s="116"/>
+      <c r="AC28" s="116"/>
+      <c r="AD28" s="116"/>
+      <c r="AE28" s="117"/>
+      <c r="AF28" s="115"/>
+      <c r="AG28" s="116"/>
+      <c r="AH28" s="116"/>
+      <c r="AI28" s="116"/>
+      <c r="AJ28" s="116"/>
+      <c r="AK28" s="116"/>
+      <c r="AL28" s="117"/>
+      <c r="AM28" s="44"/>
+      <c r="AN28" s="69"/>
+      <c r="AO28" s="154"/>
+      <c r="AP28" s="155"/>
+      <c r="AQ28" s="154"/>
+      <c r="AR28" s="158"/>
+      <c r="AS28" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT28" s="142"/>
+      <c r="AU28" s="143"/>
+      <c r="AV28" s="146"/>
+      <c r="AW28" s="143"/>
+      <c r="AX28" s="148"/>
+      <c r="AY28" s="149"/>
+      <c r="AZ28" s="146"/>
+      <c r="BA28" s="143"/>
+      <c r="BB28" s="146"/>
+      <c r="BC28" s="142"/>
+      <c r="BD28" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE28" s="142"/>
+      <c r="BF28" s="143"/>
+      <c r="BG28" s="146"/>
+      <c r="BH28" s="143"/>
     </row>
-    <row r="29" spans="2:60" ht="13.2" customHeight="1">
-      <c r="B29" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="175"/>
-      <c r="K29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" s="129"/>
-      <c r="M29" s="129"/>
-      <c r="N29" s="129"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="129"/>
-      <c r="Q29" s="130"/>
-      <c r="R29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="S29" s="110"/>
-      <c r="T29" s="110"/>
-      <c r="U29" s="110"/>
-      <c r="V29" s="110"/>
-      <c r="W29" s="110"/>
-      <c r="X29" s="111"/>
-      <c r="Y29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="110"/>
-      <c r="AB29" s="110"/>
-      <c r="AC29" s="110"/>
-      <c r="AD29" s="110"/>
-      <c r="AE29" s="111"/>
-      <c r="AF29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG29" s="129"/>
-      <c r="AH29" s="129"/>
-      <c r="AI29" s="129"/>
-      <c r="AJ29" s="129"/>
-      <c r="AK29" s="129"/>
-      <c r="AL29" s="130"/>
-      <c r="AM29" s="62"/>
-      <c r="AN29" s="124"/>
-      <c r="AO29" s="125"/>
-      <c r="AP29" s="76"/>
-      <c r="AQ29" s="126"/>
-      <c r="AR29" s="78"/>
-      <c r="AS29" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT29" s="79"/>
-      <c r="AU29" s="80"/>
-      <c r="AV29" s="75"/>
-      <c r="AW29" s="76"/>
-      <c r="AX29" s="123"/>
-      <c r="AY29" s="124"/>
-      <c r="AZ29" s="75"/>
-      <c r="BA29" s="76"/>
-      <c r="BB29" s="77"/>
-      <c r="BC29" s="78"/>
-      <c r="BD29" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE29" s="79"/>
-      <c r="BF29" s="80"/>
-      <c r="BG29" s="75"/>
-      <c r="BH29" s="76"/>
+    <row r="29" spans="2:60" ht="6.6" customHeight="1">
+      <c r="B29" s="180"/>
+      <c r="C29" s="181"/>
+      <c r="D29" s="181"/>
+      <c r="E29" s="181"/>
+      <c r="F29" s="181"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="176"/>
+      <c r="I29" s="176"/>
+      <c r="J29" s="177"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="113"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="112"/>
+      <c r="S29" s="113"/>
+      <c r="T29" s="113"/>
+      <c r="U29" s="113"/>
+      <c r="V29" s="113"/>
+      <c r="W29" s="113"/>
+      <c r="X29" s="114"/>
+      <c r="Y29" s="112"/>
+      <c r="Z29" s="113"/>
+      <c r="AA29" s="113"/>
+      <c r="AB29" s="113"/>
+      <c r="AC29" s="113"/>
+      <c r="AD29" s="113"/>
+      <c r="AE29" s="114"/>
+      <c r="AF29" s="112"/>
+      <c r="AG29" s="113"/>
+      <c r="AH29" s="113"/>
+      <c r="AI29" s="113"/>
+      <c r="AJ29" s="113"/>
+      <c r="AK29" s="113"/>
+      <c r="AL29" s="114"/>
+      <c r="AM29" s="46"/>
+      <c r="AN29" s="70"/>
+      <c r="AO29" s="156"/>
+      <c r="AP29" s="157"/>
+      <c r="AQ29" s="156"/>
+      <c r="AR29" s="159"/>
+      <c r="AS29" s="153"/>
+      <c r="AT29" s="144"/>
+      <c r="AU29" s="145"/>
+      <c r="AV29" s="147"/>
+      <c r="AW29" s="145"/>
+      <c r="AX29" s="150"/>
+      <c r="AY29" s="151"/>
+      <c r="AZ29" s="147"/>
+      <c r="BA29" s="145"/>
+      <c r="BB29" s="147"/>
+      <c r="BC29" s="144"/>
+      <c r="BD29" s="153"/>
+      <c r="BE29" s="144"/>
+      <c r="BF29" s="145"/>
+      <c r="BG29" s="147"/>
+      <c r="BH29" s="145"/>
     </row>
-    <row r="30" spans="2:60" ht="6.6" customHeight="1">
-      <c r="B30" s="178"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="176"/>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="115"/>
-      <c r="L30" s="116"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="116"/>
-      <c r="O30" s="116"/>
-      <c r="P30" s="116"/>
-      <c r="Q30" s="117"/>
-      <c r="R30" s="115"/>
-      <c r="S30" s="116"/>
-      <c r="T30" s="116"/>
-      <c r="U30" s="116"/>
-      <c r="V30" s="116"/>
-      <c r="W30" s="116"/>
-      <c r="X30" s="117"/>
-      <c r="Y30" s="115"/>
-      <c r="Z30" s="116"/>
-      <c r="AA30" s="116"/>
-      <c r="AB30" s="116"/>
-      <c r="AC30" s="116"/>
-      <c r="AD30" s="116"/>
-      <c r="AE30" s="117"/>
-      <c r="AF30" s="115"/>
-      <c r="AG30" s="116"/>
-      <c r="AH30" s="116"/>
-      <c r="AI30" s="116"/>
-      <c r="AJ30" s="116"/>
-      <c r="AK30" s="116"/>
-      <c r="AL30" s="117"/>
-      <c r="AM30" s="44"/>
-      <c r="AN30" s="69"/>
-      <c r="AO30" s="154"/>
-      <c r="AP30" s="155"/>
-      <c r="AQ30" s="154"/>
-      <c r="AR30" s="158"/>
-      <c r="AS30" s="152" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT30" s="142"/>
-      <c r="AU30" s="143"/>
-      <c r="AV30" s="146"/>
-      <c r="AW30" s="143"/>
-      <c r="AX30" s="148"/>
-      <c r="AY30" s="149"/>
-      <c r="AZ30" s="146"/>
-      <c r="BA30" s="143"/>
-      <c r="BB30" s="146"/>
-      <c r="BC30" s="142"/>
-      <c r="BD30" s="152" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE30" s="142"/>
-      <c r="BF30" s="143"/>
-      <c r="BG30" s="146"/>
-      <c r="BH30" s="143"/>
+    <row r="30" spans="2:60">
+      <c r="B30" s="81"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="61"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="60"/>
+      <c r="AB30" s="60"/>
+      <c r="AC30" s="60"/>
+      <c r="AD30" s="60"/>
+      <c r="AE30" s="61"/>
+      <c r="AF30" s="59"/>
+      <c r="AG30" s="60"/>
+      <c r="AH30" s="60"/>
+      <c r="AI30" s="60"/>
+      <c r="AJ30" s="60"/>
+      <c r="AK30" s="60"/>
+      <c r="AL30" s="61"/>
+      <c r="AM30" s="123"/>
+      <c r="AN30" s="124"/>
+      <c r="AO30" s="75"/>
+      <c r="AP30" s="76"/>
+      <c r="AQ30" s="77"/>
+      <c r="AR30" s="78"/>
+      <c r="AS30" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="79"/>
+      <c r="AU30" s="80"/>
+      <c r="AV30" s="75"/>
+      <c r="AW30" s="76"/>
+      <c r="AX30" s="123"/>
+      <c r="AY30" s="124"/>
+      <c r="AZ30" s="75"/>
+      <c r="BA30" s="76"/>
+      <c r="BB30" s="77"/>
+      <c r="BC30" s="78"/>
+      <c r="BD30" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE30" s="79"/>
+      <c r="BF30" s="80"/>
+      <c r="BG30" s="75"/>
+      <c r="BH30" s="76"/>
     </row>
-    <row r="31" spans="2:60" ht="6.6" customHeight="1">
-      <c r="B31" s="180"/>
-      <c r="C31" s="181"/>
-      <c r="D31" s="181"/>
-      <c r="E31" s="181"/>
-      <c r="F31" s="181"/>
-      <c r="G31" s="176"/>
-      <c r="H31" s="176"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="113"/>
-      <c r="Q31" s="114"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="113"/>
-      <c r="T31" s="113"/>
-      <c r="U31" s="113"/>
-      <c r="V31" s="113"/>
-      <c r="W31" s="113"/>
-      <c r="X31" s="114"/>
-      <c r="Y31" s="112"/>
-      <c r="Z31" s="113"/>
-      <c r="AA31" s="113"/>
-      <c r="AB31" s="113"/>
-      <c r="AC31" s="113"/>
-      <c r="AD31" s="113"/>
-      <c r="AE31" s="114"/>
-      <c r="AF31" s="112"/>
-      <c r="AG31" s="113"/>
-      <c r="AH31" s="113"/>
-      <c r="AI31" s="113"/>
-      <c r="AJ31" s="113"/>
-      <c r="AK31" s="113"/>
-      <c r="AL31" s="114"/>
-      <c r="AM31" s="46"/>
-      <c r="AN31" s="70"/>
-      <c r="AO31" s="156"/>
-      <c r="AP31" s="157"/>
-      <c r="AQ31" s="156"/>
-      <c r="AR31" s="159"/>
-      <c r="AS31" s="153"/>
-      <c r="AT31" s="144"/>
-      <c r="AU31" s="145"/>
-      <c r="AV31" s="147"/>
-      <c r="AW31" s="145"/>
-      <c r="AX31" s="150"/>
-      <c r="AY31" s="151"/>
-      <c r="AZ31" s="147"/>
-      <c r="BA31" s="145"/>
-      <c r="BB31" s="147"/>
-      <c r="BC31" s="144"/>
-      <c r="BD31" s="153"/>
-      <c r="BE31" s="144"/>
-      <c r="BF31" s="145"/>
-      <c r="BG31" s="147"/>
-      <c r="BH31" s="145"/>
+    <row r="31" spans="2:60">
+      <c r="B31" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" s="52"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="52"/>
+      <c r="X31" s="53"/>
+      <c r="Y31" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z31" s="52"/>
+      <c r="AA31" s="52"/>
+      <c r="AB31" s="52"/>
+      <c r="AC31" s="52"/>
+      <c r="AD31" s="52"/>
+      <c r="AE31" s="53"/>
+      <c r="AF31" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG31" s="52"/>
+      <c r="AH31" s="52"/>
+      <c r="AI31" s="52"/>
+      <c r="AJ31" s="52"/>
+      <c r="AK31" s="52"/>
+      <c r="AL31" s="53"/>
+      <c r="AM31" s="123"/>
+      <c r="AN31" s="124"/>
+      <c r="AO31" s="75"/>
+      <c r="AP31" s="76"/>
+      <c r="AQ31" s="77"/>
+      <c r="AR31" s="78"/>
+      <c r="AS31" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT31" s="79"/>
+      <c r="AU31" s="80"/>
+      <c r="AV31" s="75"/>
+      <c r="AW31" s="76"/>
+      <c r="AX31" s="123"/>
+      <c r="AY31" s="124"/>
+      <c r="AZ31" s="75"/>
+      <c r="BA31" s="76"/>
+      <c r="BB31" s="77"/>
+      <c r="BC31" s="78"/>
+      <c r="BD31" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE31" s="79"/>
+      <c r="BF31" s="80"/>
+      <c r="BG31" s="75"/>
+      <c r="BH31" s="76"/>
     </row>
     <row r="32" spans="2:60">
-      <c r="B32" s="81"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="60"/>
-      <c r="O32" s="60"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="59"/>
-      <c r="S32" s="60"/>
-      <c r="T32" s="60"/>
-      <c r="U32" s="60"/>
-      <c r="V32" s="60"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="61"/>
-      <c r="Y32" s="59"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="60"/>
-      <c r="AB32" s="60"/>
-      <c r="AC32" s="60"/>
-      <c r="AD32" s="60"/>
-      <c r="AE32" s="61"/>
-      <c r="AF32" s="59"/>
-      <c r="AG32" s="60"/>
-      <c r="AH32" s="60"/>
-      <c r="AI32" s="60"/>
-      <c r="AJ32" s="60"/>
-      <c r="AK32" s="60"/>
-      <c r="AL32" s="61"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="56"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="55"/>
+      <c r="T32" s="55"/>
+      <c r="U32" s="55"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="55"/>
+      <c r="X32" s="56"/>
+      <c r="Y32" s="54"/>
+      <c r="Z32" s="55"/>
+      <c r="AA32" s="55"/>
+      <c r="AB32" s="55"/>
+      <c r="AC32" s="55"/>
+      <c r="AD32" s="55"/>
+      <c r="AE32" s="56"/>
+      <c r="AF32" s="54"/>
+      <c r="AG32" s="55"/>
+      <c r="AH32" s="55"/>
+      <c r="AI32" s="55"/>
+      <c r="AJ32" s="55"/>
+      <c r="AK32" s="55"/>
+      <c r="AL32" s="56"/>
       <c r="AM32" s="123"/>
       <c r="AN32" s="124"/>
       <c r="AO32" s="75"/>
@@ -3985,53 +3995,50 @@
       <c r="BH32" s="76"/>
     </row>
     <row r="33" spans="2:60">
-      <c r="B33" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="52"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="52"/>
-      <c r="O33" s="52"/>
-      <c r="P33" s="52"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="S33" s="52"/>
-      <c r="T33" s="52"/>
-      <c r="U33" s="52"/>
-      <c r="V33" s="52"/>
-      <c r="W33" s="52"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z33" s="52"/>
-      <c r="AA33" s="52"/>
-      <c r="AB33" s="52"/>
-      <c r="AC33" s="52"/>
-      <c r="AD33" s="52"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG33" s="52"/>
-      <c r="AH33" s="52"/>
-      <c r="AI33" s="52"/>
-      <c r="AJ33" s="52"/>
-      <c r="AK33" s="52"/>
-      <c r="AL33" s="53"/>
+      <c r="B33" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="171">
+        <f>D7</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="171"/>
+      <c r="G33" s="171"/>
+      <c r="H33" s="171"/>
+      <c r="I33" s="171"/>
+      <c r="J33" s="171"/>
+      <c r="K33" s="171"/>
+      <c r="L33" s="171"/>
+      <c r="M33" s="171"/>
+      <c r="N33" s="171"/>
+      <c r="O33" s="171"/>
+      <c r="P33" s="171"/>
+      <c r="Q33" s="171"/>
+      <c r="R33" s="171"/>
+      <c r="S33" s="171"/>
+      <c r="T33" s="171"/>
+      <c r="U33" s="172"/>
+      <c r="V33" s="128" t="s">
+        <v>19</v>
+      </c>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="57"/>
+      <c r="AJ33" s="57"/>
+      <c r="AK33" s="57"/>
+      <c r="AL33" s="58"/>
       <c r="AM33" s="123"/>
       <c r="AN33" s="124"/>
       <c r="AO33" s="75"/>
@@ -4060,43 +4067,63 @@
       <c r="BH33" s="76"/>
     </row>
     <row r="34" spans="2:60">
-      <c r="B34" s="54"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="55"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="54"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="55"/>
-      <c r="N34" s="55"/>
-      <c r="O34" s="55"/>
-      <c r="P34" s="55"/>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="54"/>
-      <c r="S34" s="55"/>
-      <c r="T34" s="55"/>
-      <c r="U34" s="55"/>
-      <c r="V34" s="55"/>
-      <c r="W34" s="55"/>
-      <c r="X34" s="56"/>
-      <c r="Y34" s="54"/>
-      <c r="Z34" s="55"/>
-      <c r="AA34" s="55"/>
-      <c r="AB34" s="55"/>
-      <c r="AC34" s="55"/>
-      <c r="AD34" s="55"/>
-      <c r="AE34" s="56"/>
-      <c r="AF34" s="54"/>
-      <c r="AG34" s="55"/>
-      <c r="AH34" s="55"/>
-      <c r="AI34" s="55"/>
-      <c r="AJ34" s="55"/>
-      <c r="AK34" s="55"/>
-      <c r="AL34" s="56"/>
+      <c r="B34" s="128" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="58"/>
+      <c r="D34" s="128" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="S34" s="58"/>
+      <c r="T34" s="128" t="s">
+        <v>15</v>
+      </c>
+      <c r="U34" s="58"/>
+      <c r="V34" s="128" t="s">
+        <v>16</v>
+      </c>
+      <c r="W34" s="58"/>
+      <c r="X34" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y34" s="57"/>
+      <c r="Z34" s="58"/>
+      <c r="AA34" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB34" s="57"/>
+      <c r="AC34" s="58"/>
+      <c r="AD34" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="58"/>
+      <c r="AG34" s="128" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH34" s="57"/>
+      <c r="AI34" s="58"/>
+      <c r="AJ34" s="128" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK34" s="57"/>
+      <c r="AL34" s="58"/>
       <c r="AM34" s="123"/>
       <c r="AN34" s="124"/>
       <c r="AO34" s="75"/>
@@ -4124,51 +4151,44 @@
       <c r="BG34" s="75"/>
       <c r="BH34" s="76"/>
     </row>
-    <row r="35" spans="2:60">
-      <c r="B35" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="171">
-        <f>D7</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="171"/>
-      <c r="I35" s="171"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="171"/>
-      <c r="M35" s="171"/>
-      <c r="N35" s="171"/>
-      <c r="O35" s="171"/>
-      <c r="P35" s="171"/>
-      <c r="Q35" s="171"/>
-      <c r="R35" s="171"/>
-      <c r="S35" s="171"/>
-      <c r="T35" s="171"/>
-      <c r="U35" s="172"/>
-      <c r="V35" s="128" t="s">
-        <v>19</v>
-      </c>
-      <c r="W35" s="57"/>
-      <c r="X35" s="57"/>
-      <c r="Y35" s="57"/>
-      <c r="Z35" s="57"/>
-      <c r="AA35" s="57"/>
-      <c r="AB35" s="57"/>
-      <c r="AC35" s="57"/>
-      <c r="AD35" s="57"/>
-      <c r="AE35" s="57"/>
-      <c r="AF35" s="57"/>
-      <c r="AG35" s="57"/>
-      <c r="AH35" s="57"/>
-      <c r="AI35" s="57"/>
-      <c r="AJ35" s="57"/>
-      <c r="AK35" s="57"/>
-      <c r="AL35" s="58"/>
+    <row r="35" spans="2:60" ht="14.85" customHeight="1">
+      <c r="B35" s="62"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="66"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="68"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="72"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="72"/>
+      <c r="Y35" s="73"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="72"/>
+      <c r="AB35" s="73"/>
+      <c r="AC35" s="74"/>
+      <c r="AD35" s="72"/>
+      <c r="AE35" s="73"/>
+      <c r="AF35" s="74"/>
+      <c r="AG35" s="72"/>
+      <c r="AH35" s="73"/>
+      <c r="AI35" s="74"/>
+      <c r="AJ35" s="72"/>
+      <c r="AK35" s="73"/>
+      <c r="AL35" s="74"/>
       <c r="AM35" s="123"/>
       <c r="AN35" s="124"/>
       <c r="AO35" s="75"/>
@@ -4196,64 +4216,44 @@
       <c r="BG35" s="75"/>
       <c r="BH35" s="76"/>
     </row>
-    <row r="36" spans="2:60">
-      <c r="B36" s="128" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="128" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="57"/>
-      <c r="N36" s="57"/>
-      <c r="O36" s="57"/>
-      <c r="P36" s="57"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="S36" s="58"/>
-      <c r="T36" s="128" t="s">
-        <v>15</v>
-      </c>
-      <c r="U36" s="58"/>
-      <c r="V36" s="128" t="s">
-        <v>16</v>
-      </c>
-      <c r="W36" s="58"/>
-      <c r="X36" s="128" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y36" s="57"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="128" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB36" s="57"/>
-      <c r="AC36" s="58"/>
-      <c r="AD36" s="128" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE36" s="57"/>
-      <c r="AF36" s="58"/>
-      <c r="AG36" s="128" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH36" s="57"/>
-      <c r="AI36" s="58"/>
-      <c r="AJ36" s="128" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK36" s="57"/>
-      <c r="AL36" s="58"/>
+    <row r="36" spans="2:60" ht="14.85" customHeight="1">
+      <c r="B36" s="62"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="66"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="68"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="68"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="74"/>
+      <c r="X36" s="72"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="72"/>
+      <c r="AB36" s="73"/>
+      <c r="AC36" s="74"/>
+      <c r="AD36" s="72"/>
+      <c r="AE36" s="73"/>
+      <c r="AF36" s="74"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="73"/>
+      <c r="AI36" s="74"/>
+      <c r="AJ36" s="72"/>
+      <c r="AK36" s="73"/>
+      <c r="AL36" s="74"/>
       <c r="AM36" s="123"/>
       <c r="AN36" s="124"/>
       <c r="AO36" s="75"/>
@@ -4281,7 +4281,7 @@
       <c r="BG36" s="75"/>
       <c r="BH36" s="76"/>
     </row>
-    <row r="37" spans="2:60">
+    <row r="37" spans="2:60" ht="14.85" customHeight="1">
       <c r="B37" s="62"/>
       <c r="C37" s="63"/>
       <c r="D37" s="64"/>
@@ -4346,7 +4346,7 @@
       <c r="BG37" s="75"/>
       <c r="BH37" s="76"/>
     </row>
-    <row r="38" spans="2:60">
+    <row r="38" spans="2:60" ht="14.85" customHeight="1">
       <c r="B38" s="62"/>
       <c r="C38" s="63"/>
       <c r="D38" s="64"/>
@@ -4411,7 +4411,7 @@
       <c r="BG38" s="75"/>
       <c r="BH38" s="76"/>
     </row>
-    <row r="39" spans="2:60">
+    <row r="39" spans="2:60" ht="14.85" customHeight="1">
       <c r="B39" s="62"/>
       <c r="C39" s="63"/>
       <c r="D39" s="64"/>
@@ -4476,7 +4476,7 @@
       <c r="BG39" s="75"/>
       <c r="BH39" s="76"/>
     </row>
-    <row r="40" spans="2:60">
+    <row r="40" spans="2:60" ht="14.85" customHeight="1">
       <c r="B40" s="62"/>
       <c r="C40" s="63"/>
       <c r="D40" s="64"/>
@@ -4541,7 +4541,7 @@
       <c r="BG40" s="75"/>
       <c r="BH40" s="76"/>
     </row>
-    <row r="41" spans="2:60">
+    <row r="41" spans="2:60" ht="14.85" customHeight="1">
       <c r="B41" s="62"/>
       <c r="C41" s="63"/>
       <c r="D41" s="64"/>
@@ -4606,7 +4606,7 @@
       <c r="BG41" s="75"/>
       <c r="BH41" s="76"/>
     </row>
-    <row r="42" spans="2:60">
+    <row r="42" spans="2:60" ht="14.85" customHeight="1">
       <c r="B42" s="62"/>
       <c r="C42" s="63"/>
       <c r="D42" s="64"/>
@@ -4671,7 +4671,7 @@
       <c r="BG42" s="75"/>
       <c r="BH42" s="76"/>
     </row>
-    <row r="43" spans="2:60">
+    <row r="43" spans="2:60" ht="14.85" customHeight="1">
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
       <c r="D43" s="64"/>
@@ -4736,7 +4736,7 @@
       <c r="BG43" s="75"/>
       <c r="BH43" s="76"/>
     </row>
-    <row r="44" spans="2:60">
+    <row r="44" spans="2:60" ht="14.85" customHeight="1">
       <c r="B44" s="62"/>
       <c r="C44" s="63"/>
       <c r="D44" s="64"/>
@@ -4801,7 +4801,7 @@
       <c r="BG44" s="75"/>
       <c r="BH44" s="76"/>
     </row>
-    <row r="45" spans="2:60">
+    <row r="45" spans="2:60" ht="14.85" customHeight="1">
       <c r="B45" s="62"/>
       <c r="C45" s="63"/>
       <c r="D45" s="64"/>
@@ -4866,7 +4866,7 @@
       <c r="BG45" s="75"/>
       <c r="BH45" s="76"/>
     </row>
-    <row r="46" spans="2:60">
+    <row r="46" spans="2:60" ht="14.85" customHeight="1">
       <c r="B46" s="62"/>
       <c r="C46" s="63"/>
       <c r="D46" s="64"/>
@@ -4931,7 +4931,7 @@
       <c r="BG46" s="75"/>
       <c r="BH46" s="76"/>
     </row>
-    <row r="47" spans="2:60">
+    <row r="47" spans="2:60" ht="14.85" customHeight="1">
       <c r="B47" s="62"/>
       <c r="C47" s="63"/>
       <c r="D47" s="64"/>
@@ -4996,7 +4996,7 @@
       <c r="BG47" s="75"/>
       <c r="BH47" s="76"/>
     </row>
-    <row r="48" spans="2:60">
+    <row r="48" spans="2:60" ht="14.85" customHeight="1">
       <c r="B48" s="62"/>
       <c r="C48" s="63"/>
       <c r="D48" s="64"/>
@@ -5061,7 +5061,7 @@
       <c r="BG48" s="75"/>
       <c r="BH48" s="76"/>
     </row>
-    <row r="49" spans="2:60">
+    <row r="49" spans="2:60" ht="14.85" customHeight="1">
       <c r="B49" s="62"/>
       <c r="C49" s="63"/>
       <c r="D49" s="64"/>
@@ -5126,7 +5126,7 @@
       <c r="BG49" s="75"/>
       <c r="BH49" s="76"/>
     </row>
-    <row r="50" spans="2:60">
+    <row r="50" spans="2:60" ht="14.85" customHeight="1">
       <c r="B50" s="62"/>
       <c r="C50" s="63"/>
       <c r="D50" s="64"/>
@@ -5191,44 +5191,54 @@
       <c r="BG50" s="75"/>
       <c r="BH50" s="76"/>
     </row>
-    <row r="51" spans="2:60">
-      <c r="B51" s="62"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
-      <c r="N51" s="65"/>
-      <c r="O51" s="65"/>
-      <c r="P51" s="65"/>
-      <c r="Q51" s="66"/>
-      <c r="R51" s="67"/>
-      <c r="S51" s="68"/>
-      <c r="T51" s="67"/>
-      <c r="U51" s="68"/>
-      <c r="V51" s="72"/>
-      <c r="W51" s="74"/>
-      <c r="X51" s="72"/>
-      <c r="Y51" s="73"/>
-      <c r="Z51" s="74"/>
-      <c r="AA51" s="72"/>
-      <c r="AB51" s="73"/>
-      <c r="AC51" s="74"/>
-      <c r="AD51" s="72"/>
-      <c r="AE51" s="73"/>
-      <c r="AF51" s="74"/>
-      <c r="AG51" s="72"/>
-      <c r="AH51" s="73"/>
-      <c r="AI51" s="74"/>
-      <c r="AJ51" s="72"/>
-      <c r="AK51" s="73"/>
-      <c r="AL51" s="74"/>
+    <row r="51" spans="2:60" ht="13.95" customHeight="1">
+      <c r="B51" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="173"/>
+      <c r="D51" s="173"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="173"/>
+      <c r="G51" s="174"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="175"/>
+      <c r="K51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" s="110"/>
+      <c r="M51" s="110"/>
+      <c r="N51" s="110"/>
+      <c r="O51" s="110"/>
+      <c r="P51" s="110"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S51" s="110"/>
+      <c r="T51" s="110"/>
+      <c r="U51" s="110"/>
+      <c r="V51" s="110"/>
+      <c r="W51" s="110"/>
+      <c r="X51" s="111"/>
+      <c r="Y51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z51" s="110"/>
+      <c r="AA51" s="110"/>
+      <c r="AB51" s="110"/>
+      <c r="AC51" s="110"/>
+      <c r="AD51" s="110"/>
+      <c r="AE51" s="111"/>
+      <c r="AF51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG51" s="110"/>
+      <c r="AH51" s="110"/>
+      <c r="AI51" s="110"/>
+      <c r="AJ51" s="110"/>
+      <c r="AK51" s="110"/>
+      <c r="AL51" s="111"/>
       <c r="AM51" s="123"/>
       <c r="AN51" s="124"/>
       <c r="AO51" s="75"/>
@@ -5256,174 +5266,170 @@
       <c r="BG51" s="75"/>
       <c r="BH51" s="76"/>
     </row>
-    <row r="52" spans="2:60">
-      <c r="B52" s="62"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="65"/>
-      <c r="P52" s="65"/>
-      <c r="Q52" s="66"/>
-      <c r="R52" s="67"/>
-      <c r="S52" s="68"/>
-      <c r="T52" s="67"/>
-      <c r="U52" s="68"/>
-      <c r="V52" s="72"/>
-      <c r="W52" s="74"/>
-      <c r="X52" s="72"/>
-      <c r="Y52" s="73"/>
-      <c r="Z52" s="74"/>
-      <c r="AA52" s="72"/>
-      <c r="AB52" s="73"/>
-      <c r="AC52" s="74"/>
-      <c r="AD52" s="72"/>
-      <c r="AE52" s="73"/>
-      <c r="AF52" s="74"/>
-      <c r="AG52" s="72"/>
-      <c r="AH52" s="73"/>
-      <c r="AI52" s="74"/>
-      <c r="AJ52" s="72"/>
-      <c r="AK52" s="73"/>
-      <c r="AL52" s="74"/>
-      <c r="AM52" s="123"/>
-      <c r="AN52" s="124"/>
-      <c r="AO52" s="75"/>
-      <c r="AP52" s="76"/>
-      <c r="AQ52" s="77"/>
-      <c r="AR52" s="78"/>
-      <c r="AS52" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT52" s="79"/>
-      <c r="AU52" s="80"/>
-      <c r="AV52" s="75"/>
-      <c r="AW52" s="76"/>
-      <c r="AX52" s="123"/>
-      <c r="AY52" s="124"/>
-      <c r="AZ52" s="75"/>
-      <c r="BA52" s="76"/>
-      <c r="BB52" s="77"/>
-      <c r="BC52" s="78"/>
-      <c r="BD52" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE52" s="79"/>
-      <c r="BF52" s="80"/>
-      <c r="BG52" s="75"/>
-      <c r="BH52" s="76"/>
+    <row r="52" spans="2:60" ht="6.6" customHeight="1">
+      <c r="B52" s="178"/>
+      <c r="C52" s="179"/>
+      <c r="D52" s="179"/>
+      <c r="E52" s="179"/>
+      <c r="F52" s="179"/>
+      <c r="G52" s="176"/>
+      <c r="H52" s="176"/>
+      <c r="I52" s="176"/>
+      <c r="J52" s="177"/>
+      <c r="K52" s="115"/>
+      <c r="L52" s="116"/>
+      <c r="M52" s="116"/>
+      <c r="N52" s="116"/>
+      <c r="O52" s="116"/>
+      <c r="P52" s="116"/>
+      <c r="Q52" s="117"/>
+      <c r="R52" s="115"/>
+      <c r="S52" s="116"/>
+      <c r="T52" s="116"/>
+      <c r="U52" s="116"/>
+      <c r="V52" s="116"/>
+      <c r="W52" s="116"/>
+      <c r="X52" s="117"/>
+      <c r="Y52" s="115"/>
+      <c r="Z52" s="116"/>
+      <c r="AA52" s="116"/>
+      <c r="AB52" s="116"/>
+      <c r="AC52" s="116"/>
+      <c r="AD52" s="116"/>
+      <c r="AE52" s="117"/>
+      <c r="AF52" s="115"/>
+      <c r="AG52" s="116"/>
+      <c r="AH52" s="116"/>
+      <c r="AI52" s="116"/>
+      <c r="AJ52" s="116"/>
+      <c r="AK52" s="116"/>
+      <c r="AL52" s="117"/>
+      <c r="AM52" s="44"/>
+      <c r="AN52" s="69"/>
+      <c r="AO52" s="154"/>
+      <c r="AP52" s="155"/>
+      <c r="AQ52" s="154"/>
+      <c r="AR52" s="158"/>
+      <c r="AS52" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT52" s="142"/>
+      <c r="AU52" s="143"/>
+      <c r="AV52" s="146"/>
+      <c r="AW52" s="143"/>
+      <c r="AX52" s="148"/>
+      <c r="AY52" s="149"/>
+      <c r="AZ52" s="146"/>
+      <c r="BA52" s="143"/>
+      <c r="BB52" s="146"/>
+      <c r="BC52" s="142"/>
+      <c r="BD52" s="152" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE52" s="142"/>
+      <c r="BF52" s="143"/>
+      <c r="BG52" s="146"/>
+      <c r="BH52" s="143"/>
     </row>
-    <row r="53" spans="2:60">
-      <c r="B53" s="62"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="65"/>
-      <c r="I53" s="65"/>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65"/>
-      <c r="L53" s="65"/>
-      <c r="M53" s="65"/>
-      <c r="N53" s="65"/>
-      <c r="O53" s="65"/>
-      <c r="P53" s="65"/>
-      <c r="Q53" s="66"/>
-      <c r="R53" s="67"/>
-      <c r="S53" s="68"/>
-      <c r="T53" s="67"/>
-      <c r="U53" s="68"/>
-      <c r="V53" s="72"/>
-      <c r="W53" s="74"/>
-      <c r="X53" s="72"/>
-      <c r="Y53" s="73"/>
-      <c r="Z53" s="74"/>
-      <c r="AA53" s="72"/>
-      <c r="AB53" s="73"/>
-      <c r="AC53" s="74"/>
-      <c r="AD53" s="72"/>
-      <c r="AE53" s="73"/>
-      <c r="AF53" s="74"/>
-      <c r="AG53" s="72"/>
-      <c r="AH53" s="73"/>
-      <c r="AI53" s="74"/>
-      <c r="AJ53" s="72"/>
-      <c r="AK53" s="73"/>
-      <c r="AL53" s="74"/>
-      <c r="AM53" s="123"/>
-      <c r="AN53" s="124"/>
-      <c r="AO53" s="75"/>
-      <c r="AP53" s="76"/>
-      <c r="AQ53" s="77"/>
-      <c r="AR53" s="78"/>
-      <c r="AS53" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT53" s="79"/>
-      <c r="AU53" s="80"/>
-      <c r="AV53" s="75"/>
-      <c r="AW53" s="76"/>
-      <c r="AX53" s="123"/>
-      <c r="AY53" s="124"/>
-      <c r="AZ53" s="75"/>
-      <c r="BA53" s="76"/>
-      <c r="BB53" s="77"/>
-      <c r="BC53" s="78"/>
-      <c r="BD53" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE53" s="79"/>
-      <c r="BF53" s="80"/>
-      <c r="BG53" s="75"/>
-      <c r="BH53" s="76"/>
+    <row r="53" spans="2:60" ht="6.6" customHeight="1">
+      <c r="B53" s="180"/>
+      <c r="C53" s="181"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="181"/>
+      <c r="G53" s="176"/>
+      <c r="H53" s="176"/>
+      <c r="I53" s="176"/>
+      <c r="J53" s="177"/>
+      <c r="K53" s="112"/>
+      <c r="L53" s="113"/>
+      <c r="M53" s="113"/>
+      <c r="N53" s="113"/>
+      <c r="O53" s="113"/>
+      <c r="P53" s="113"/>
+      <c r="Q53" s="114"/>
+      <c r="R53" s="112"/>
+      <c r="S53" s="113"/>
+      <c r="T53" s="113"/>
+      <c r="U53" s="113"/>
+      <c r="V53" s="113"/>
+      <c r="W53" s="113"/>
+      <c r="X53" s="114"/>
+      <c r="Y53" s="112"/>
+      <c r="Z53" s="113"/>
+      <c r="AA53" s="113"/>
+      <c r="AB53" s="113"/>
+      <c r="AC53" s="113"/>
+      <c r="AD53" s="113"/>
+      <c r="AE53" s="114"/>
+      <c r="AF53" s="112"/>
+      <c r="AG53" s="113"/>
+      <c r="AH53" s="113"/>
+      <c r="AI53" s="113"/>
+      <c r="AJ53" s="113"/>
+      <c r="AK53" s="113"/>
+      <c r="AL53" s="114"/>
+      <c r="AM53" s="46"/>
+      <c r="AN53" s="70"/>
+      <c r="AO53" s="156"/>
+      <c r="AP53" s="157"/>
+      <c r="AQ53" s="156"/>
+      <c r="AR53" s="159"/>
+      <c r="AS53" s="153"/>
+      <c r="AT53" s="144"/>
+      <c r="AU53" s="145"/>
+      <c r="AV53" s="147"/>
+      <c r="AW53" s="145"/>
+      <c r="AX53" s="150"/>
+      <c r="AY53" s="151"/>
+      <c r="AZ53" s="147"/>
+      <c r="BA53" s="145"/>
+      <c r="BB53" s="147"/>
+      <c r="BC53" s="144"/>
+      <c r="BD53" s="153"/>
+      <c r="BE53" s="144"/>
+      <c r="BF53" s="145"/>
+      <c r="BG53" s="147"/>
+      <c r="BH53" s="145"/>
     </row>
     <row r="54" spans="2:60">
-      <c r="B54" s="62"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="65"/>
-      <c r="O54" s="65"/>
-      <c r="P54" s="65"/>
-      <c r="Q54" s="66"/>
-      <c r="R54" s="67"/>
-      <c r="S54" s="68"/>
-      <c r="T54" s="67"/>
-      <c r="U54" s="68"/>
-      <c r="V54" s="72"/>
-      <c r="W54" s="74"/>
-      <c r="X54" s="72"/>
-      <c r="Y54" s="73"/>
-      <c r="Z54" s="74"/>
-      <c r="AA54" s="72"/>
-      <c r="AB54" s="73"/>
-      <c r="AC54" s="74"/>
-      <c r="AD54" s="72"/>
-      <c r="AE54" s="73"/>
-      <c r="AF54" s="74"/>
-      <c r="AG54" s="72"/>
-      <c r="AH54" s="73"/>
-      <c r="AI54" s="74"/>
-      <c r="AJ54" s="72"/>
-      <c r="AK54" s="73"/>
-      <c r="AL54" s="74"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="83"/>
+      <c r="K54" s="59"/>
+      <c r="L54" s="60"/>
+      <c r="M54" s="60"/>
+      <c r="N54" s="60"/>
+      <c r="O54" s="60"/>
+      <c r="P54" s="60"/>
+      <c r="Q54" s="61"/>
+      <c r="R54" s="59"/>
+      <c r="S54" s="60"/>
+      <c r="T54" s="60"/>
+      <c r="U54" s="60"/>
+      <c r="V54" s="60"/>
+      <c r="W54" s="60"/>
+      <c r="X54" s="61"/>
+      <c r="Y54" s="59"/>
+      <c r="Z54" s="60"/>
+      <c r="AA54" s="60"/>
+      <c r="AB54" s="60"/>
+      <c r="AC54" s="60"/>
+      <c r="AD54" s="60"/>
+      <c r="AE54" s="61"/>
+      <c r="AF54" s="59"/>
+      <c r="AG54" s="60"/>
+      <c r="AH54" s="60"/>
+      <c r="AI54" s="60"/>
+      <c r="AJ54" s="60"/>
+      <c r="AK54" s="60"/>
+      <c r="AL54" s="61"/>
       <c r="AM54" s="123"/>
       <c r="AN54" s="124"/>
       <c r="AO54" s="75"/>
@@ -5451,54 +5457,54 @@
       <c r="BG54" s="75"/>
       <c r="BH54" s="76"/>
     </row>
-    <row r="55" spans="2:60" ht="13.95" customHeight="1">
-      <c r="B55" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" s="173"/>
-      <c r="D55" s="173"/>
-      <c r="E55" s="173"/>
-      <c r="F55" s="173"/>
-      <c r="G55" s="174"/>
-      <c r="H55" s="174"/>
-      <c r="I55" s="174"/>
-      <c r="J55" s="175"/>
-      <c r="K55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L55" s="110"/>
-      <c r="M55" s="110"/>
-      <c r="N55" s="110"/>
-      <c r="O55" s="110"/>
-      <c r="P55" s="110"/>
-      <c r="Q55" s="111"/>
-      <c r="R55" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="S55" s="110"/>
-      <c r="T55" s="110"/>
-      <c r="U55" s="110"/>
-      <c r="V55" s="110"/>
-      <c r="W55" s="110"/>
-      <c r="X55" s="111"/>
-      <c r="Y55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z55" s="110"/>
-      <c r="AA55" s="110"/>
-      <c r="AB55" s="110"/>
-      <c r="AC55" s="110"/>
-      <c r="AD55" s="110"/>
-      <c r="AE55" s="111"/>
-      <c r="AF55" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG55" s="110"/>
-      <c r="AH55" s="110"/>
-      <c r="AI55" s="110"/>
-      <c r="AJ55" s="110"/>
-      <c r="AK55" s="110"/>
-      <c r="AL55" s="111"/>
+    <row r="55" spans="2:60">
+      <c r="B55" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="52"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="52"/>
+      <c r="O55" s="52"/>
+      <c r="P55" s="52"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="S55" s="52"/>
+      <c r="T55" s="52"/>
+      <c r="U55" s="52"/>
+      <c r="V55" s="52"/>
+      <c r="W55" s="52"/>
+      <c r="X55" s="53"/>
+      <c r="Y55" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z55" s="52"/>
+      <c r="AA55" s="52"/>
+      <c r="AB55" s="52"/>
+      <c r="AC55" s="52"/>
+      <c r="AD55" s="52"/>
+      <c r="AE55" s="53"/>
+      <c r="AF55" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG55" s="52"/>
+      <c r="AH55" s="52"/>
+      <c r="AI55" s="52"/>
+      <c r="AJ55" s="52"/>
+      <c r="AK55" s="52"/>
+      <c r="AL55" s="53"/>
       <c r="AM55" s="123"/>
       <c r="AN55" s="124"/>
       <c r="AO55" s="75"/>
@@ -5526,170 +5532,184 @@
       <c r="BG55" s="75"/>
       <c r="BH55" s="76"/>
     </row>
-    <row r="56" spans="2:60" ht="6.6" customHeight="1">
-      <c r="B56" s="178"/>
-      <c r="C56" s="179"/>
-      <c r="D56" s="179"/>
-      <c r="E56" s="179"/>
-      <c r="F56" s="179"/>
-      <c r="G56" s="176"/>
-      <c r="H56" s="176"/>
-      <c r="I56" s="176"/>
-      <c r="J56" s="177"/>
-      <c r="K56" s="115"/>
-      <c r="L56" s="116"/>
-      <c r="M56" s="116"/>
-      <c r="N56" s="116"/>
-      <c r="O56" s="116"/>
-      <c r="P56" s="116"/>
-      <c r="Q56" s="117"/>
-      <c r="R56" s="115"/>
-      <c r="S56" s="116"/>
-      <c r="T56" s="116"/>
-      <c r="U56" s="116"/>
-      <c r="V56" s="116"/>
-      <c r="W56" s="116"/>
-      <c r="X56" s="117"/>
-      <c r="Y56" s="115"/>
-      <c r="Z56" s="116"/>
-      <c r="AA56" s="116"/>
-      <c r="AB56" s="116"/>
-      <c r="AC56" s="116"/>
-      <c r="AD56" s="116"/>
-      <c r="AE56" s="117"/>
-      <c r="AF56" s="115"/>
-      <c r="AG56" s="116"/>
-      <c r="AH56" s="116"/>
-      <c r="AI56" s="116"/>
-      <c r="AJ56" s="116"/>
-      <c r="AK56" s="116"/>
-      <c r="AL56" s="117"/>
-      <c r="AM56" s="44"/>
-      <c r="AN56" s="69"/>
-      <c r="AO56" s="154"/>
-      <c r="AP56" s="155"/>
-      <c r="AQ56" s="154"/>
-      <c r="AR56" s="158"/>
-      <c r="AS56" s="152" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT56" s="142"/>
-      <c r="AU56" s="143"/>
-      <c r="AV56" s="146"/>
-      <c r="AW56" s="143"/>
-      <c r="AX56" s="148"/>
-      <c r="AY56" s="149"/>
-      <c r="AZ56" s="146"/>
-      <c r="BA56" s="143"/>
-      <c r="BB56" s="146"/>
-      <c r="BC56" s="142"/>
-      <c r="BD56" s="152" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE56" s="142"/>
-      <c r="BF56" s="143"/>
-      <c r="BG56" s="146"/>
-      <c r="BH56" s="143"/>
+    <row r="56" spans="2:60">
+      <c r="B56" s="54"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="55"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="55"/>
+      <c r="N56" s="55"/>
+      <c r="O56" s="55"/>
+      <c r="P56" s="55"/>
+      <c r="Q56" s="56"/>
+      <c r="R56" s="54"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="55"/>
+      <c r="U56" s="55"/>
+      <c r="V56" s="55"/>
+      <c r="W56" s="55"/>
+      <c r="X56" s="56"/>
+      <c r="Y56" s="54"/>
+      <c r="Z56" s="55"/>
+      <c r="AA56" s="55"/>
+      <c r="AB56" s="55"/>
+      <c r="AC56" s="55"/>
+      <c r="AD56" s="55"/>
+      <c r="AE56" s="56"/>
+      <c r="AF56" s="54"/>
+      <c r="AG56" s="55"/>
+      <c r="AH56" s="55"/>
+      <c r="AI56" s="55"/>
+      <c r="AJ56" s="55"/>
+      <c r="AK56" s="55"/>
+      <c r="AL56" s="56"/>
+      <c r="AM56" s="123"/>
+      <c r="AN56" s="124"/>
+      <c r="AO56" s="75"/>
+      <c r="AP56" s="76"/>
+      <c r="AQ56" s="77"/>
+      <c r="AR56" s="78"/>
+      <c r="AS56" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT56" s="79"/>
+      <c r="AU56" s="80"/>
+      <c r="AV56" s="75"/>
+      <c r="AW56" s="76"/>
+      <c r="AX56" s="123"/>
+      <c r="AY56" s="124"/>
+      <c r="AZ56" s="75"/>
+      <c r="BA56" s="76"/>
+      <c r="BB56" s="77"/>
+      <c r="BC56" s="78"/>
+      <c r="BD56" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE56" s="79"/>
+      <c r="BF56" s="80"/>
+      <c r="BG56" s="75"/>
+      <c r="BH56" s="76"/>
     </row>
-    <row r="57" spans="2:60" ht="6.6" customHeight="1">
-      <c r="B57" s="180"/>
-      <c r="C57" s="181"/>
-      <c r="D57" s="181"/>
-      <c r="E57" s="181"/>
-      <c r="F57" s="181"/>
-      <c r="G57" s="176"/>
-      <c r="H57" s="176"/>
-      <c r="I57" s="176"/>
-      <c r="J57" s="177"/>
-      <c r="K57" s="112"/>
-      <c r="L57" s="113"/>
-      <c r="M57" s="113"/>
-      <c r="N57" s="113"/>
-      <c r="O57" s="113"/>
-      <c r="P57" s="113"/>
-      <c r="Q57" s="114"/>
-      <c r="R57" s="112"/>
-      <c r="S57" s="113"/>
-      <c r="T57" s="113"/>
-      <c r="U57" s="113"/>
-      <c r="V57" s="113"/>
-      <c r="W57" s="113"/>
-      <c r="X57" s="114"/>
-      <c r="Y57" s="112"/>
-      <c r="Z57" s="113"/>
-      <c r="AA57" s="113"/>
-      <c r="AB57" s="113"/>
-      <c r="AC57" s="113"/>
-      <c r="AD57" s="113"/>
-      <c r="AE57" s="114"/>
-      <c r="AF57" s="112"/>
-      <c r="AG57" s="113"/>
-      <c r="AH57" s="113"/>
-      <c r="AI57" s="113"/>
-      <c r="AJ57" s="113"/>
-      <c r="AK57" s="113"/>
-      <c r="AL57" s="114"/>
-      <c r="AM57" s="46"/>
-      <c r="AN57" s="70"/>
-      <c r="AO57" s="156"/>
-      <c r="AP57" s="157"/>
-      <c r="AQ57" s="156"/>
-      <c r="AR57" s="159"/>
-      <c r="AS57" s="153"/>
-      <c r="AT57" s="144"/>
-      <c r="AU57" s="145"/>
-      <c r="AV57" s="147"/>
-      <c r="AW57" s="145"/>
-      <c r="AX57" s="150"/>
-      <c r="AY57" s="151"/>
-      <c r="AZ57" s="147"/>
-      <c r="BA57" s="145"/>
-      <c r="BB57" s="147"/>
-      <c r="BC57" s="144"/>
-      <c r="BD57" s="153"/>
-      <c r="BE57" s="144"/>
-      <c r="BF57" s="145"/>
-      <c r="BG57" s="147"/>
-      <c r="BH57" s="145"/>
+    <row r="57" spans="2:60">
+      <c r="B57" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="50"/>
+      <c r="N57" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="O57" s="92"/>
+      <c r="P57" s="88"/>
+      <c r="Q57" s="88"/>
+      <c r="R57" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="S57" s="98"/>
+      <c r="T57" s="89"/>
+      <c r="U57" s="89"/>
+      <c r="V57" s="243"/>
+      <c r="W57" s="244"/>
+      <c r="X57" s="244"/>
+      <c r="Y57" s="244"/>
+      <c r="Z57" s="244"/>
+      <c r="AA57" s="244"/>
+      <c r="AB57" s="244"/>
+      <c r="AC57" s="244"/>
+      <c r="AD57" s="244"/>
+      <c r="AE57" s="244"/>
+      <c r="AF57" s="244"/>
+      <c r="AG57" s="244"/>
+      <c r="AH57" s="244"/>
+      <c r="AI57" s="244"/>
+      <c r="AJ57" s="244"/>
+      <c r="AK57" s="244"/>
+      <c r="AL57" s="245"/>
+      <c r="AM57" s="123"/>
+      <c r="AN57" s="124"/>
+      <c r="AO57" s="75"/>
+      <c r="AP57" s="76"/>
+      <c r="AQ57" s="77"/>
+      <c r="AR57" s="78"/>
+      <c r="AS57" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT57" s="79"/>
+      <c r="AU57" s="80"/>
+      <c r="AV57" s="75"/>
+      <c r="AW57" s="76"/>
+      <c r="AX57" s="123"/>
+      <c r="AY57" s="124"/>
+      <c r="AZ57" s="75"/>
+      <c r="BA57" s="76"/>
+      <c r="BB57" s="77"/>
+      <c r="BC57" s="78"/>
+      <c r="BD57" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE57" s="79"/>
+      <c r="BF57" s="80"/>
+      <c r="BG57" s="75"/>
+      <c r="BH57" s="76"/>
     </row>
     <row r="58" spans="2:60">
-      <c r="B58" s="81"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="59"/>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="60"/>
-      <c r="O58" s="60"/>
-      <c r="P58" s="60"/>
-      <c r="Q58" s="61"/>
-      <c r="R58" s="59"/>
-      <c r="S58" s="60"/>
-      <c r="T58" s="60"/>
-      <c r="U58" s="60"/>
-      <c r="V58" s="60"/>
-      <c r="W58" s="60"/>
-      <c r="X58" s="61"/>
-      <c r="Y58" s="59"/>
-      <c r="Z58" s="60"/>
-      <c r="AA58" s="60"/>
-      <c r="AB58" s="60"/>
-      <c r="AC58" s="60"/>
-      <c r="AD58" s="60"/>
-      <c r="AE58" s="61"/>
-      <c r="AF58" s="59"/>
-      <c r="AG58" s="60"/>
-      <c r="AH58" s="60"/>
-      <c r="AI58" s="60"/>
-      <c r="AJ58" s="60"/>
-      <c r="AK58" s="60"/>
-      <c r="AL58" s="61"/>
+      <c r="B58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="58"/>
+      <c r="K58" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="L58" s="102"/>
+      <c r="M58" s="102"/>
+      <c r="N58" s="102"/>
+      <c r="O58" s="102"/>
+      <c r="P58" s="102"/>
+      <c r="Q58" s="102"/>
+      <c r="R58" s="99"/>
+      <c r="S58" s="99"/>
+      <c r="T58" s="99"/>
+      <c r="U58" s="100"/>
+      <c r="V58" s="246"/>
+      <c r="W58" s="247"/>
+      <c r="X58" s="247"/>
+      <c r="Y58" s="247"/>
+      <c r="Z58" s="247"/>
+      <c r="AA58" s="247"/>
+      <c r="AB58" s="247"/>
+      <c r="AC58" s="247"/>
+      <c r="AD58" s="247"/>
+      <c r="AE58" s="247"/>
+      <c r="AF58" s="247"/>
+      <c r="AG58" s="247"/>
+      <c r="AH58" s="247"/>
+      <c r="AI58" s="247"/>
+      <c r="AJ58" s="247"/>
+      <c r="AK58" s="247"/>
+      <c r="AL58" s="248"/>
       <c r="AM58" s="123"/>
       <c r="AN58" s="124"/>
       <c r="AO58" s="75"/>
@@ -5718,53 +5738,49 @@
       <c r="BH58" s="76"/>
     </row>
     <row r="59" spans="2:60">
-      <c r="B59" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="53"/>
-      <c r="K59" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="52"/>
-      <c r="M59" s="52"/>
-      <c r="N59" s="52"/>
-      <c r="O59" s="52"/>
-      <c r="P59" s="52"/>
-      <c r="Q59" s="53"/>
-      <c r="R59" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="S59" s="52"/>
-      <c r="T59" s="52"/>
-      <c r="U59" s="52"/>
-      <c r="V59" s="52"/>
-      <c r="W59" s="52"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z59" s="52"/>
-      <c r="AA59" s="52"/>
-      <c r="AB59" s="52"/>
-      <c r="AC59" s="52"/>
-      <c r="AD59" s="52"/>
-      <c r="AE59" s="53"/>
-      <c r="AF59" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG59" s="52"/>
-      <c r="AH59" s="52"/>
-      <c r="AI59" s="52"/>
-      <c r="AJ59" s="52"/>
-      <c r="AK59" s="52"/>
-      <c r="AL59" s="53"/>
+      <c r="B59" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="49"/>
+      <c r="M59" s="50"/>
+      <c r="N59" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="O59" s="94"/>
+      <c r="P59" s="88"/>
+      <c r="Q59" s="88"/>
+      <c r="R59" s="95" t="s">
+        <v>32</v>
+      </c>
+      <c r="S59" s="96"/>
+      <c r="T59" s="90"/>
+      <c r="U59" s="90"/>
+      <c r="V59" s="246"/>
+      <c r="W59" s="247"/>
+      <c r="X59" s="247"/>
+      <c r="Y59" s="247"/>
+      <c r="Z59" s="247"/>
+      <c r="AA59" s="247"/>
+      <c r="AB59" s="247"/>
+      <c r="AC59" s="247"/>
+      <c r="AD59" s="247"/>
+      <c r="AE59" s="247"/>
+      <c r="AF59" s="247"/>
+      <c r="AG59" s="247"/>
+      <c r="AH59" s="247"/>
+      <c r="AI59" s="247"/>
+      <c r="AJ59" s="247"/>
+      <c r="AK59" s="247"/>
+      <c r="AL59" s="248"/>
       <c r="AM59" s="123"/>
       <c r="AN59" s="124"/>
       <c r="AO59" s="75"/>
@@ -5793,439 +5809,443 @@
       <c r="BH59" s="76"/>
     </row>
     <row r="60" spans="2:60">
-      <c r="B60" s="54"/>
-      <c r="C60" s="55"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="55"/>
-      <c r="I60" s="55"/>
-      <c r="J60" s="56"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="55"/>
-      <c r="M60" s="55"/>
-      <c r="N60" s="55"/>
-      <c r="O60" s="55"/>
-      <c r="P60" s="55"/>
-      <c r="Q60" s="56"/>
-      <c r="R60" s="54"/>
-      <c r="S60" s="55"/>
-      <c r="T60" s="55"/>
-      <c r="U60" s="55"/>
-      <c r="V60" s="55"/>
-      <c r="W60" s="55"/>
-      <c r="X60" s="56"/>
-      <c r="Y60" s="54"/>
-      <c r="Z60" s="55"/>
-      <c r="AA60" s="55"/>
-      <c r="AB60" s="55"/>
-      <c r="AC60" s="55"/>
-      <c r="AD60" s="55"/>
-      <c r="AE60" s="56"/>
-      <c r="AF60" s="54"/>
-      <c r="AG60" s="55"/>
-      <c r="AH60" s="55"/>
-      <c r="AI60" s="55"/>
-      <c r="AJ60" s="55"/>
-      <c r="AK60" s="55"/>
-      <c r="AL60" s="56"/>
-      <c r="AM60" s="123"/>
-      <c r="AN60" s="124"/>
-      <c r="AO60" s="75"/>
-      <c r="AP60" s="76"/>
-      <c r="AQ60" s="77"/>
-      <c r="AR60" s="78"/>
-      <c r="AS60" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT60" s="79"/>
-      <c r="AU60" s="80"/>
-      <c r="AV60" s="75"/>
-      <c r="AW60" s="76"/>
-      <c r="AX60" s="123"/>
-      <c r="AY60" s="124"/>
-      <c r="AZ60" s="75"/>
-      <c r="BA60" s="76"/>
-      <c r="BB60" s="77"/>
-      <c r="BC60" s="78"/>
-      <c r="BD60" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE60" s="79"/>
-      <c r="BF60" s="80"/>
-      <c r="BG60" s="75"/>
-      <c r="BH60" s="76"/>
+      <c r="B60" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="105"/>
+      <c r="N60" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="O60" s="94"/>
+      <c r="P60" s="88"/>
+      <c r="Q60" s="88"/>
+      <c r="R60" s="93" t="s">
+        <v>32</v>
+      </c>
+      <c r="S60" s="94"/>
+      <c r="T60" s="88"/>
+      <c r="U60" s="88"/>
+      <c r="V60" s="256"/>
+      <c r="W60" s="255"/>
+      <c r="X60" s="255"/>
+      <c r="Y60" s="255"/>
+      <c r="Z60" s="255"/>
+      <c r="AA60" s="255"/>
+      <c r="AB60" s="255"/>
+      <c r="AC60" s="255"/>
+      <c r="AD60" s="255"/>
+      <c r="AE60" s="255"/>
+      <c r="AF60" s="255"/>
+      <c r="AG60" s="255"/>
+      <c r="AH60" s="255"/>
+      <c r="AI60" s="255"/>
+      <c r="AJ60" s="255"/>
+      <c r="AK60" s="255"/>
+      <c r="AL60" s="257"/>
+      <c r="AM60" s="170" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN60" s="170"/>
+      <c r="AO60" s="170" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP60" s="170"/>
+      <c r="AQ60" s="170"/>
+      <c r="AR60" s="170"/>
+      <c r="AS60" s="170" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT60" s="170"/>
+      <c r="AU60" s="170"/>
+      <c r="AV60" s="170"/>
+      <c r="AW60" s="170"/>
+      <c r="AX60" s="170" t="s">
+        <v>15</v>
+      </c>
+      <c r="AY60" s="170"/>
+      <c r="AZ60" s="170" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA60" s="170"/>
+      <c r="BB60" s="170"/>
+      <c r="BC60" s="170"/>
+      <c r="BD60" s="170" t="s">
+        <v>46</v>
+      </c>
+      <c r="BE60" s="170"/>
+      <c r="BF60" s="170"/>
+      <c r="BG60" s="170"/>
+      <c r="BH60" s="170"/>
     </row>
-    <row r="61" spans="2:60">
-      <c r="B61" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-      <c r="K61" s="49"/>
-      <c r="L61" s="49"/>
-      <c r="M61" s="50"/>
-      <c r="N61" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="O61" s="92"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="88"/>
-      <c r="R61" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="S61" s="98"/>
-      <c r="T61" s="89"/>
-      <c r="U61" s="89"/>
-      <c r="V61" s="243"/>
-      <c r="W61" s="244"/>
-      <c r="X61" s="244"/>
-      <c r="Y61" s="244"/>
-      <c r="Z61" s="244"/>
-      <c r="AA61" s="244"/>
-      <c r="AB61" s="244"/>
-      <c r="AC61" s="244"/>
-      <c r="AD61" s="244"/>
-      <c r="AE61" s="244"/>
-      <c r="AF61" s="244"/>
-      <c r="AG61" s="244"/>
-      <c r="AH61" s="244"/>
-      <c r="AI61" s="244"/>
-      <c r="AJ61" s="244"/>
-      <c r="AK61" s="244"/>
-      <c r="AL61" s="245"/>
-      <c r="AM61" s="123"/>
-      <c r="AN61" s="124"/>
-      <c r="AO61" s="75"/>
-      <c r="AP61" s="76"/>
-      <c r="AQ61" s="77"/>
-      <c r="AR61" s="78"/>
-      <c r="AS61" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT61" s="79"/>
-      <c r="AU61" s="80"/>
-      <c r="AV61" s="75"/>
-      <c r="AW61" s="76"/>
-      <c r="AX61" s="123"/>
-      <c r="AY61" s="124"/>
-      <c r="AZ61" s="75"/>
-      <c r="BA61" s="76"/>
-      <c r="BB61" s="77"/>
-      <c r="BC61" s="78"/>
-      <c r="BD61" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE61" s="79"/>
-      <c r="BF61" s="80"/>
-      <c r="BG61" s="75"/>
-      <c r="BH61" s="76"/>
+    <row r="61" spans="2:60" ht="14.4" customHeight="1">
+      <c r="B61" s="84"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="85"/>
+      <c r="E61" s="85"/>
+      <c r="F61" s="85"/>
+      <c r="G61" s="85"/>
+      <c r="H61" s="85"/>
+      <c r="I61" s="85"/>
+      <c r="J61" s="85"/>
+      <c r="K61" s="85"/>
+      <c r="L61" s="85"/>
+      <c r="M61" s="85"/>
+      <c r="N61" s="85"/>
+      <c r="O61" s="85"/>
+      <c r="P61" s="85"/>
+      <c r="Q61" s="85"/>
+      <c r="R61" s="85"/>
+      <c r="S61" s="85"/>
+      <c r="T61" s="85"/>
+      <c r="U61" s="86"/>
+      <c r="V61" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
+      <c r="AC61" s="28"/>
+      <c r="AD61" s="28"/>
+      <c r="AE61" s="28"/>
+      <c r="AF61" s="28"/>
+      <c r="AG61" s="28"/>
+      <c r="AH61" s="28"/>
+      <c r="AI61" s="28"/>
+      <c r="AJ61" s="28"/>
+      <c r="AK61" s="28"/>
+      <c r="AL61" s="29"/>
+      <c r="AM61" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN61" s="169"/>
+      <c r="AO61" s="208"/>
+      <c r="AP61" s="208"/>
+      <c r="AQ61" s="208"/>
+      <c r="AR61" s="208"/>
+      <c r="AS61" s="208"/>
+      <c r="AT61" s="208"/>
+      <c r="AU61" s="208"/>
+      <c r="AV61" s="208"/>
+      <c r="AW61" s="208"/>
+      <c r="AX61" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="AY61" s="169"/>
+      <c r="AZ61" s="208"/>
+      <c r="BA61" s="208"/>
+      <c r="BB61" s="208"/>
+      <c r="BC61" s="208"/>
+      <c r="BD61" s="208"/>
+      <c r="BE61" s="208"/>
+      <c r="BF61" s="208"/>
+      <c r="BG61" s="208"/>
+      <c r="BH61" s="208"/>
     </row>
-    <row r="62" spans="2:60">
-      <c r="B62" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="58"/>
-      <c r="K62" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="L62" s="102"/>
-      <c r="M62" s="102"/>
-      <c r="N62" s="102"/>
-      <c r="O62" s="102"/>
-      <c r="P62" s="102"/>
-      <c r="Q62" s="102"/>
-      <c r="R62" s="99"/>
-      <c r="S62" s="99"/>
-      <c r="T62" s="99"/>
-      <c r="U62" s="100"/>
-      <c r="V62" s="246"/>
-      <c r="W62" s="247"/>
-      <c r="X62" s="247"/>
-      <c r="Y62" s="247"/>
-      <c r="Z62" s="247"/>
-      <c r="AA62" s="247"/>
-      <c r="AB62" s="247"/>
-      <c r="AC62" s="247"/>
-      <c r="AD62" s="247"/>
-      <c r="AE62" s="247"/>
-      <c r="AF62" s="247"/>
-      <c r="AG62" s="247"/>
-      <c r="AH62" s="247"/>
-      <c r="AI62" s="247"/>
-      <c r="AJ62" s="247"/>
-      <c r="AK62" s="247"/>
-      <c r="AL62" s="248"/>
-      <c r="AM62" s="123"/>
-      <c r="AN62" s="124"/>
-      <c r="AO62" s="75"/>
-      <c r="AP62" s="76"/>
-      <c r="AQ62" s="77"/>
-      <c r="AR62" s="78"/>
-      <c r="AS62" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT62" s="79"/>
-      <c r="AU62" s="80"/>
-      <c r="AV62" s="75"/>
-      <c r="AW62" s="76"/>
-      <c r="AX62" s="123"/>
-      <c r="AY62" s="124"/>
-      <c r="AZ62" s="75"/>
-      <c r="BA62" s="76"/>
-      <c r="BB62" s="77"/>
-      <c r="BC62" s="78"/>
-      <c r="BD62" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE62" s="79"/>
-      <c r="BF62" s="80"/>
-      <c r="BG62" s="75"/>
-      <c r="BH62" s="76"/>
+    <row r="62" spans="2:60" ht="14.4" customHeight="1">
+      <c r="B62" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="31"/>
+      <c r="D62" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="253"/>
+      <c r="K62" s="253"/>
+      <c r="L62" s="253"/>
+      <c r="M62" s="253"/>
+      <c r="N62" s="253"/>
+      <c r="O62" s="253"/>
+      <c r="P62" s="253"/>
+      <c r="Q62" s="253"/>
+      <c r="R62" s="253"/>
+      <c r="S62" s="254"/>
+      <c r="T62" s="213" t="s">
+        <v>41</v>
+      </c>
+      <c r="U62" s="214"/>
+      <c r="V62" s="214"/>
+      <c r="W62" s="215"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="26"/>
+      <c r="Z62" s="26"/>
+      <c r="AA62" s="26"/>
+      <c r="AB62" s="26"/>
+      <c r="AC62" s="27"/>
+      <c r="AD62" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE62" s="37"/>
+      <c r="AF62" s="37"/>
+      <c r="AG62" s="38"/>
+      <c r="AH62" s="28"/>
+      <c r="AI62" s="28"/>
+      <c r="AJ62" s="28"/>
+      <c r="AK62" s="28"/>
+      <c r="AL62" s="29"/>
+      <c r="AM62" s="169"/>
+      <c r="AN62" s="169"/>
+      <c r="AO62" s="208"/>
+      <c r="AP62" s="208"/>
+      <c r="AQ62" s="208"/>
+      <c r="AR62" s="208"/>
+      <c r="AS62" s="208"/>
+      <c r="AT62" s="208"/>
+      <c r="AU62" s="208"/>
+      <c r="AV62" s="208"/>
+      <c r="AW62" s="208"/>
+      <c r="AX62" s="169"/>
+      <c r="AY62" s="169"/>
+      <c r="AZ62" s="208"/>
+      <c r="BA62" s="208"/>
+      <c r="BB62" s="208"/>
+      <c r="BC62" s="208"/>
+      <c r="BD62" s="208"/>
+      <c r="BE62" s="208"/>
+      <c r="BF62" s="208"/>
+      <c r="BG62" s="208"/>
+      <c r="BH62" s="208"/>
     </row>
     <row r="63" spans="2:60">
-      <c r="B63" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-      <c r="K63" s="49"/>
-      <c r="L63" s="49"/>
-      <c r="M63" s="50"/>
-      <c r="N63" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="O63" s="94"/>
-      <c r="P63" s="88"/>
-      <c r="Q63" s="88"/>
-      <c r="R63" s="95" t="s">
-        <v>32</v>
-      </c>
-      <c r="S63" s="96"/>
-      <c r="T63" s="90"/>
-      <c r="U63" s="90"/>
-      <c r="V63" s="246"/>
-      <c r="W63" s="247"/>
-      <c r="X63" s="247"/>
-      <c r="Y63" s="247"/>
-      <c r="Z63" s="247"/>
-      <c r="AA63" s="247"/>
-      <c r="AB63" s="247"/>
-      <c r="AC63" s="247"/>
-      <c r="AD63" s="247"/>
-      <c r="AE63" s="247"/>
-      <c r="AF63" s="247"/>
-      <c r="AG63" s="247"/>
-      <c r="AH63" s="247"/>
-      <c r="AI63" s="247"/>
-      <c r="AJ63" s="247"/>
-      <c r="AK63" s="247"/>
-      <c r="AL63" s="248"/>
-      <c r="AM63" s="123"/>
-      <c r="AN63" s="124"/>
-      <c r="AO63" s="75"/>
-      <c r="AP63" s="76"/>
-      <c r="AQ63" s="77"/>
-      <c r="AR63" s="78"/>
-      <c r="AS63" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AT63" s="79"/>
-      <c r="AU63" s="80"/>
-      <c r="AV63" s="75"/>
-      <c r="AW63" s="76"/>
-      <c r="AX63" s="123"/>
-      <c r="AY63" s="124"/>
-      <c r="AZ63" s="75"/>
-      <c r="BA63" s="76"/>
-      <c r="BB63" s="77"/>
-      <c r="BC63" s="78"/>
-      <c r="BD63" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE63" s="79"/>
-      <c r="BF63" s="80"/>
-      <c r="BG63" s="75"/>
-      <c r="BH63" s="76"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="253"/>
+      <c r="K63" s="253"/>
+      <c r="L63" s="253"/>
+      <c r="M63" s="253"/>
+      <c r="N63" s="253"/>
+      <c r="O63" s="253"/>
+      <c r="P63" s="253"/>
+      <c r="Q63" s="253"/>
+      <c r="R63" s="253"/>
+      <c r="S63" s="254"/>
+      <c r="T63" s="213" t="s">
+        <v>41</v>
+      </c>
+      <c r="U63" s="214"/>
+      <c r="V63" s="214"/>
+      <c r="W63" s="215"/>
+      <c r="X63" s="25"/>
+      <c r="Y63" s="26"/>
+      <c r="Z63" s="26"/>
+      <c r="AA63" s="26"/>
+      <c r="AB63" s="26"/>
+      <c r="AC63" s="27"/>
+      <c r="AD63" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE63" s="37"/>
+      <c r="AF63" s="37"/>
+      <c r="AG63" s="38"/>
+      <c r="AH63" s="28"/>
+      <c r="AI63" s="28"/>
+      <c r="AJ63" s="28"/>
+      <c r="AK63" s="28"/>
+      <c r="AL63" s="29"/>
+      <c r="AM63" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN63" s="22"/>
+      <c r="AO63" s="22"/>
+      <c r="AP63" s="22"/>
+      <c r="AQ63" s="22"/>
+      <c r="AR63" s="22"/>
+      <c r="AS63" s="22"/>
+      <c r="AT63" s="22"/>
+      <c r="AU63" s="23"/>
+      <c r="AV63" s="71"/>
+      <c r="AW63" s="71"/>
+      <c r="AX63" s="71"/>
+      <c r="AY63" s="71"/>
+      <c r="AZ63" s="71"/>
+      <c r="BA63" s="71"/>
+      <c r="BB63" s="71"/>
+      <c r="BC63" s="71"/>
+      <c r="BD63" s="71"/>
+      <c r="BE63" s="71"/>
+      <c r="BF63" s="71"/>
+      <c r="BG63" s="71"/>
+      <c r="BH63" s="63"/>
     </row>
-    <row r="64" spans="2:60">
-      <c r="B64" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="C64" s="104"/>
-      <c r="D64" s="104"/>
-      <c r="E64" s="104"/>
-      <c r="F64" s="104"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="104"/>
-      <c r="I64" s="104"/>
-      <c r="J64" s="104"/>
-      <c r="K64" s="104"/>
-      <c r="L64" s="104"/>
-      <c r="M64" s="105"/>
-      <c r="N64" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="94"/>
-      <c r="P64" s="88"/>
-      <c r="Q64" s="88"/>
-      <c r="R64" s="93" t="s">
-        <v>32</v>
-      </c>
-      <c r="S64" s="94"/>
-      <c r="T64" s="88"/>
-      <c r="U64" s="88"/>
-      <c r="V64" s="256"/>
-      <c r="W64" s="255"/>
-      <c r="X64" s="255"/>
-      <c r="Y64" s="255"/>
-      <c r="Z64" s="255"/>
-      <c r="AA64" s="255"/>
-      <c r="AB64" s="255"/>
-      <c r="AC64" s="255"/>
-      <c r="AD64" s="255"/>
-      <c r="AE64" s="255"/>
-      <c r="AF64" s="255"/>
-      <c r="AG64" s="255"/>
-      <c r="AH64" s="255"/>
-      <c r="AI64" s="255"/>
-      <c r="AJ64" s="255"/>
-      <c r="AK64" s="255"/>
-      <c r="AL64" s="257"/>
-      <c r="AM64" s="170" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN64" s="170"/>
-      <c r="AO64" s="170" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP64" s="170"/>
-      <c r="AQ64" s="170"/>
-      <c r="AR64" s="170"/>
-      <c r="AS64" s="170" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT64" s="170"/>
-      <c r="AU64" s="170"/>
-      <c r="AV64" s="170"/>
-      <c r="AW64" s="170"/>
-      <c r="AX64" s="170" t="s">
-        <v>15</v>
-      </c>
-      <c r="AY64" s="170"/>
-      <c r="AZ64" s="170" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA64" s="170"/>
-      <c r="BB64" s="170"/>
-      <c r="BC64" s="170"/>
-      <c r="BD64" s="170" t="s">
-        <v>46</v>
-      </c>
-      <c r="BE64" s="170"/>
-      <c r="BF64" s="170"/>
-      <c r="BG64" s="170"/>
-      <c r="BH64" s="170"/>
+    <row r="64" spans="2:60" ht="13.8">
+      <c r="B64" s="32"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="253"/>
+      <c r="K64" s="253"/>
+      <c r="L64" s="253"/>
+      <c r="M64" s="253"/>
+      <c r="N64" s="253"/>
+      <c r="O64" s="253"/>
+      <c r="P64" s="253"/>
+      <c r="Q64" s="253"/>
+      <c r="R64" s="253"/>
+      <c r="S64" s="254"/>
+      <c r="T64" s="213" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64" s="214"/>
+      <c r="V64" s="214"/>
+      <c r="W64" s="215"/>
+      <c r="X64" s="25"/>
+      <c r="Y64" s="26"/>
+      <c r="Z64" s="26"/>
+      <c r="AA64" s="26"/>
+      <c r="AB64" s="26"/>
+      <c r="AC64" s="27"/>
+      <c r="AD64" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE64" s="37"/>
+      <c r="AF64" s="37"/>
+      <c r="AG64" s="38"/>
+      <c r="AH64" s="28"/>
+      <c r="AI64" s="28"/>
+      <c r="AJ64" s="28"/>
+      <c r="AK64" s="28"/>
+      <c r="AL64" s="29"/>
+      <c r="AM64" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN64" s="42"/>
+      <c r="AO64" s="42"/>
+      <c r="AP64" s="42"/>
+      <c r="AQ64" s="42"/>
+      <c r="AR64" s="204"/>
+      <c r="AS64" s="205"/>
+      <c r="AT64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU64" s="206"/>
+      <c r="AV64" s="207"/>
+      <c r="AW64" s="212" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX64" s="212"/>
+      <c r="AY64" s="212"/>
+      <c r="AZ64" s="212"/>
+      <c r="BA64" s="212"/>
+      <c r="BB64" s="212"/>
+      <c r="BC64" s="212"/>
+      <c r="BD64" s="204"/>
+      <c r="BE64" s="205"/>
+      <c r="BF64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG64" s="206"/>
+      <c r="BH64" s="207"/>
     </row>
-    <row r="65" spans="2:60" ht="14.4" customHeight="1">
-      <c r="B65" s="84"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="85"/>
-      <c r="E65" s="85"/>
-      <c r="F65" s="85"/>
-      <c r="G65" s="85"/>
-      <c r="H65" s="85"/>
-      <c r="I65" s="85"/>
-      <c r="J65" s="85"/>
-      <c r="K65" s="85"/>
-      <c r="L65" s="85"/>
-      <c r="M65" s="85"/>
-      <c r="N65" s="85"/>
-      <c r="O65" s="85"/>
-      <c r="P65" s="85"/>
-      <c r="Q65" s="85"/>
-      <c r="R65" s="85"/>
-      <c r="S65" s="85"/>
-      <c r="T65" s="85"/>
-      <c r="U65" s="86"/>
-      <c r="V65" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="W65" s="28"/>
-      <c r="X65" s="28"/>
-      <c r="Y65" s="28"/>
-      <c r="Z65" s="28"/>
-      <c r="AA65" s="28"/>
-      <c r="AB65" s="28"/>
-      <c r="AC65" s="28"/>
-      <c r="AD65" s="28"/>
-      <c r="AE65" s="28"/>
-      <c r="AF65" s="28"/>
-      <c r="AG65" s="28"/>
+    <row r="65" spans="2:60" ht="13.8">
+      <c r="B65" s="32"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="253"/>
+      <c r="K65" s="253"/>
+      <c r="L65" s="253"/>
+      <c r="M65" s="253"/>
+      <c r="N65" s="253"/>
+      <c r="O65" s="253"/>
+      <c r="P65" s="253"/>
+      <c r="Q65" s="253"/>
+      <c r="R65" s="253"/>
+      <c r="S65" s="254"/>
+      <c r="T65" s="213" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65" s="214"/>
+      <c r="V65" s="214"/>
+      <c r="W65" s="215"/>
+      <c r="X65" s="25"/>
+      <c r="Y65" s="26"/>
+      <c r="Z65" s="26"/>
+      <c r="AA65" s="26"/>
+      <c r="AB65" s="26"/>
+      <c r="AC65" s="27"/>
+      <c r="AD65" s="258" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE65" s="259"/>
+      <c r="AF65" s="259"/>
+      <c r="AG65" s="260"/>
       <c r="AH65" s="28"/>
       <c r="AI65" s="28"/>
       <c r="AJ65" s="28"/>
       <c r="AK65" s="28"/>
       <c r="AL65" s="29"/>
-      <c r="AM65" s="169" t="s">
-        <v>47</v>
-      </c>
-      <c r="AN65" s="169"/>
-      <c r="AO65" s="208"/>
-      <c r="AP65" s="208"/>
-      <c r="AQ65" s="208"/>
-      <c r="AR65" s="208"/>
-      <c r="AS65" s="208"/>
-      <c r="AT65" s="208"/>
-      <c r="AU65" s="208"/>
-      <c r="AV65" s="208"/>
-      <c r="AW65" s="208"/>
-      <c r="AX65" s="169" t="s">
-        <v>47</v>
-      </c>
-      <c r="AY65" s="169"/>
-      <c r="AZ65" s="208"/>
-      <c r="BA65" s="208"/>
-      <c r="BB65" s="208"/>
-      <c r="BC65" s="208"/>
-      <c r="BD65" s="208"/>
-      <c r="BE65" s="208"/>
-      <c r="BF65" s="208"/>
-      <c r="BG65" s="208"/>
-      <c r="BH65" s="208"/>
+      <c r="AM65" s="87" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN65" s="28"/>
+      <c r="AO65" s="28"/>
+      <c r="AP65" s="28"/>
+      <c r="AQ65" s="28"/>
+      <c r="AR65" s="209"/>
+      <c r="AS65" s="209"/>
+      <c r="AT65" s="210"/>
+      <c r="AU65" s="210"/>
+      <c r="AV65" s="210"/>
+      <c r="AW65" s="210"/>
+      <c r="AX65" s="210"/>
+      <c r="AY65" s="210"/>
+      <c r="AZ65" s="210"/>
+      <c r="BA65" s="210"/>
+      <c r="BB65" s="210"/>
+      <c r="BC65" s="210"/>
+      <c r="BD65" s="209"/>
+      <c r="BE65" s="209"/>
+      <c r="BF65" s="210"/>
+      <c r="BG65" s="210"/>
+      <c r="BH65" s="211"/>
     </row>
-    <row r="66" spans="2:60" ht="14.4" customHeight="1">
-      <c r="B66" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66" s="31"/>
+    <row r="66" spans="2:60">
+      <c r="B66" s="32"/>
+      <c r="C66" s="33"/>
       <c r="D66" s="36" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="E66" s="37"/>
       <c r="F66" s="37"/>
       <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
+      <c r="H66" s="38"/>
       <c r="I66" s="5"/>
       <c r="J66" s="253"/>
       <c r="K66" s="253"/>
@@ -6237,79 +6257,81 @@
       <c r="Q66" s="253"/>
       <c r="R66" s="253"/>
       <c r="S66" s="254"/>
-      <c r="T66" s="213" t="s">
+      <c r="T66" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="U66" s="214"/>
-      <c r="V66" s="214"/>
-      <c r="W66" s="215"/>
+      <c r="U66" s="42"/>
+      <c r="V66" s="42"/>
+      <c r="W66" s="43"/>
       <c r="X66" s="25"/>
       <c r="Y66" s="26"/>
       <c r="Z66" s="26"/>
       <c r="AA66" s="26"/>
       <c r="AB66" s="26"/>
       <c r="AC66" s="27"/>
-      <c r="AD66" s="36" t="s">
+      <c r="AD66" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="AE66" s="37"/>
-      <c r="AF66" s="37"/>
-      <c r="AG66" s="38"/>
+      <c r="AE66" s="259"/>
+      <c r="AF66" s="259"/>
+      <c r="AG66" s="260"/>
       <c r="AH66" s="28"/>
       <c r="AI66" s="28"/>
       <c r="AJ66" s="28"/>
       <c r="AK66" s="28"/>
       <c r="AL66" s="29"/>
-      <c r="AM66" s="169"/>
-      <c r="AN66" s="169"/>
-      <c r="AO66" s="208"/>
-      <c r="AP66" s="208"/>
-      <c r="AQ66" s="208"/>
-      <c r="AR66" s="208"/>
-      <c r="AS66" s="208"/>
-      <c r="AT66" s="208"/>
-      <c r="AU66" s="208"/>
-      <c r="AV66" s="208"/>
-      <c r="AW66" s="208"/>
-      <c r="AX66" s="169"/>
-      <c r="AY66" s="169"/>
-      <c r="AZ66" s="208"/>
-      <c r="BA66" s="208"/>
-      <c r="BB66" s="208"/>
-      <c r="BC66" s="208"/>
-      <c r="BD66" s="208"/>
-      <c r="BE66" s="208"/>
-      <c r="BF66" s="208"/>
-      <c r="BG66" s="208"/>
-      <c r="BH66" s="208"/>
+      <c r="AM66" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN66" s="45"/>
+      <c r="AO66" s="45"/>
+      <c r="AP66" s="45"/>
+      <c r="AQ66" s="45"/>
+      <c r="AR66" s="45"/>
+      <c r="AS66" s="45"/>
+      <c r="AT66" s="45"/>
+      <c r="AU66" s="45"/>
+      <c r="AV66" s="45"/>
+      <c r="AW66" s="45"/>
+      <c r="AX66" s="45"/>
+      <c r="AY66" s="45"/>
+      <c r="AZ66" s="45"/>
+      <c r="BA66" s="45"/>
+      <c r="BB66" s="45"/>
+      <c r="BC66" s="45"/>
+      <c r="BD66" s="45"/>
+      <c r="BE66" s="45"/>
+      <c r="BF66" s="45"/>
+      <c r="BG66" s="45"/>
+      <c r="BH66" s="69"/>
     </row>
     <row r="67" spans="2:60">
-      <c r="B67" s="32"/>
-      <c r="C67" s="33"/>
+      <c r="B67" s="34"/>
+      <c r="C67" s="35"/>
       <c r="D67" s="36" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="E67" s="37"/>
       <c r="F67" s="37"/>
       <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="253"/>
-      <c r="K67" s="253"/>
-      <c r="L67" s="253"/>
-      <c r="M67" s="253"/>
-      <c r="N67" s="253"/>
-      <c r="O67" s="253"/>
-      <c r="P67" s="253"/>
-      <c r="Q67" s="253"/>
-      <c r="R67" s="253"/>
-      <c r="S67" s="254"/>
-      <c r="T67" s="213" t="s">
+      <c r="H67" s="38"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
+      <c r="N67" s="39"/>
+      <c r="O67" s="39"/>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
+      <c r="R67" s="39"/>
+      <c r="S67" s="40"/>
+      <c r="T67" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="U67" s="214"/>
-      <c r="V67" s="214"/>
-      <c r="W67" s="215"/>
+      <c r="U67" s="42"/>
+      <c r="V67" s="42"/>
+      <c r="W67" s="43"/>
       <c r="X67" s="25"/>
       <c r="Y67" s="26"/>
       <c r="Z67" s="26"/>
@@ -6327,434 +6349,149 @@
       <c r="AJ67" s="28"/>
       <c r="AK67" s="28"/>
       <c r="AL67" s="29"/>
-      <c r="AM67" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN67" s="22"/>
-      <c r="AO67" s="22"/>
-      <c r="AP67" s="22"/>
-      <c r="AQ67" s="22"/>
-      <c r="AR67" s="22"/>
-      <c r="AS67" s="22"/>
-      <c r="AT67" s="22"/>
-      <c r="AU67" s="23"/>
-      <c r="AV67" s="71"/>
-      <c r="AW67" s="71"/>
-      <c r="AX67" s="71"/>
-      <c r="AY67" s="71"/>
-      <c r="AZ67" s="71"/>
-      <c r="BA67" s="71"/>
-      <c r="BB67" s="71"/>
-      <c r="BC67" s="71"/>
-      <c r="BD67" s="71"/>
-      <c r="BE67" s="71"/>
-      <c r="BF67" s="71"/>
-      <c r="BG67" s="71"/>
-      <c r="BH67" s="63"/>
+      <c r="AM67" s="46"/>
+      <c r="AN67" s="47"/>
+      <c r="AO67" s="47"/>
+      <c r="AP67" s="47"/>
+      <c r="AQ67" s="47"/>
+      <c r="AR67" s="47"/>
+      <c r="AS67" s="47"/>
+      <c r="AT67" s="47"/>
+      <c r="AU67" s="47"/>
+      <c r="AV67" s="47"/>
+      <c r="AW67" s="47"/>
+      <c r="AX67" s="47"/>
+      <c r="AY67" s="47"/>
+      <c r="AZ67" s="47"/>
+      <c r="BA67" s="47"/>
+      <c r="BB67" s="47"/>
+      <c r="BC67" s="47"/>
+      <c r="BD67" s="47"/>
+      <c r="BE67" s="47"/>
+      <c r="BF67" s="47"/>
+      <c r="BG67" s="47"/>
+      <c r="BH67" s="70"/>
     </row>
-    <row r="68" spans="2:60" ht="13.8">
-      <c r="B68" s="32"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="253"/>
-      <c r="K68" s="253"/>
-      <c r="L68" s="253"/>
-      <c r="M68" s="253"/>
-      <c r="N68" s="253"/>
-      <c r="O68" s="253"/>
-      <c r="P68" s="253"/>
-      <c r="Q68" s="253"/>
-      <c r="R68" s="253"/>
-      <c r="S68" s="254"/>
-      <c r="T68" s="213" t="s">
-        <v>41</v>
-      </c>
-      <c r="U68" s="214"/>
-      <c r="V68" s="214"/>
-      <c r="W68" s="215"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="26"/>
-      <c r="Z68" s="26"/>
-      <c r="AA68" s="26"/>
-      <c r="AB68" s="26"/>
-      <c r="AC68" s="27"/>
-      <c r="AD68" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE68" s="37"/>
-      <c r="AF68" s="37"/>
-      <c r="AG68" s="38"/>
-      <c r="AH68" s="28"/>
-      <c r="AI68" s="28"/>
-      <c r="AJ68" s="28"/>
-      <c r="AK68" s="28"/>
-      <c r="AL68" s="29"/>
-      <c r="AM68" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN68" s="42"/>
-      <c r="AO68" s="42"/>
-      <c r="AP68" s="42"/>
-      <c r="AQ68" s="42"/>
-      <c r="AR68" s="204"/>
-      <c r="AS68" s="205"/>
-      <c r="AT68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU68" s="206"/>
-      <c r="AV68" s="207"/>
-      <c r="AW68" s="212" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX68" s="212"/>
-      <c r="AY68" s="212"/>
-      <c r="AZ68" s="212"/>
-      <c r="BA68" s="212"/>
-      <c r="BB68" s="212"/>
-      <c r="BC68" s="212"/>
-      <c r="BD68" s="204"/>
-      <c r="BE68" s="205"/>
-      <c r="BF68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG68" s="206"/>
-      <c r="BH68" s="207"/>
-    </row>
-    <row r="69" spans="2:60" ht="13.8">
-      <c r="B69" s="32"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="253"/>
-      <c r="K69" s="253"/>
-      <c r="L69" s="253"/>
-      <c r="M69" s="253"/>
-      <c r="N69" s="253"/>
-      <c r="O69" s="253"/>
-      <c r="P69" s="253"/>
-      <c r="Q69" s="253"/>
-      <c r="R69" s="253"/>
-      <c r="S69" s="254"/>
-      <c r="T69" s="213" t="s">
-        <v>41</v>
-      </c>
-      <c r="U69" s="214"/>
-      <c r="V69" s="214"/>
-      <c r="W69" s="215"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="26"/>
-      <c r="Z69" s="26"/>
-      <c r="AA69" s="26"/>
-      <c r="AB69" s="26"/>
-      <c r="AC69" s="27"/>
-      <c r="AD69" s="258" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE69" s="259"/>
-      <c r="AF69" s="259"/>
-      <c r="AG69" s="260"/>
-      <c r="AH69" s="28"/>
-      <c r="AI69" s="28"/>
-      <c r="AJ69" s="28"/>
-      <c r="AK69" s="28"/>
-      <c r="AL69" s="29"/>
-      <c r="AM69" s="87" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN69" s="28"/>
-      <c r="AO69" s="28"/>
-      <c r="AP69" s="28"/>
-      <c r="AQ69" s="28"/>
-      <c r="AR69" s="209"/>
-      <c r="AS69" s="209"/>
-      <c r="AT69" s="210"/>
-      <c r="AU69" s="210"/>
-      <c r="AV69" s="210"/>
-      <c r="AW69" s="210"/>
-      <c r="AX69" s="210"/>
-      <c r="AY69" s="210"/>
-      <c r="AZ69" s="210"/>
-      <c r="BA69" s="210"/>
-      <c r="BB69" s="210"/>
-      <c r="BC69" s="210"/>
-      <c r="BD69" s="209"/>
-      <c r="BE69" s="209"/>
-      <c r="BF69" s="210"/>
-      <c r="BG69" s="210"/>
-      <c r="BH69" s="211"/>
-    </row>
-    <row r="70" spans="2:60">
-      <c r="B70" s="32"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="253"/>
-      <c r="K70" s="253"/>
-      <c r="L70" s="253"/>
-      <c r="M70" s="253"/>
-      <c r="N70" s="253"/>
-      <c r="O70" s="253"/>
-      <c r="P70" s="253"/>
-      <c r="Q70" s="253"/>
-      <c r="R70" s="253"/>
-      <c r="S70" s="254"/>
-      <c r="T70" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="U70" s="42"/>
-      <c r="V70" s="42"/>
-      <c r="W70" s="43"/>
-      <c r="X70" s="25"/>
-      <c r="Y70" s="26"/>
-      <c r="Z70" s="26"/>
-      <c r="AA70" s="26"/>
-      <c r="AB70" s="26"/>
-      <c r="AC70" s="27"/>
-      <c r="AD70" s="258" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE70" s="259"/>
-      <c r="AF70" s="259"/>
-      <c r="AG70" s="260"/>
-      <c r="AH70" s="28"/>
-      <c r="AI70" s="28"/>
-      <c r="AJ70" s="28"/>
-      <c r="AK70" s="28"/>
-      <c r="AL70" s="29"/>
-      <c r="AM70" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="AN70" s="45"/>
-      <c r="AO70" s="45"/>
-      <c r="AP70" s="45"/>
-      <c r="AQ70" s="45"/>
-      <c r="AR70" s="45"/>
-      <c r="AS70" s="45"/>
-      <c r="AT70" s="45"/>
-      <c r="AU70" s="45"/>
-      <c r="AV70" s="45"/>
-      <c r="AW70" s="45"/>
-      <c r="AX70" s="45"/>
-      <c r="AY70" s="45"/>
-      <c r="AZ70" s="45"/>
-      <c r="BA70" s="45"/>
-      <c r="BB70" s="45"/>
-      <c r="BC70" s="45"/>
-      <c r="BD70" s="45"/>
-      <c r="BE70" s="45"/>
-      <c r="BF70" s="45"/>
-      <c r="BG70" s="45"/>
-      <c r="BH70" s="69"/>
-    </row>
-    <row r="71" spans="2:60">
-      <c r="B71" s="34"/>
-      <c r="C71" s="35"/>
-      <c r="D71" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="24"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="39"/>
-      <c r="O71" s="39"/>
-      <c r="P71" s="39"/>
-      <c r="Q71" s="39"/>
-      <c r="R71" s="39"/>
-      <c r="S71" s="40"/>
-      <c r="T71" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="U71" s="42"/>
-      <c r="V71" s="42"/>
-      <c r="W71" s="43"/>
-      <c r="X71" s="25"/>
-      <c r="Y71" s="26"/>
-      <c r="Z71" s="26"/>
-      <c r="AA71" s="26"/>
-      <c r="AB71" s="26"/>
-      <c r="AC71" s="27"/>
-      <c r="AD71" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE71" s="37"/>
-      <c r="AF71" s="37"/>
-      <c r="AG71" s="38"/>
-      <c r="AH71" s="28"/>
-      <c r="AI71" s="28"/>
-      <c r="AJ71" s="28"/>
-      <c r="AK71" s="28"/>
-      <c r="AL71" s="29"/>
-      <c r="AM71" s="46"/>
-      <c r="AN71" s="47"/>
-      <c r="AO71" s="47"/>
-      <c r="AP71" s="47"/>
-      <c r="AQ71" s="47"/>
-      <c r="AR71" s="47"/>
-      <c r="AS71" s="47"/>
-      <c r="AT71" s="47"/>
-      <c r="AU71" s="47"/>
-      <c r="AV71" s="47"/>
-      <c r="AW71" s="47"/>
-      <c r="AX71" s="47"/>
-      <c r="AY71" s="47"/>
-      <c r="AZ71" s="47"/>
-      <c r="BA71" s="47"/>
-      <c r="BB71" s="47"/>
-      <c r="BC71" s="47"/>
-      <c r="BD71" s="47"/>
-      <c r="BE71" s="47"/>
-      <c r="BF71" s="47"/>
-      <c r="BG71" s="47"/>
-      <c r="BH71" s="70"/>
-    </row>
-    <row r="72" spans="2:60">
-      <c r="B72" s="101" t="s">
+    <row r="68" spans="2:60">
+      <c r="B68" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="102"/>
-      <c r="D72" s="102"/>
-      <c r="E72" s="102"/>
-      <c r="F72" s="102"/>
-      <c r="G72" s="102"/>
-      <c r="H72" s="102"/>
-      <c r="I72" s="102"/>
-      <c r="J72" s="102"/>
-      <c r="K72" s="102"/>
-      <c r="L72" s="102"/>
-      <c r="M72" s="102"/>
-      <c r="N72" s="102"/>
-      <c r="O72" s="102"/>
-      <c r="P72" s="102"/>
-      <c r="Q72" s="102"/>
-      <c r="R72" s="102"/>
-      <c r="S72" s="102"/>
-      <c r="T72" s="102"/>
-      <c r="U72" s="102"/>
-      <c r="V72" s="102"/>
-      <c r="W72" s="102"/>
-      <c r="X72" s="102"/>
-      <c r="Y72" s="102"/>
-      <c r="Z72" s="102"/>
-      <c r="AA72" s="102"/>
-      <c r="AB72" s="102"/>
-      <c r="AC72" s="102"/>
-      <c r="AD72" s="102"/>
-      <c r="AE72" s="102"/>
-      <c r="AF72" s="102"/>
-      <c r="AG72" s="102"/>
-      <c r="AH72" s="102"/>
-      <c r="AI72" s="102"/>
-      <c r="AJ72" s="102"/>
-      <c r="AK72" s="102"/>
-      <c r="AL72" s="102"/>
-      <c r="AM72" s="102"/>
-      <c r="AN72" s="102"/>
-      <c r="AO72" s="102"/>
-      <c r="AP72" s="102"/>
-      <c r="AQ72" s="102"/>
-      <c r="AR72" s="102"/>
-      <c r="AS72" s="102"/>
-      <c r="AT72" s="102"/>
-      <c r="AU72" s="102"/>
-      <c r="AV72" s="102"/>
-      <c r="AW72" s="102"/>
-      <c r="AX72" s="102"/>
-      <c r="AY72" s="102"/>
-      <c r="AZ72" s="102"/>
-      <c r="BA72" s="102"/>
-      <c r="BB72" s="102"/>
-      <c r="BC72" s="102"/>
-      <c r="BD72" s="102"/>
-      <c r="BE72" s="102"/>
-      <c r="BF72" s="102"/>
-      <c r="BG72" s="102"/>
-      <c r="BH72" s="164"/>
+      <c r="C68" s="102"/>
+      <c r="D68" s="102"/>
+      <c r="E68" s="102"/>
+      <c r="F68" s="102"/>
+      <c r="G68" s="102"/>
+      <c r="H68" s="102"/>
+      <c r="I68" s="102"/>
+      <c r="J68" s="102"/>
+      <c r="K68" s="102"/>
+      <c r="L68" s="102"/>
+      <c r="M68" s="102"/>
+      <c r="N68" s="102"/>
+      <c r="O68" s="102"/>
+      <c r="P68" s="102"/>
+      <c r="Q68" s="102"/>
+      <c r="R68" s="102"/>
+      <c r="S68" s="102"/>
+      <c r="T68" s="102"/>
+      <c r="U68" s="102"/>
+      <c r="V68" s="102"/>
+      <c r="W68" s="102"/>
+      <c r="X68" s="102"/>
+      <c r="Y68" s="102"/>
+      <c r="Z68" s="102"/>
+      <c r="AA68" s="102"/>
+      <c r="AB68" s="102"/>
+      <c r="AC68" s="102"/>
+      <c r="AD68" s="102"/>
+      <c r="AE68" s="102"/>
+      <c r="AF68" s="102"/>
+      <c r="AG68" s="102"/>
+      <c r="AH68" s="102"/>
+      <c r="AI68" s="102"/>
+      <c r="AJ68" s="102"/>
+      <c r="AK68" s="102"/>
+      <c r="AL68" s="102"/>
+      <c r="AM68" s="102"/>
+      <c r="AN68" s="102"/>
+      <c r="AO68" s="102"/>
+      <c r="AP68" s="102"/>
+      <c r="AQ68" s="102"/>
+      <c r="AR68" s="102"/>
+      <c r="AS68" s="102"/>
+      <c r="AT68" s="102"/>
+      <c r="AU68" s="102"/>
+      <c r="AV68" s="102"/>
+      <c r="AW68" s="102"/>
+      <c r="AX68" s="102"/>
+      <c r="AY68" s="102"/>
+      <c r="AZ68" s="102"/>
+      <c r="BA68" s="102"/>
+      <c r="BB68" s="102"/>
+      <c r="BC68" s="102"/>
+      <c r="BD68" s="102"/>
+      <c r="BE68" s="102"/>
+      <c r="BF68" s="102"/>
+      <c r="BG68" s="102"/>
+      <c r="BH68" s="164"/>
     </row>
   </sheetData>
-  <mergeCells count="1080">
-    <mergeCell ref="V63:AE64"/>
-    <mergeCell ref="AF63:AL64"/>
-    <mergeCell ref="AZ65:BC66"/>
-    <mergeCell ref="BD65:BH66"/>
-    <mergeCell ref="AS64:AW64"/>
-    <mergeCell ref="BB54:BC54"/>
-    <mergeCell ref="BB59:BC59"/>
+  <mergeCells count="1000">
+    <mergeCell ref="V59:AE60"/>
+    <mergeCell ref="AF59:AL60"/>
+    <mergeCell ref="AZ61:BC62"/>
+    <mergeCell ref="BD61:BH62"/>
+    <mergeCell ref="AS60:AW60"/>
+    <mergeCell ref="BB55:BC55"/>
     <mergeCell ref="AZ12:BA14"/>
     <mergeCell ref="D4:R5"/>
     <mergeCell ref="D7:R8"/>
-    <mergeCell ref="T67:W67"/>
-    <mergeCell ref="T68:W68"/>
-    <mergeCell ref="T69:W69"/>
-    <mergeCell ref="T70:W70"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="T64:W64"/>
+    <mergeCell ref="T65:W65"/>
+    <mergeCell ref="T66:W66"/>
+    <mergeCell ref="J62:S62"/>
+    <mergeCell ref="J63:S63"/>
+    <mergeCell ref="J64:S64"/>
+    <mergeCell ref="J65:S65"/>
     <mergeCell ref="J66:S66"/>
-    <mergeCell ref="J67:S67"/>
-    <mergeCell ref="J68:S68"/>
-    <mergeCell ref="J69:S69"/>
-    <mergeCell ref="J70:S70"/>
     <mergeCell ref="AQ12:AU14"/>
     <mergeCell ref="AV12:AW14"/>
     <mergeCell ref="AX12:AY14"/>
     <mergeCell ref="BG15:BH15"/>
     <mergeCell ref="AM16:AN16"/>
     <mergeCell ref="AO16:AP16"/>
-    <mergeCell ref="AS65:AW66"/>
+    <mergeCell ref="AS61:AW62"/>
+    <mergeCell ref="AD62:AG62"/>
+    <mergeCell ref="AD63:AG63"/>
+    <mergeCell ref="AD64:AG64"/>
+    <mergeCell ref="AD65:AG65"/>
     <mergeCell ref="AD66:AG66"/>
-    <mergeCell ref="AD67:AG67"/>
-    <mergeCell ref="AD68:AG68"/>
-    <mergeCell ref="AD69:AG69"/>
-    <mergeCell ref="AD70:AG70"/>
-    <mergeCell ref="V61:AL61"/>
-    <mergeCell ref="V62:AL62"/>
-    <mergeCell ref="AM61:AN61"/>
-    <mergeCell ref="AO61:AP61"/>
-    <mergeCell ref="AJ27:AL27"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="AV61:AW61"/>
-    <mergeCell ref="AX61:AY61"/>
-    <mergeCell ref="AQ61:AR61"/>
-    <mergeCell ref="AT61:AU61"/>
+    <mergeCell ref="V57:AL57"/>
+    <mergeCell ref="V58:AL58"/>
+    <mergeCell ref="AM57:AN57"/>
+    <mergeCell ref="AO57:AP57"/>
+    <mergeCell ref="AV57:AW57"/>
+    <mergeCell ref="AX57:AY57"/>
+    <mergeCell ref="AQ57:AR57"/>
+    <mergeCell ref="AT57:AU57"/>
     <mergeCell ref="AG20:AI20"/>
-    <mergeCell ref="V35:AL35"/>
+    <mergeCell ref="V33:AL33"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AG23:AI23"/>
     <mergeCell ref="AJ23:AL23"/>
     <mergeCell ref="AD13:AF13"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="AA37:AC37"/>
-    <mergeCell ref="AD37:AF37"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AF35"/>
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="AJ14:AL14"/>
-    <mergeCell ref="AW68:BC68"/>
-    <mergeCell ref="BD68:BE68"/>
-    <mergeCell ref="BG68:BH68"/>
-    <mergeCell ref="T66:W66"/>
+    <mergeCell ref="AW64:BC64"/>
+    <mergeCell ref="BD64:BE64"/>
+    <mergeCell ref="BG64:BH64"/>
+    <mergeCell ref="T62:W62"/>
     <mergeCell ref="AZ10:BF10"/>
     <mergeCell ref="AZ11:BF11"/>
     <mergeCell ref="AM6:AP7"/>
@@ -6781,52 +6518,51 @@
     <mergeCell ref="BB23:BC23"/>
     <mergeCell ref="AH6:AL6"/>
     <mergeCell ref="T10:U10"/>
-    <mergeCell ref="AX65:AY66"/>
+    <mergeCell ref="AX61:AY62"/>
     <mergeCell ref="AJ13:AL13"/>
-    <mergeCell ref="BD64:BH64"/>
+    <mergeCell ref="BD60:BH60"/>
     <mergeCell ref="AH7:AL7"/>
-    <mergeCell ref="AR68:AS68"/>
-    <mergeCell ref="AU68:AV68"/>
-    <mergeCell ref="AO64:AR64"/>
-    <mergeCell ref="AO65:AR66"/>
-    <mergeCell ref="AM69:AQ69"/>
-    <mergeCell ref="AR69:BH69"/>
-    <mergeCell ref="BB61:BC61"/>
-    <mergeCell ref="BE61:BF61"/>
-    <mergeCell ref="BB62:BC62"/>
-    <mergeCell ref="BE62:BF62"/>
-    <mergeCell ref="BB63:BC63"/>
-    <mergeCell ref="BE63:BF63"/>
-    <mergeCell ref="AO63:AP63"/>
-    <mergeCell ref="AV63:AW63"/>
-    <mergeCell ref="AX63:AY63"/>
-    <mergeCell ref="BG61:BH61"/>
-    <mergeCell ref="AM62:AN62"/>
-    <mergeCell ref="AO62:AP62"/>
-    <mergeCell ref="AV62:AW62"/>
-    <mergeCell ref="AX62:AY62"/>
-    <mergeCell ref="BG62:BH62"/>
+    <mergeCell ref="AR64:AS64"/>
+    <mergeCell ref="AU64:AV64"/>
+    <mergeCell ref="AO60:AR60"/>
+    <mergeCell ref="AO61:AR62"/>
+    <mergeCell ref="AM65:AQ65"/>
+    <mergeCell ref="AR65:BH65"/>
+    <mergeCell ref="BB57:BC57"/>
+    <mergeCell ref="BE57:BF57"/>
+    <mergeCell ref="BB58:BC58"/>
+    <mergeCell ref="BE58:BF58"/>
+    <mergeCell ref="BB59:BC59"/>
+    <mergeCell ref="BE59:BF59"/>
+    <mergeCell ref="AO59:AP59"/>
+    <mergeCell ref="AV59:AW59"/>
+    <mergeCell ref="AX59:AY59"/>
+    <mergeCell ref="BG57:BH57"/>
+    <mergeCell ref="AM58:AN58"/>
+    <mergeCell ref="AO58:AP58"/>
+    <mergeCell ref="AV58:AW58"/>
+    <mergeCell ref="AX58:AY58"/>
+    <mergeCell ref="BG58:BH58"/>
     <mergeCell ref="BG11:BH11"/>
     <mergeCell ref="BE16:BF16"/>
     <mergeCell ref="BB17:BC17"/>
-    <mergeCell ref="AX64:AY64"/>
+    <mergeCell ref="AX60:AY60"/>
     <mergeCell ref="BE17:BF17"/>
-    <mergeCell ref="AZ64:BC64"/>
+    <mergeCell ref="AZ60:BC60"/>
     <mergeCell ref="AJ12:AL12"/>
     <mergeCell ref="AG21:AI21"/>
     <mergeCell ref="AJ21:AL21"/>
-    <mergeCell ref="AT62:AU62"/>
-    <mergeCell ref="AQ63:AR63"/>
+    <mergeCell ref="AT58:AU58"/>
+    <mergeCell ref="AQ59:AR59"/>
     <mergeCell ref="B1:P2"/>
-    <mergeCell ref="L29:Q29"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="S29:X29"/>
-    <mergeCell ref="R31:X31"/>
-    <mergeCell ref="Z29:AE29"/>
-    <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="AT63:AU63"/>
+    <mergeCell ref="L27:Q27"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="S27:X27"/>
+    <mergeCell ref="R29:X29"/>
+    <mergeCell ref="Z27:AE27"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="AT59:AU59"/>
     <mergeCell ref="BB15:BC15"/>
-    <mergeCell ref="T28:U28"/>
     <mergeCell ref="AH3:AL3"/>
     <mergeCell ref="AH4:AL4"/>
     <mergeCell ref="AH5:AL5"/>
@@ -6912,13 +6648,10 @@
     <mergeCell ref="BB20:BC20"/>
     <mergeCell ref="BE20:BF20"/>
     <mergeCell ref="D16:Q16"/>
-    <mergeCell ref="V28:W28"/>
     <mergeCell ref="T23:U23"/>
     <mergeCell ref="D10:Q10"/>
     <mergeCell ref="T17:U17"/>
     <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R28:S28"/>
     <mergeCell ref="R17:S17"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:C10"/>
@@ -6968,48 +6701,29 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="AA28:AC28"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="X25:Z25"/>
     <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="Y30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
     <mergeCell ref="AD25:AF25"/>
     <mergeCell ref="AG25:AI25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J31"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J29"/>
     <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="D27:Q27"/>
-    <mergeCell ref="D28:Q28"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="AG36:AI36"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:Q38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="AA38:AC38"/>
-    <mergeCell ref="AD38:AF38"/>
-    <mergeCell ref="AG38:AI38"/>
-    <mergeCell ref="B33:J34"/>
-    <mergeCell ref="K33:Q34"/>
-    <mergeCell ref="R33:X34"/>
-    <mergeCell ref="Y33:AE34"/>
-    <mergeCell ref="AF33:AL34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="AG34:AI34"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:O30"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="D36:Q36"/>
     <mergeCell ref="R36:S36"/>
@@ -7017,6 +6731,20 @@
     <mergeCell ref="V36:W36"/>
     <mergeCell ref="X36:Z36"/>
     <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AG36:AI36"/>
+    <mergeCell ref="B31:J32"/>
+    <mergeCell ref="K31:Q32"/>
+    <mergeCell ref="R31:X32"/>
+    <mergeCell ref="Y31:AE32"/>
+    <mergeCell ref="AF31:AL32"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:Q34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="AA34:AC34"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -7028,14 +6756,9 @@
     <mergeCell ref="AD15:AF15"/>
     <mergeCell ref="AD24:AF24"/>
     <mergeCell ref="AA18:AC18"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AF27"/>
     <mergeCell ref="X23:Z23"/>
     <mergeCell ref="AA23:AC23"/>
     <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="T12:U12"/>
@@ -7049,6 +6772,26 @@
     <mergeCell ref="AD14:AF14"/>
     <mergeCell ref="T26:U26"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="AA37:AC37"/>
+    <mergeCell ref="AD37:AF37"/>
+    <mergeCell ref="AG37:AI37"/>
+    <mergeCell ref="AJ37:AL37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:Q38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="AA38:AC38"/>
+    <mergeCell ref="AD38:AF38"/>
+    <mergeCell ref="AG38:AI38"/>
+    <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D39:Q39"/>
     <mergeCell ref="R39:S39"/>
@@ -7089,6 +6832,22 @@
     <mergeCell ref="AD42:AF42"/>
     <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:Q45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="T45:U45"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="X45:Z45"/>
+    <mergeCell ref="AA45:AC45"/>
+    <mergeCell ref="AD45:AF45"/>
+    <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AJ45:AL45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:Q46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="V46:W46"/>
+    <mergeCell ref="X46:Z46"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="D43:Q43"/>
     <mergeCell ref="R43:S43"/>
@@ -7105,74 +6864,38 @@
     <mergeCell ref="T44:U44"/>
     <mergeCell ref="V44:W44"/>
     <mergeCell ref="X44:Z44"/>
-    <mergeCell ref="AA44:AC44"/>
-    <mergeCell ref="AD44:AF44"/>
-    <mergeCell ref="AG44:AI44"/>
-    <mergeCell ref="AJ44:AL44"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:Q47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="V47:W47"/>
-    <mergeCell ref="X47:Z47"/>
-    <mergeCell ref="AA47:AC47"/>
-    <mergeCell ref="AD47:AF47"/>
-    <mergeCell ref="AG47:AI47"/>
-    <mergeCell ref="AJ47:AL47"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="T54:V54"/>
+    <mergeCell ref="W54:X54"/>
+    <mergeCell ref="Y54:Z54"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="G51:J53"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="R55:X56"/>
+    <mergeCell ref="Y55:AE56"/>
+    <mergeCell ref="AF55:AL56"/>
+    <mergeCell ref="B57:M57"/>
+    <mergeCell ref="B55:J56"/>
+    <mergeCell ref="Y52:AE52"/>
+    <mergeCell ref="AF52:AL52"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="D48:Q48"/>
     <mergeCell ref="R48:S48"/>
     <mergeCell ref="T48:U48"/>
     <mergeCell ref="V48:W48"/>
     <mergeCell ref="X48:Z48"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:Q45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="T45:U45"/>
-    <mergeCell ref="V45:W45"/>
-    <mergeCell ref="X45:Z45"/>
-    <mergeCell ref="AA45:AC45"/>
-    <mergeCell ref="AD45:AF45"/>
-    <mergeCell ref="AG45:AI45"/>
-    <mergeCell ref="AJ45:AL45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:Q46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="V46:W46"/>
-    <mergeCell ref="X46:Z46"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="T58:V58"/>
-    <mergeCell ref="W58:X58"/>
-    <mergeCell ref="Y58:Z58"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="G55:J57"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="R59:X60"/>
-    <mergeCell ref="Y59:AE60"/>
-    <mergeCell ref="AF59:AL60"/>
-    <mergeCell ref="B61:M61"/>
-    <mergeCell ref="B59:J60"/>
-    <mergeCell ref="Y56:AE56"/>
-    <mergeCell ref="AF56:AL56"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:Q50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="V50:W50"/>
-    <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="AA50:AC50"/>
-    <mergeCell ref="AD50:AF50"/>
-    <mergeCell ref="AG50:AI50"/>
-    <mergeCell ref="AJ50:AL50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="AG51:AI51"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="X51:Z51"/>
-    <mergeCell ref="AA51:AC51"/>
-    <mergeCell ref="AD51:AF51"/>
-    <mergeCell ref="AJ51:AL51"/>
+    <mergeCell ref="AA48:AC48"/>
+    <mergeCell ref="AD48:AF48"/>
+    <mergeCell ref="AG48:AI48"/>
+    <mergeCell ref="AJ48:AL48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="AG49:AI49"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="X49:Z49"/>
+    <mergeCell ref="AA49:AC49"/>
+    <mergeCell ref="AD49:AF49"/>
+    <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AV16:AW16"/>
     <mergeCell ref="AX16:AY16"/>
     <mergeCell ref="BG16:BH16"/>
@@ -7254,21 +6977,6 @@
     <mergeCell ref="BE25:BF25"/>
     <mergeCell ref="BE23:BF23"/>
     <mergeCell ref="AZ25:BA25"/>
-    <mergeCell ref="BG28:BH28"/>
-    <mergeCell ref="AM27:AN27"/>
-    <mergeCell ref="AO27:AP27"/>
-    <mergeCell ref="AV27:AW27"/>
-    <mergeCell ref="AX27:AY27"/>
-    <mergeCell ref="AQ27:AR27"/>
-    <mergeCell ref="AT27:AU27"/>
-    <mergeCell ref="AQ28:AR28"/>
-    <mergeCell ref="AT28:AU28"/>
-    <mergeCell ref="BB27:BC27"/>
-    <mergeCell ref="BE27:BF27"/>
-    <mergeCell ref="BB28:BC28"/>
-    <mergeCell ref="BE28:BF28"/>
-    <mergeCell ref="AZ27:BA27"/>
-    <mergeCell ref="AZ28:BA28"/>
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="AO26:AP26"/>
     <mergeCell ref="AV26:AW26"/>
@@ -7277,31 +6985,50 @@
     <mergeCell ref="AQ26:AR26"/>
     <mergeCell ref="AT26:AU26"/>
     <mergeCell ref="BE26:BF26"/>
-    <mergeCell ref="BG27:BH27"/>
     <mergeCell ref="BB26:BC26"/>
     <mergeCell ref="AZ26:BA26"/>
-    <mergeCell ref="BG29:BH29"/>
-    <mergeCell ref="AM29:AN29"/>
-    <mergeCell ref="AO29:AP29"/>
-    <mergeCell ref="AV29:AW29"/>
-    <mergeCell ref="AX29:AY29"/>
-    <mergeCell ref="AQ29:AR29"/>
-    <mergeCell ref="AT29:AU29"/>
-    <mergeCell ref="BB29:BC29"/>
-    <mergeCell ref="BE29:BF29"/>
-    <mergeCell ref="AZ29:BA29"/>
-    <mergeCell ref="AM30:AN31"/>
-    <mergeCell ref="AO30:AP31"/>
-    <mergeCell ref="AQ30:AR31"/>
-    <mergeCell ref="AS30:AS31"/>
-    <mergeCell ref="AT30:AU31"/>
-    <mergeCell ref="AV30:AW31"/>
-    <mergeCell ref="AX30:AY31"/>
-    <mergeCell ref="AZ30:BA31"/>
-    <mergeCell ref="BB30:BC31"/>
-    <mergeCell ref="BD30:BD31"/>
-    <mergeCell ref="BE30:BF31"/>
-    <mergeCell ref="BG30:BH31"/>
+    <mergeCell ref="BG27:BH27"/>
+    <mergeCell ref="AM27:AN27"/>
+    <mergeCell ref="AO27:AP27"/>
+    <mergeCell ref="AV27:AW27"/>
+    <mergeCell ref="AX27:AY27"/>
+    <mergeCell ref="AQ27:AR27"/>
+    <mergeCell ref="AT27:AU27"/>
+    <mergeCell ref="BB27:BC27"/>
+    <mergeCell ref="BE27:BF27"/>
+    <mergeCell ref="AZ27:BA27"/>
+    <mergeCell ref="AM28:AN29"/>
+    <mergeCell ref="AO28:AP29"/>
+    <mergeCell ref="AQ28:AR29"/>
+    <mergeCell ref="AS28:AS29"/>
+    <mergeCell ref="AT28:AU29"/>
+    <mergeCell ref="AV28:AW29"/>
+    <mergeCell ref="AX28:AY29"/>
+    <mergeCell ref="AZ28:BA29"/>
+    <mergeCell ref="BB28:BC29"/>
+    <mergeCell ref="BD28:BD29"/>
+    <mergeCell ref="BE28:BF29"/>
+    <mergeCell ref="BG28:BH29"/>
+    <mergeCell ref="BG30:BH30"/>
+    <mergeCell ref="AM31:AN31"/>
+    <mergeCell ref="AO31:AP31"/>
+    <mergeCell ref="AV31:AW31"/>
+    <mergeCell ref="AX31:AY31"/>
+    <mergeCell ref="BG31:BH31"/>
+    <mergeCell ref="AM30:AN30"/>
+    <mergeCell ref="AO30:AP30"/>
+    <mergeCell ref="AV30:AW30"/>
+    <mergeCell ref="AX30:AY30"/>
+    <mergeCell ref="AQ30:AR30"/>
+    <mergeCell ref="AT30:AU30"/>
+    <mergeCell ref="AQ31:AR31"/>
+    <mergeCell ref="AT31:AU31"/>
+    <mergeCell ref="BB30:BC30"/>
+    <mergeCell ref="BE30:BF30"/>
+    <mergeCell ref="BB31:BC31"/>
+    <mergeCell ref="BE31:BF31"/>
+    <mergeCell ref="AZ30:BA30"/>
+    <mergeCell ref="AZ31:BA31"/>
     <mergeCell ref="BG32:BH32"/>
     <mergeCell ref="AM33:AN33"/>
     <mergeCell ref="AO33:AP33"/>
@@ -7462,6 +7189,7 @@
     <mergeCell ref="BE47:BF47"/>
     <mergeCell ref="AZ46:BA46"/>
     <mergeCell ref="AZ47:BA47"/>
+    <mergeCell ref="AZ50:BA50"/>
     <mergeCell ref="BG48:BH48"/>
     <mergeCell ref="AM49:AN49"/>
     <mergeCell ref="AO49:AP49"/>
@@ -7482,130 +7210,81 @@
     <mergeCell ref="BE49:BF49"/>
     <mergeCell ref="AZ48:BA48"/>
     <mergeCell ref="AZ49:BA49"/>
-    <mergeCell ref="BB53:BC53"/>
-    <mergeCell ref="BE53:BF53"/>
-    <mergeCell ref="AZ52:BA52"/>
-    <mergeCell ref="AZ53:BA53"/>
-    <mergeCell ref="BG50:BH50"/>
+    <mergeCell ref="B68:BH68"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AF8"/>
+    <mergeCell ref="AM64:AQ64"/>
+    <mergeCell ref="AM61:AN62"/>
+    <mergeCell ref="AM60:AN60"/>
+    <mergeCell ref="BG59:BH59"/>
+    <mergeCell ref="AM59:AN59"/>
+    <mergeCell ref="E33:U33"/>
+    <mergeCell ref="BG55:BH55"/>
+    <mergeCell ref="AM56:AN56"/>
+    <mergeCell ref="AO56:AP56"/>
+    <mergeCell ref="AV56:AW56"/>
+    <mergeCell ref="AX56:AY56"/>
+    <mergeCell ref="BG56:BH56"/>
+    <mergeCell ref="AM55:AN55"/>
+    <mergeCell ref="AO55:AP55"/>
+    <mergeCell ref="AA54:AC54"/>
+    <mergeCell ref="AD54:AE54"/>
+    <mergeCell ref="AF54:AH54"/>
+    <mergeCell ref="AI54:AJ54"/>
+    <mergeCell ref="AK54:AL54"/>
     <mergeCell ref="AM51:AN51"/>
     <mergeCell ref="AO51:AP51"/>
     <mergeCell ref="AV51:AW51"/>
     <mergeCell ref="AX51:AY51"/>
     <mergeCell ref="BG51:BH51"/>
+    <mergeCell ref="AR1:AY1"/>
+    <mergeCell ref="AZ1:BH1"/>
+    <mergeCell ref="AR2:BH2"/>
+    <mergeCell ref="B3:R3"/>
+    <mergeCell ref="B6:R6"/>
+    <mergeCell ref="BE54:BF54"/>
+    <mergeCell ref="AZ54:BA54"/>
+    <mergeCell ref="AT52:AU53"/>
+    <mergeCell ref="AV52:AW53"/>
+    <mergeCell ref="AX52:AY53"/>
+    <mergeCell ref="AZ52:BA53"/>
+    <mergeCell ref="BB52:BC53"/>
+    <mergeCell ref="BD52:BD53"/>
+    <mergeCell ref="BE52:BF53"/>
+    <mergeCell ref="BG52:BH53"/>
+    <mergeCell ref="AV54:AW54"/>
+    <mergeCell ref="AM52:AN53"/>
+    <mergeCell ref="AO52:AP53"/>
+    <mergeCell ref="AQ52:AR53"/>
+    <mergeCell ref="AS52:AS53"/>
+    <mergeCell ref="Q1:AQ2"/>
+    <mergeCell ref="BB51:BC51"/>
+    <mergeCell ref="BE51:BF51"/>
+    <mergeCell ref="AZ51:BA51"/>
+    <mergeCell ref="AM54:AN54"/>
+    <mergeCell ref="AO54:AP54"/>
+    <mergeCell ref="AX54:AY54"/>
+    <mergeCell ref="BG50:BH50"/>
+    <mergeCell ref="BE55:BF55"/>
+    <mergeCell ref="AZ55:BA55"/>
+    <mergeCell ref="AQ54:AR54"/>
+    <mergeCell ref="AT54:AU54"/>
+    <mergeCell ref="BB54:BC54"/>
+    <mergeCell ref="AG27:AL27"/>
+    <mergeCell ref="AF29:AL29"/>
+    <mergeCell ref="AD34:AF34"/>
+    <mergeCell ref="AJ25:AL25"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AF30:AH30"/>
+    <mergeCell ref="AM4:BH5"/>
     <mergeCell ref="AM50:AN50"/>
     <mergeCell ref="AO50:AP50"/>
     <mergeCell ref="AV50:AW50"/>
     <mergeCell ref="AX50:AY50"/>
     <mergeCell ref="AQ50:AR50"/>
     <mergeCell ref="AT50:AU50"/>
-    <mergeCell ref="AQ51:AR51"/>
-    <mergeCell ref="AT51:AU51"/>
     <mergeCell ref="BB50:BC50"/>
     <mergeCell ref="BE50:BF50"/>
-    <mergeCell ref="BB51:BC51"/>
-    <mergeCell ref="BE51:BF51"/>
-    <mergeCell ref="AZ50:BA50"/>
-    <mergeCell ref="AZ51:BA51"/>
-    <mergeCell ref="B72:BH72"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AF8"/>
-    <mergeCell ref="AM68:AQ68"/>
-    <mergeCell ref="AM65:AN66"/>
-    <mergeCell ref="AM64:AN64"/>
-    <mergeCell ref="BG63:BH63"/>
-    <mergeCell ref="AM63:AN63"/>
-    <mergeCell ref="E35:U35"/>
-    <mergeCell ref="BG59:BH59"/>
-    <mergeCell ref="AM60:AN60"/>
-    <mergeCell ref="AO60:AP60"/>
-    <mergeCell ref="AV60:AW60"/>
-    <mergeCell ref="AX60:AY60"/>
-    <mergeCell ref="BG60:BH60"/>
-    <mergeCell ref="AM59:AN59"/>
-    <mergeCell ref="AO59:AP59"/>
-    <mergeCell ref="AA58:AC58"/>
-    <mergeCell ref="AD58:AE58"/>
-    <mergeCell ref="AF58:AH58"/>
-    <mergeCell ref="AI58:AJ58"/>
-    <mergeCell ref="AK58:AL58"/>
-    <mergeCell ref="BG54:BH54"/>
-    <mergeCell ref="AM55:AN55"/>
-    <mergeCell ref="AO55:AP55"/>
-    <mergeCell ref="AV55:AW55"/>
-    <mergeCell ref="AX55:AY55"/>
-    <mergeCell ref="BG55:BH55"/>
-    <mergeCell ref="AM54:AN54"/>
-    <mergeCell ref="AO54:AP54"/>
-    <mergeCell ref="AV54:AW54"/>
-    <mergeCell ref="AX54:AY54"/>
-    <mergeCell ref="AR1:AY1"/>
-    <mergeCell ref="AZ1:BH1"/>
-    <mergeCell ref="AR2:BH2"/>
-    <mergeCell ref="B3:R3"/>
-    <mergeCell ref="B6:R6"/>
-    <mergeCell ref="BE58:BF58"/>
-    <mergeCell ref="AZ58:BA58"/>
-    <mergeCell ref="AT56:AU57"/>
-    <mergeCell ref="AV56:AW57"/>
-    <mergeCell ref="AX56:AY57"/>
-    <mergeCell ref="AZ56:BA57"/>
-    <mergeCell ref="BB56:BC57"/>
-    <mergeCell ref="BD56:BD57"/>
-    <mergeCell ref="BE56:BF57"/>
-    <mergeCell ref="BG56:BH57"/>
-    <mergeCell ref="AV58:AW58"/>
-    <mergeCell ref="AM56:AN57"/>
-    <mergeCell ref="AO56:AP57"/>
-    <mergeCell ref="AQ56:AR57"/>
-    <mergeCell ref="AS56:AS57"/>
-    <mergeCell ref="AQ54:AR54"/>
-    <mergeCell ref="AT54:AU54"/>
-    <mergeCell ref="Q1:AQ2"/>
-    <mergeCell ref="BE54:BF54"/>
-    <mergeCell ref="BB55:BC55"/>
-    <mergeCell ref="BE55:BF55"/>
-    <mergeCell ref="AZ54:BA54"/>
-    <mergeCell ref="AZ55:BA55"/>
-    <mergeCell ref="AM58:AN58"/>
-    <mergeCell ref="AO58:AP58"/>
-    <mergeCell ref="AX58:AY58"/>
-    <mergeCell ref="BG52:BH52"/>
-    <mergeCell ref="BE59:BF59"/>
-    <mergeCell ref="AZ59:BA59"/>
-    <mergeCell ref="AQ58:AR58"/>
-    <mergeCell ref="AT58:AU58"/>
-    <mergeCell ref="BB58:BC58"/>
-    <mergeCell ref="AG29:AL29"/>
-    <mergeCell ref="AF31:AL31"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="AD54:AF54"/>
-    <mergeCell ref="AG54:AI54"/>
-    <mergeCell ref="AJ54:AL54"/>
-    <mergeCell ref="AJ25:AL25"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AF32:AH32"/>
-    <mergeCell ref="AD28:AF28"/>
-    <mergeCell ref="AG28:AI28"/>
-    <mergeCell ref="AM4:BH5"/>
-    <mergeCell ref="AM53:AN53"/>
-    <mergeCell ref="AO53:AP53"/>
-    <mergeCell ref="AV53:AW53"/>
-    <mergeCell ref="AX53:AY53"/>
-    <mergeCell ref="BG53:BH53"/>
-    <mergeCell ref="AM52:AN52"/>
-    <mergeCell ref="AO52:AP52"/>
-    <mergeCell ref="AV52:AW52"/>
-    <mergeCell ref="AX52:AY52"/>
-    <mergeCell ref="AQ52:AR52"/>
-    <mergeCell ref="AT52:AU52"/>
-    <mergeCell ref="AQ53:AR53"/>
-    <mergeCell ref="AT53:AU53"/>
-    <mergeCell ref="BB52:BC52"/>
-    <mergeCell ref="BE52:BF52"/>
-    <mergeCell ref="AM28:AN28"/>
-    <mergeCell ref="AO28:AP28"/>
-    <mergeCell ref="AV28:AW28"/>
-    <mergeCell ref="AX28:AY28"/>
     <mergeCell ref="AM25:AN25"/>
     <mergeCell ref="AO25:AP25"/>
     <mergeCell ref="AV25:AW25"/>
@@ -7613,62 +7292,53 @@
     <mergeCell ref="AQ25:AR25"/>
     <mergeCell ref="AT25:AU25"/>
     <mergeCell ref="AT18:AU18"/>
-    <mergeCell ref="AI32:AJ32"/>
-    <mergeCell ref="AK32:AL32"/>
-    <mergeCell ref="AG52:AI52"/>
-    <mergeCell ref="AJ52:AL52"/>
-    <mergeCell ref="AG49:AI49"/>
-    <mergeCell ref="AJ49:AL49"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AJ48:AL48"/>
-    <mergeCell ref="AG37:AI37"/>
-    <mergeCell ref="AJ37:AL37"/>
-    <mergeCell ref="AJ36:AL36"/>
+    <mergeCell ref="AI30:AJ30"/>
+    <mergeCell ref="AK30:AL30"/>
+    <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AJ50:AL50"/>
+    <mergeCell ref="AG47:AI47"/>
+    <mergeCell ref="AJ47:AL47"/>
+    <mergeCell ref="AG46:AI46"/>
+    <mergeCell ref="AJ46:AL46"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AJ38:AL38"/>
-    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ36:AL36"/>
     <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AJ28:AL28"/>
-    <mergeCell ref="AG46:AI46"/>
-    <mergeCell ref="AJ46:AL46"/>
-    <mergeCell ref="AV59:AW59"/>
-    <mergeCell ref="AX59:AY59"/>
-    <mergeCell ref="AQ59:AR59"/>
-    <mergeCell ref="AT59:AU59"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="AA53:AC53"/>
-    <mergeCell ref="AD53:AF53"/>
-    <mergeCell ref="V54:W54"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="AA54:AC54"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="X52:Z52"/>
-    <mergeCell ref="AA52:AC52"/>
-    <mergeCell ref="AD52:AF52"/>
+    <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AJ44:AL44"/>
+    <mergeCell ref="AV55:AW55"/>
+    <mergeCell ref="AX55:AY55"/>
     <mergeCell ref="AQ55:AR55"/>
     <mergeCell ref="AT55:AU55"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="V49:W49"/>
-    <mergeCell ref="X49:Z49"/>
-    <mergeCell ref="AA49:AC49"/>
-    <mergeCell ref="AD49:AF49"/>
-    <mergeCell ref="AA48:AC48"/>
-    <mergeCell ref="AD48:AF48"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="X50:Z50"/>
+    <mergeCell ref="AA50:AC50"/>
+    <mergeCell ref="AD50:AF50"/>
+    <mergeCell ref="AQ51:AR51"/>
+    <mergeCell ref="AT51:AU51"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="V47:W47"/>
+    <mergeCell ref="X47:Z47"/>
+    <mergeCell ref="AA47:AC47"/>
+    <mergeCell ref="AD47:AF47"/>
+    <mergeCell ref="AA46:AC46"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="T30:V30"/>
+    <mergeCell ref="W30:X30"/>
     <mergeCell ref="T24:U24"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="X22:Z22"/>
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="V25:W25"/>
-    <mergeCell ref="AA46:AC46"/>
-    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AA44:AC44"/>
+    <mergeCell ref="AD44:AF44"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="R24:S24"/>
@@ -7681,102 +7351,92 @@
     <mergeCell ref="AD20:AF20"/>
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="R62:U62"/>
-    <mergeCell ref="K62:Q62"/>
-    <mergeCell ref="B64:M64"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="T53:U53"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="R59:S59"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="R57:S57"/>
+    <mergeCell ref="R58:U58"/>
+    <mergeCell ref="K58:Q58"/>
+    <mergeCell ref="B60:M60"/>
     <mergeCell ref="AG8:AH8"/>
     <mergeCell ref="AI8:AL8"/>
-    <mergeCell ref="L55:Q55"/>
-    <mergeCell ref="S55:X55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AG55:AL55"/>
-    <mergeCell ref="K57:Q57"/>
-    <mergeCell ref="R57:X57"/>
-    <mergeCell ref="Y57:AE57"/>
-    <mergeCell ref="AF57:AL57"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="R30:X30"/>
-    <mergeCell ref="Y30:AE30"/>
-    <mergeCell ref="AF30:AL30"/>
-    <mergeCell ref="K56:Q56"/>
-    <mergeCell ref="R56:X56"/>
-    <mergeCell ref="D51:Q51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:Q52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="L51:Q51"/>
+    <mergeCell ref="S51:X51"/>
+    <mergeCell ref="Z51:AE51"/>
+    <mergeCell ref="AG51:AL51"/>
+    <mergeCell ref="K53:Q53"/>
+    <mergeCell ref="R53:X53"/>
+    <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="AF53:AL53"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:X28"/>
+    <mergeCell ref="Y28:AE28"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="K52:Q52"/>
+    <mergeCell ref="R52:X52"/>
     <mergeCell ref="D49:Q49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="AR70:BH71"/>
-    <mergeCell ref="AV67:BH67"/>
-    <mergeCell ref="AG53:AI53"/>
-    <mergeCell ref="AJ53:AL53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:Q54"/>
-    <mergeCell ref="AZ61:BA61"/>
-    <mergeCell ref="AZ62:BA62"/>
-    <mergeCell ref="AZ63:BA63"/>
-    <mergeCell ref="AQ62:AR62"/>
-    <mergeCell ref="AQ60:AR60"/>
-    <mergeCell ref="AT60:AU60"/>
-    <mergeCell ref="BB60:BC60"/>
-    <mergeCell ref="BE60:BF60"/>
-    <mergeCell ref="AZ60:BA60"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:Q50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:Q47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="AR66:BH67"/>
+    <mergeCell ref="AV63:BH63"/>
+    <mergeCell ref="AZ57:BA57"/>
+    <mergeCell ref="AZ58:BA58"/>
+    <mergeCell ref="AZ59:BA59"/>
+    <mergeCell ref="AQ58:AR58"/>
+    <mergeCell ref="AQ56:AR56"/>
+    <mergeCell ref="AT56:AU56"/>
+    <mergeCell ref="BB56:BC56"/>
+    <mergeCell ref="BE56:BF56"/>
+    <mergeCell ref="AZ56:BA56"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="BG54:BH54"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="V61:AL61"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="X67:AC67"/>
+    <mergeCell ref="AH67:AL67"/>
+    <mergeCell ref="B62:C67"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="J67:S67"/>
+    <mergeCell ref="T67:W67"/>
+    <mergeCell ref="AM66:AQ67"/>
+    <mergeCell ref="AD67:AG67"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="B59:M59"/>
+    <mergeCell ref="K55:Q56"/>
     <mergeCell ref="H58:J58"/>
-    <mergeCell ref="BG58:BH58"/>
-    <mergeCell ref="B65:U65"/>
-    <mergeCell ref="V65:AL65"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="X71:AC71"/>
-    <mergeCell ref="AH71:AL71"/>
-    <mergeCell ref="B66:C71"/>
-    <mergeCell ref="D71:H71"/>
-    <mergeCell ref="J71:S71"/>
-    <mergeCell ref="T71:W71"/>
-    <mergeCell ref="AM70:AQ71"/>
-    <mergeCell ref="AD71:AG71"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="B63:M63"/>
-    <mergeCell ref="K59:Q60"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="M58:O58"/>
-    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="X62:AC62"/>
+    <mergeCell ref="AH62:AL62"/>
+    <mergeCell ref="X63:AC63"/>
+    <mergeCell ref="AH63:AL63"/>
+    <mergeCell ref="X64:AC64"/>
+    <mergeCell ref="AH64:AL64"/>
+    <mergeCell ref="X65:AC65"/>
+    <mergeCell ref="AH65:AL65"/>
     <mergeCell ref="X66:AC66"/>
     <mergeCell ref="AH66:AL66"/>
-    <mergeCell ref="X67:AC67"/>
-    <mergeCell ref="AH67:AL67"/>
-    <mergeCell ref="X68:AC68"/>
-    <mergeCell ref="AH68:AL68"/>
-    <mergeCell ref="X69:AC69"/>
-    <mergeCell ref="AH69:AL69"/>
-    <mergeCell ref="X70:AC70"/>
-    <mergeCell ref="AH70:AL70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="T63:U63"/>
-    <mergeCell ref="T64:U64"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="T57:U57"/>
+    <mergeCell ref="T59:U59"/>
+    <mergeCell ref="T60:U60"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="9.3503937007874127E-3" right="0.19685039370078741" top="0.31496062992125984" bottom="0" header="0" footer="0"/>

--- a/app/templates/protocol_template_2.xlsx
+++ b/app/templates/protocol_template_2.xlsx
@@ -2393,11 +2393,11 @@
         <v>20</v>
       </c>
       <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="171">
+      <c r="D9" s="171">
         <f>D4</f>
         <v>0</v>
       </c>
+      <c r="E9" s="171"/>
       <c r="F9" s="171"/>
       <c r="G9" s="171"/>
       <c r="H9" s="171"/>
@@ -3999,11 +3999,11 @@
         <v>27</v>
       </c>
       <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="171">
+      <c r="D33" s="171">
         <f>D7</f>
         <v>0</v>
       </c>
+      <c r="E33" s="171"/>
       <c r="F33" s="171"/>
       <c r="G33" s="171"/>
       <c r="H33" s="171"/>
@@ -6625,7 +6625,7 @@
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="X17:Z17"/>
     <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="E9:U9"/>
+    <mergeCell ref="D9:U9"/>
     <mergeCell ref="AJ10:AL10"/>
     <mergeCell ref="AG10:AI10"/>
     <mergeCell ref="AD10:AF10"/>
@@ -6653,7 +6653,7 @@
     <mergeCell ref="T17:U17"/>
     <mergeCell ref="R26:S26"/>
     <mergeCell ref="R17:S17"/>
-    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="X14:Z14"/>
@@ -6701,7 +6701,7 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="X25:Z25"/>
@@ -7218,7 +7218,7 @@
     <mergeCell ref="AM60:AN60"/>
     <mergeCell ref="BG59:BH59"/>
     <mergeCell ref="AM59:AN59"/>
-    <mergeCell ref="E33:U33"/>
+    <mergeCell ref="D33:U33"/>
     <mergeCell ref="BG55:BH55"/>
     <mergeCell ref="AM56:AN56"/>
     <mergeCell ref="AO56:AP56"/>
